--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY170"/>
+  <dimension ref="A1:AY176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23677,6 +23677,788 @@
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>67626396</v>
+      </c>
+      <c r="B171" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>537632</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6657004</v>
+      </c>
+      <c r="S171" t="n">
+        <v>5</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2017-09-16</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2017-09-16</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>mest mossigt men här och var örtrikt</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>96304670</v>
+      </c>
+      <c r="B172" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>537735</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6656772</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t># Picea abies</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>6611593</v>
+      </c>
+      <c r="B173" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>537723</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6656738</v>
+      </c>
+      <c r="S173" t="n">
+        <v>5</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2011-09-21</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2011-09-21</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>kalkgranskog med inslag av asp</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>96304894</v>
+      </c>
+      <c r="B174" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>537700</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6656742</v>
+      </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t># Picea abies</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>6611592</v>
+      </c>
+      <c r="B175" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>537691</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6656708</v>
+      </c>
+      <c r="S175" t="n">
+        <v>5</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2011-09-21</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2011-09-21</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>kalkgranskog med inslag av asp</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>96304643</v>
+      </c>
+      <c r="B176" t="n">
+        <v>89772</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Sörsnäset, Dlr</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>537765</v>
+      </c>
+      <c r="R176" t="n">
+        <v>6656863</v>
+      </c>
+      <c r="S176" t="n">
+        <v>5</v>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>Smedjebacken</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Söderbärke</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AD176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO176" t="inlineStr">
+        <is>
+          <t># Picea abies</t>
+        </is>
+      </c>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX176" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -25212,7 +25212,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076866</v>
+        <v>120076366</v>
       </c>
       <c r="B183" t="n">
         <v>91317</v>
@@ -25245,16 +25245,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25263,10 +25255,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537754</v>
+        <v>537677</v>
       </c>
       <c r="R183" t="n">
-        <v>6656827</v>
+        <v>6656730</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25331,9 +25323,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25351,7 +25348,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076366</v>
+        <v>120076866</v>
       </c>
       <c r="B184" t="n">
         <v>91317</v>
@@ -25384,8 +25381,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -25394,10 +25399,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537677</v>
+        <v>537754</v>
       </c>
       <c r="R184" t="n">
-        <v>6656730</v>
+        <v>6656827</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25462,14 +25467,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -25212,7 +25212,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076366</v>
+        <v>120076866</v>
       </c>
       <c r="B183" t="n">
         <v>91317</v>
@@ -25245,8 +25245,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25255,10 +25263,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537677</v>
+        <v>537754</v>
       </c>
       <c r="R183" t="n">
-        <v>6656730</v>
+        <v>6656827</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25323,14 +25331,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25348,7 +25351,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076866</v>
+        <v>120076366</v>
       </c>
       <c r="B184" t="n">
         <v>91317</v>
@@ -25381,16 +25384,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -25399,10 +25394,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537754</v>
+        <v>537677</v>
       </c>
       <c r="R184" t="n">
-        <v>6656827</v>
+        <v>6656730</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25467,9 +25462,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,7 +24790,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076873</v>
+        <v>120076829</v>
       </c>
       <c r="B180" t="n">
         <v>91317</v>
@@ -24825,7 +24825,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -24841,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537760</v>
+        <v>537715</v>
       </c>
       <c r="R180" t="n">
-        <v>6656840</v>
+        <v>6656750</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24929,7 +24929,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076805</v>
+        <v>120076366</v>
       </c>
       <c r="B181" t="n">
         <v>91317</v>
@@ -24962,16 +24962,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -24980,10 +24972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537663</v>
+        <v>537677</v>
       </c>
       <c r="R181" t="n">
-        <v>6656709</v>
+        <v>6656730</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25055,7 +25047,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25073,10 +25065,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076879</v>
+        <v>120076850</v>
       </c>
       <c r="B182" t="n">
-        <v>91317</v>
+        <v>91494</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25085,37 +25077,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -25124,10 +25108,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537784</v>
+        <v>537744</v>
       </c>
       <c r="R182" t="n">
-        <v>6656889</v>
+        <v>6656806</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25184,17 +25168,17 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25212,7 +25196,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076866</v>
+        <v>120076805</v>
       </c>
       <c r="B183" t="n">
         <v>91317</v>
@@ -25247,7 +25231,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25263,10 +25247,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537754</v>
+        <v>537663</v>
       </c>
       <c r="R183" t="n">
-        <v>6656827</v>
+        <v>6656709</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25331,9 +25315,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25351,10 +25340,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076366</v>
+        <v>120076351</v>
       </c>
       <c r="B184" t="n">
-        <v>91317</v>
+        <v>86381</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25363,29 +25352,37 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
@@ -25394,10 +25391,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537677</v>
+        <v>537522</v>
       </c>
       <c r="R184" t="n">
-        <v>6656730</v>
+        <v>6656647</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25432,6 +25429,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25454,22 +25456,17 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25626,10 +25623,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076789</v>
+        <v>120076879</v>
       </c>
       <c r="B186" t="n">
-        <v>90825</v>
+        <v>91317</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -25642,25 +25639,33 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -25669,10 +25674,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537696</v>
+        <v>537784</v>
       </c>
       <c r="R186" t="n">
-        <v>6656708</v>
+        <v>6656889</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25737,14 +25742,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25762,7 +25762,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076829</v>
+        <v>120076866</v>
       </c>
       <c r="B187" t="n">
         <v>91317</v>
@@ -25797,7 +25797,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -25813,10 +25813,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537715</v>
+        <v>537754</v>
       </c>
       <c r="R187" t="n">
-        <v>6656750</v>
+        <v>6656827</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25901,10 +25901,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076850</v>
+        <v>120076873</v>
       </c>
       <c r="B188" t="n">
-        <v>91494</v>
+        <v>91317</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25913,29 +25913,37 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -25944,10 +25952,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537744</v>
+        <v>537760</v>
       </c>
       <c r="R188" t="n">
-        <v>6656806</v>
+        <v>6656840</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26004,17 +26012,17 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -26032,10 +26040,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076351</v>
+        <v>120076789</v>
       </c>
       <c r="B189" t="n">
-        <v>86381</v>
+        <v>90825</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26044,37 +26052,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>248955</v>
+        <v>73</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -26083,10 +26083,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537522</v>
+        <v>537696</v>
       </c>
       <c r="R189" t="n">
-        <v>6656647</v>
+        <v>6656708</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26121,11 +26121,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -26148,17 +26143,22 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076829</v>
+        <v>120076789</v>
       </c>
       <c r="B180" t="n">
-        <v>91317</v>
+        <v>90825</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24806,33 +24806,25 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -24841,10 +24833,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537715</v>
+        <v>537696</v>
       </c>
       <c r="R180" t="n">
-        <v>6656750</v>
+        <v>6656708</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24909,9 +24901,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24929,7 +24926,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076366</v>
+        <v>120076873</v>
       </c>
       <c r="B181" t="n">
         <v>91317</v>
@@ -24962,8 +24959,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -24972,10 +24977,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537677</v>
+        <v>537760</v>
       </c>
       <c r="R181" t="n">
-        <v>6656730</v>
+        <v>6656840</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25040,14 +25045,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25065,10 +25065,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076850</v>
+        <v>120076805</v>
       </c>
       <c r="B182" t="n">
-        <v>91494</v>
+        <v>91317</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25077,29 +25077,37 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -25108,10 +25116,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537744</v>
+        <v>537663</v>
       </c>
       <c r="R182" t="n">
-        <v>6656806</v>
+        <v>6656709</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25168,17 +25176,22 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM182" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25196,7 +25209,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076805</v>
+        <v>120076879</v>
       </c>
       <c r="B183" t="n">
         <v>91317</v>
@@ -25231,7 +25244,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25247,10 +25260,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537663</v>
+        <v>537784</v>
       </c>
       <c r="R183" t="n">
-        <v>6656709</v>
+        <v>6656889</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25315,14 +25328,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25340,10 +25348,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076351</v>
+        <v>120076829</v>
       </c>
       <c r="B184" t="n">
-        <v>86381</v>
+        <v>91317</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25352,30 +25360,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25391,10 +25399,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537522</v>
+        <v>537715</v>
       </c>
       <c r="R184" t="n">
-        <v>6656647</v>
+        <v>6656750</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25429,11 +25437,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25456,17 +25459,17 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25484,10 +25487,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076824</v>
+        <v>120076351</v>
       </c>
       <c r="B185" t="n">
-        <v>91317</v>
+        <v>86381</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25496,30 +25499,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -25535,10 +25538,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537719</v>
+        <v>537522</v>
       </c>
       <c r="R185" t="n">
-        <v>6656716</v>
+        <v>6656647</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25573,6 +25576,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25595,17 +25603,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25623,7 +25631,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076879</v>
+        <v>120076824</v>
       </c>
       <c r="B186" t="n">
         <v>91317</v>
@@ -25658,7 +25666,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25674,10 +25682,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537784</v>
+        <v>537719</v>
       </c>
       <c r="R186" t="n">
-        <v>6656889</v>
+        <v>6656716</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25762,10 +25770,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076866</v>
+        <v>120076850</v>
       </c>
       <c r="B187" t="n">
-        <v>91317</v>
+        <v>91494</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -25774,37 +25782,29 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -25813,10 +25813,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537754</v>
+        <v>537744</v>
       </c>
       <c r="R187" t="n">
-        <v>6656827</v>
+        <v>6656806</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25873,17 +25873,17 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25901,7 +25901,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076873</v>
+        <v>120076866</v>
       </c>
       <c r="B188" t="n">
         <v>91317</v>
@@ -25936,7 +25936,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -25952,10 +25952,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537760</v>
+        <v>537754</v>
       </c>
       <c r="R188" t="n">
-        <v>6656840</v>
+        <v>6656827</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26040,10 +26040,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076789</v>
+        <v>120076366</v>
       </c>
       <c r="B189" t="n">
-        <v>90825</v>
+        <v>91317</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26056,21 +26056,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -26083,10 +26083,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537696</v>
+        <v>537677</v>
       </c>
       <c r="R189" t="n">
-        <v>6656708</v>
+        <v>6656730</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076789</v>
+        <v>120076366</v>
       </c>
       <c r="B180" t="n">
-        <v>90825</v>
+        <v>91317</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24806,21 +24806,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -24833,10 +24833,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537696</v>
+        <v>537677</v>
       </c>
       <c r="R180" t="n">
-        <v>6656708</v>
+        <v>6656730</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -25065,7 +25065,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076805</v>
+        <v>120076879</v>
       </c>
       <c r="B182" t="n">
         <v>91317</v>
@@ -25100,7 +25100,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25116,10 +25116,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537663</v>
+        <v>537784</v>
       </c>
       <c r="R182" t="n">
-        <v>6656709</v>
+        <v>6656889</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25184,14 +25184,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM182" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25209,7 +25204,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076879</v>
+        <v>120076805</v>
       </c>
       <c r="B183" t="n">
         <v>91317</v>
@@ -25244,7 +25239,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25260,10 +25255,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537784</v>
+        <v>537663</v>
       </c>
       <c r="R183" t="n">
-        <v>6656889</v>
+        <v>6656709</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25328,9 +25323,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25348,10 +25348,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076829</v>
+        <v>120076351</v>
       </c>
       <c r="B184" t="n">
-        <v>91317</v>
+        <v>86381</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25360,30 +25360,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25399,10 +25399,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537715</v>
+        <v>537522</v>
       </c>
       <c r="R184" t="n">
-        <v>6656750</v>
+        <v>6656647</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25437,6 +25437,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25459,17 +25464,17 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25487,10 +25492,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076351</v>
+        <v>120076829</v>
       </c>
       <c r="B185" t="n">
-        <v>86381</v>
+        <v>91317</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25499,30 +25504,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -25538,10 +25543,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537522</v>
+        <v>537715</v>
       </c>
       <c r="R185" t="n">
-        <v>6656647</v>
+        <v>6656750</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25576,11 +25581,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25603,17 +25603,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25631,7 +25631,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076824</v>
+        <v>120076866</v>
       </c>
       <c r="B186" t="n">
         <v>91317</v>
@@ -25666,7 +25666,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25682,10 +25682,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537719</v>
+        <v>537754</v>
       </c>
       <c r="R186" t="n">
-        <v>6656716</v>
+        <v>6656827</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25770,10 +25770,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076850</v>
+        <v>120076789</v>
       </c>
       <c r="B187" t="n">
-        <v>91494</v>
+        <v>90825</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -25782,25 +25782,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4769</v>
+        <v>73</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -25813,10 +25813,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537744</v>
+        <v>537696</v>
       </c>
       <c r="R187" t="n">
-        <v>6656806</v>
+        <v>6656708</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25873,17 +25873,22 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25901,7 +25906,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076866</v>
+        <v>120076824</v>
       </c>
       <c r="B188" t="n">
         <v>91317</v>
@@ -25936,7 +25941,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -25952,10 +25957,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537754</v>
+        <v>537719</v>
       </c>
       <c r="R188" t="n">
-        <v>6656827</v>
+        <v>6656716</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26040,10 +26045,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076366</v>
+        <v>120076850</v>
       </c>
       <c r="B189" t="n">
-        <v>91317</v>
+        <v>91494</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26052,25 +26057,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -26083,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537677</v>
+        <v>537744</v>
       </c>
       <c r="R189" t="n">
-        <v>6656730</v>
+        <v>6656806</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26143,22 +26148,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076366</v>
+        <v>120076829</v>
       </c>
       <c r="B180" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24823,8 +24823,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -24833,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537677</v>
+        <v>537715</v>
       </c>
       <c r="R180" t="n">
-        <v>6656730</v>
+        <v>6656750</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24901,14 +24909,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24926,10 +24929,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076873</v>
+        <v>120076805</v>
       </c>
       <c r="B181" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -24961,7 +24964,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -24977,10 +24980,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537760</v>
+        <v>537663</v>
       </c>
       <c r="R181" t="n">
-        <v>6656840</v>
+        <v>6656709</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25045,9 +25048,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25065,10 +25073,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076879</v>
+        <v>120076873</v>
       </c>
       <c r="B182" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25100,7 +25108,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25116,10 +25124,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537784</v>
+        <v>537760</v>
       </c>
       <c r="R182" t="n">
-        <v>6656889</v>
+        <v>6656840</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25204,10 +25212,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076805</v>
+        <v>120076879</v>
       </c>
       <c r="B183" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25239,7 +25247,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -25255,10 +25263,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537663</v>
+        <v>537784</v>
       </c>
       <c r="R183" t="n">
-        <v>6656709</v>
+        <v>6656889</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25323,14 +25331,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25348,10 +25351,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076351</v>
+        <v>120076824</v>
       </c>
       <c r="B184" t="n">
-        <v>86381</v>
+        <v>91335</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -25360,30 +25363,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25399,10 +25402,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537522</v>
+        <v>537719</v>
       </c>
       <c r="R184" t="n">
-        <v>6656647</v>
+        <v>6656716</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25437,11 +25440,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
@@ -25464,17 +25462,17 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25492,10 +25490,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076829</v>
+        <v>120076351</v>
       </c>
       <c r="B185" t="n">
-        <v>91317</v>
+        <v>86398</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25504,30 +25502,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -25543,10 +25541,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537715</v>
+        <v>537522</v>
       </c>
       <c r="R185" t="n">
-        <v>6656750</v>
+        <v>6656647</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25581,6 +25579,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25603,17 +25606,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25631,10 +25634,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076866</v>
+        <v>120076366</v>
       </c>
       <c r="B186" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -25664,16 +25667,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -25682,10 +25677,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537754</v>
+        <v>537677</v>
       </c>
       <c r="R186" t="n">
-        <v>6656827</v>
+        <v>6656730</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25750,9 +25745,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25770,10 +25770,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076789</v>
+        <v>120076850</v>
       </c>
       <c r="B187" t="n">
-        <v>90825</v>
+        <v>91512</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -25782,25 +25782,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>73</v>
+        <v>4769</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -25813,10 +25813,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537696</v>
+        <v>537744</v>
       </c>
       <c r="R187" t="n">
-        <v>6656708</v>
+        <v>6656806</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25873,22 +25873,17 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25906,10 +25901,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076824</v>
+        <v>120076866</v>
       </c>
       <c r="B188" t="n">
-        <v>91317</v>
+        <v>91335</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25941,7 +25936,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -25957,10 +25952,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537719</v>
+        <v>537754</v>
       </c>
       <c r="R188" t="n">
-        <v>6656716</v>
+        <v>6656827</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26045,10 +26040,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076850</v>
+        <v>120076789</v>
       </c>
       <c r="B189" t="n">
-        <v>91494</v>
+        <v>90843</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26057,25 +26052,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4769</v>
+        <v>73</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -26088,10 +26083,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537744</v>
+        <v>537696</v>
       </c>
       <c r="R189" t="n">
-        <v>6656806</v>
+        <v>6656708</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26148,17 +26143,22 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM189" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076829</v>
+        <v>120076850</v>
       </c>
       <c r="B180" t="n">
-        <v>91335</v>
+        <v>91512</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24802,37 +24802,29 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -24841,10 +24833,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537715</v>
+        <v>537744</v>
       </c>
       <c r="R180" t="n">
-        <v>6656750</v>
+        <v>6656806</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24901,17 +24893,17 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24929,7 +24921,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076805</v>
+        <v>120076366</v>
       </c>
       <c r="B181" t="n">
         <v>91335</v>
@@ -24962,16 +24954,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -24980,10 +24964,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537663</v>
+        <v>537677</v>
       </c>
       <c r="R181" t="n">
-        <v>6656709</v>
+        <v>6656730</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25055,7 +25039,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25073,7 +25057,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076873</v>
+        <v>120076866</v>
       </c>
       <c r="B182" t="n">
         <v>91335</v>
@@ -25108,7 +25092,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25124,10 +25108,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537760</v>
+        <v>537754</v>
       </c>
       <c r="R182" t="n">
-        <v>6656840</v>
+        <v>6656827</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25212,10 +25196,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076879</v>
+        <v>120076789</v>
       </c>
       <c r="B183" t="n">
-        <v>91335</v>
+        <v>90843</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25228,33 +25212,25 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25263,10 +25239,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537784</v>
+        <v>537696</v>
       </c>
       <c r="R183" t="n">
-        <v>6656889</v>
+        <v>6656708</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25331,9 +25307,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25351,7 +25332,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076824</v>
+        <v>120076805</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25386,7 +25367,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25402,10 +25383,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537719</v>
+        <v>537663</v>
       </c>
       <c r="R184" t="n">
-        <v>6656716</v>
+        <v>6656709</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25470,9 +25451,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25490,10 +25476,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076351</v>
+        <v>120076829</v>
       </c>
       <c r="B185" t="n">
-        <v>86398</v>
+        <v>91335</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25502,30 +25488,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -25541,10 +25527,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537522</v>
+        <v>537715</v>
       </c>
       <c r="R185" t="n">
-        <v>6656647</v>
+        <v>6656750</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25579,11 +25565,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25606,17 +25587,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25634,10 +25615,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076366</v>
+        <v>120076351</v>
       </c>
       <c r="B186" t="n">
-        <v>91335</v>
+        <v>86398</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -25646,29 +25627,37 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -25677,10 +25666,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537677</v>
+        <v>537522</v>
       </c>
       <c r="R186" t="n">
-        <v>6656730</v>
+        <v>6656647</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25715,6 +25704,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -25737,22 +25731,17 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25770,10 +25759,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076850</v>
+        <v>120076879</v>
       </c>
       <c r="B187" t="n">
-        <v>91512</v>
+        <v>91335</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -25782,29 +25771,37 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -25813,10 +25810,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537744</v>
+        <v>537784</v>
       </c>
       <c r="R187" t="n">
-        <v>6656806</v>
+        <v>6656889</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25873,17 +25870,17 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25901,7 +25898,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076866</v>
+        <v>120076873</v>
       </c>
       <c r="B188" t="n">
         <v>91335</v>
@@ -25936,7 +25933,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -25952,10 +25949,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537754</v>
+        <v>537760</v>
       </c>
       <c r="R188" t="n">
-        <v>6656827</v>
+        <v>6656840</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26040,10 +26037,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076789</v>
+        <v>120076824</v>
       </c>
       <c r="B189" t="n">
-        <v>90843</v>
+        <v>91335</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26056,25 +26053,33 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -26083,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537696</v>
+        <v>537719</v>
       </c>
       <c r="R189" t="n">
-        <v>6656708</v>
+        <v>6656716</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26151,14 +26156,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM189" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076850</v>
+        <v>120076873</v>
       </c>
       <c r="B180" t="n">
-        <v>91512</v>
+        <v>91335</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24802,29 +24802,37 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
@@ -24833,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537744</v>
+        <v>537760</v>
       </c>
       <c r="R180" t="n">
-        <v>6656806</v>
+        <v>6656840</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24893,17 +24901,17 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24921,7 +24929,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076366</v>
+        <v>120076824</v>
       </c>
       <c r="B181" t="n">
         <v>91335</v>
@@ -24954,8 +24962,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -24964,10 +24980,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537677</v>
+        <v>537719</v>
       </c>
       <c r="R181" t="n">
-        <v>6656730</v>
+        <v>6656716</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25032,14 +25048,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25057,7 +25068,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076866</v>
+        <v>120076829</v>
       </c>
       <c r="B182" t="n">
         <v>91335</v>
@@ -25092,7 +25103,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25108,10 +25119,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537754</v>
+        <v>537715</v>
       </c>
       <c r="R182" t="n">
-        <v>6656827</v>
+        <v>6656750</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25196,10 +25207,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076789</v>
+        <v>120076366</v>
       </c>
       <c r="B183" t="n">
-        <v>90843</v>
+        <v>91335</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25212,21 +25223,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -25239,10 +25250,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537696</v>
+        <v>537677</v>
       </c>
       <c r="R183" t="n">
-        <v>6656708</v>
+        <v>6656730</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25332,7 +25343,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076805</v>
+        <v>120076879</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25367,7 +25378,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25383,10 +25394,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537663</v>
+        <v>537784</v>
       </c>
       <c r="R184" t="n">
-        <v>6656709</v>
+        <v>6656889</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25451,14 +25462,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM184" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25476,10 +25482,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076829</v>
+        <v>120076850</v>
       </c>
       <c r="B185" t="n">
-        <v>91335</v>
+        <v>91512</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25488,37 +25494,29 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -25527,10 +25525,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537715</v>
+        <v>537744</v>
       </c>
       <c r="R185" t="n">
-        <v>6656750</v>
+        <v>6656806</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25587,17 +25585,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25615,10 +25613,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076351</v>
+        <v>120076866</v>
       </c>
       <c r="B186" t="n">
-        <v>86398</v>
+        <v>91335</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -25627,30 +25625,30 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25666,10 +25664,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537522</v>
+        <v>537754</v>
       </c>
       <c r="R186" t="n">
-        <v>6656647</v>
+        <v>6656827</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25704,11 +25702,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -25731,17 +25724,17 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25759,7 +25752,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076879</v>
+        <v>120076805</v>
       </c>
       <c r="B187" t="n">
         <v>91335</v>
@@ -25794,7 +25787,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -25810,10 +25803,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537784</v>
+        <v>537663</v>
       </c>
       <c r="R187" t="n">
-        <v>6656889</v>
+        <v>6656709</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25878,9 +25871,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25898,10 +25896,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076873</v>
+        <v>120076789</v>
       </c>
       <c r="B188" t="n">
-        <v>91335</v>
+        <v>90843</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25914,33 +25912,25 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -25949,10 +25939,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537760</v>
+        <v>537696</v>
       </c>
       <c r="R188" t="n">
-        <v>6656840</v>
+        <v>6656708</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26017,9 +26007,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -26037,10 +26032,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076824</v>
+        <v>120076351</v>
       </c>
       <c r="B189" t="n">
-        <v>91335</v>
+        <v>86398</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26049,30 +26044,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -26088,10 +26083,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537719</v>
+        <v>537522</v>
       </c>
       <c r="R189" t="n">
-        <v>6656716</v>
+        <v>6656647</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26126,6 +26121,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -26148,17 +26148,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076873</v>
+        <v>120076351</v>
       </c>
       <c r="B180" t="n">
-        <v>91335</v>
+        <v>86398</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24802,30 +24802,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -24841,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537760</v>
+        <v>537522</v>
       </c>
       <c r="R180" t="n">
-        <v>6656840</v>
+        <v>6656647</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24879,6 +24879,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -24901,17 +24906,17 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24929,7 +24934,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076824</v>
+        <v>120076829</v>
       </c>
       <c r="B181" t="n">
         <v>91335</v>
@@ -24964,7 +24969,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -24980,10 +24985,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537719</v>
+        <v>537715</v>
       </c>
       <c r="R181" t="n">
-        <v>6656716</v>
+        <v>6656750</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25068,7 +25073,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076829</v>
+        <v>120076866</v>
       </c>
       <c r="B182" t="n">
         <v>91335</v>
@@ -25103,7 +25108,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25119,10 +25124,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537715</v>
+        <v>537754</v>
       </c>
       <c r="R182" t="n">
-        <v>6656750</v>
+        <v>6656827</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25343,7 +25348,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076879</v>
+        <v>120076824</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25378,7 +25383,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25394,10 +25399,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537784</v>
+        <v>537719</v>
       </c>
       <c r="R184" t="n">
-        <v>6656889</v>
+        <v>6656716</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25482,10 +25487,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076850</v>
+        <v>120076789</v>
       </c>
       <c r="B185" t="n">
-        <v>91512</v>
+        <v>90843</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25494,25 +25499,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4769</v>
+        <v>73</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Pilát) Audet</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -25525,10 +25530,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537744</v>
+        <v>537696</v>
       </c>
       <c r="R185" t="n">
-        <v>6656806</v>
+        <v>6656708</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25585,17 +25590,22 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25613,7 +25623,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076866</v>
+        <v>120076805</v>
       </c>
       <c r="B186" t="n">
         <v>91335</v>
@@ -25648,7 +25658,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25664,10 +25674,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537754</v>
+        <v>537663</v>
       </c>
       <c r="R186" t="n">
-        <v>6656827</v>
+        <v>6656709</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25732,9 +25742,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25752,7 +25767,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076805</v>
+        <v>120076879</v>
       </c>
       <c r="B187" t="n">
         <v>91335</v>
@@ -25787,7 +25802,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -25803,10 +25818,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537663</v>
+        <v>537784</v>
       </c>
       <c r="R187" t="n">
-        <v>6656709</v>
+        <v>6656889</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25871,14 +25886,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25896,10 +25906,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076789</v>
+        <v>120076873</v>
       </c>
       <c r="B188" t="n">
-        <v>90843</v>
+        <v>91335</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25912,25 +25922,33 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -25939,10 +25957,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537696</v>
+        <v>537760</v>
       </c>
       <c r="R188" t="n">
-        <v>6656708</v>
+        <v>6656840</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26007,14 +26025,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM188" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -26032,10 +26045,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076351</v>
+        <v>120076850</v>
       </c>
       <c r="B189" t="n">
-        <v>86398</v>
+        <v>91512</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26044,37 +26057,29 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>248955</v>
+        <v>4769</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -26083,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537522</v>
+        <v>537744</v>
       </c>
       <c r="R189" t="n">
-        <v>6656647</v>
+        <v>6656806</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26119,11 +26124,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
         </is>
       </c>
       <c r="AD189" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,10 +24790,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076351</v>
+        <v>120076824</v>
       </c>
       <c r="B180" t="n">
-        <v>86398</v>
+        <v>91335</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -24802,30 +24802,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -24841,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537522</v>
+        <v>537719</v>
       </c>
       <c r="R180" t="n">
-        <v>6656647</v>
+        <v>6656716</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24879,11 +24879,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD180" t="b">
         <v>0</v>
       </c>
@@ -24906,17 +24901,17 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr"/>
@@ -24934,7 +24929,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076829</v>
+        <v>120076805</v>
       </c>
       <c r="B181" t="n">
         <v>91335</v>
@@ -24969,7 +24964,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -24985,10 +24980,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537715</v>
+        <v>537663</v>
       </c>
       <c r="R181" t="n">
-        <v>6656750</v>
+        <v>6656709</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25053,9 +25048,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25073,10 +25073,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076866</v>
+        <v>120076850</v>
       </c>
       <c r="B182" t="n">
-        <v>91335</v>
+        <v>91512</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25085,37 +25085,29 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -25124,10 +25116,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537754</v>
+        <v>537744</v>
       </c>
       <c r="R182" t="n">
-        <v>6656827</v>
+        <v>6656806</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25184,17 +25176,17 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25212,7 +25204,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076366</v>
+        <v>120076829</v>
       </c>
       <c r="B183" t="n">
         <v>91335</v>
@@ -25245,8 +25237,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25255,10 +25255,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537677</v>
+        <v>537715</v>
       </c>
       <c r="R183" t="n">
-        <v>6656730</v>
+        <v>6656750</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25323,14 +25323,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25348,7 +25343,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076824</v>
+        <v>120076873</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25383,7 +25378,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25399,10 +25394,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537719</v>
+        <v>537760</v>
       </c>
       <c r="R184" t="n">
-        <v>6656716</v>
+        <v>6656840</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25487,10 +25482,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076789</v>
+        <v>120076351</v>
       </c>
       <c r="B185" t="n">
-        <v>90843</v>
+        <v>86398</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25499,29 +25494,37 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>73</v>
+        <v>248955</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
@@ -25530,10 +25533,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537696</v>
+        <v>537522</v>
       </c>
       <c r="R185" t="n">
-        <v>6656708</v>
+        <v>6656647</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25568,6 +25571,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25590,22 +25598,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25623,7 +25626,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076805</v>
+        <v>120076866</v>
       </c>
       <c r="B186" t="n">
         <v>91335</v>
@@ -25658,7 +25661,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25674,10 +25677,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537663</v>
+        <v>537754</v>
       </c>
       <c r="R186" t="n">
-        <v>6656709</v>
+        <v>6656827</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25742,14 +25745,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM186" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25767,7 +25765,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076879</v>
+        <v>120076366</v>
       </c>
       <c r="B187" t="n">
         <v>91335</v>
@@ -25800,16 +25798,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -25818,10 +25808,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537784</v>
+        <v>537677</v>
       </c>
       <c r="R187" t="n">
-        <v>6656889</v>
+        <v>6656730</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25886,9 +25876,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -25906,10 +25901,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076873</v>
+        <v>120076789</v>
       </c>
       <c r="B188" t="n">
-        <v>91335</v>
+        <v>90843</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25922,33 +25917,25 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Flavidoporia pulvinascens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pilát) Audet</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
@@ -25957,10 +25944,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537760</v>
+        <v>537696</v>
       </c>
       <c r="R188" t="n">
-        <v>6656840</v>
+        <v>6656708</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -26025,9 +26012,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM188" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -26045,10 +26037,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076850</v>
+        <v>120076879</v>
       </c>
       <c r="B189" t="n">
-        <v>91512</v>
+        <v>91335</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26057,29 +26049,37 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537744</v>
+        <v>537784</v>
       </c>
       <c r="R189" t="n">
-        <v>6656806</v>
+        <v>6656889</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -26148,17 +26148,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr"/>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -25073,10 +25073,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076850</v>
+        <v>120076879</v>
       </c>
       <c r="B182" t="n">
-        <v>91512</v>
+        <v>91335</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25085,29 +25085,37 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
@@ -25116,10 +25124,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537744</v>
+        <v>537784</v>
       </c>
       <c r="R182" t="n">
-        <v>6656806</v>
+        <v>6656889</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25176,17 +25184,17 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25204,10 +25212,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076829</v>
+        <v>120076850</v>
       </c>
       <c r="B183" t="n">
-        <v>91335</v>
+        <v>91512</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25216,37 +25224,29 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25255,10 +25255,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537715</v>
+        <v>537744</v>
       </c>
       <c r="R183" t="n">
-        <v>6656750</v>
+        <v>6656806</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25315,17 +25315,17 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25343,7 +25343,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076873</v>
+        <v>120076866</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25394,10 +25394,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537760</v>
+        <v>537754</v>
       </c>
       <c r="R184" t="n">
-        <v>6656840</v>
+        <v>6656827</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25626,7 +25626,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076866</v>
+        <v>120076873</v>
       </c>
       <c r="B186" t="n">
         <v>91335</v>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -25677,10 +25677,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537754</v>
+        <v>537760</v>
       </c>
       <c r="R186" t="n">
-        <v>6656827</v>
+        <v>6656840</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -26037,7 +26037,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076879</v>
+        <v>120076829</v>
       </c>
       <c r="B189" t="n">
         <v>91335</v>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537784</v>
+        <v>537715</v>
       </c>
       <c r="R189" t="n">
-        <v>6656889</v>
+        <v>6656750</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -24790,7 +24790,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>120076824</v>
+        <v>120076879</v>
       </c>
       <c r="B180" t="n">
         <v>91335</v>
@@ -24825,7 +24825,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -24841,10 +24841,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>537719</v>
+        <v>537784</v>
       </c>
       <c r="R180" t="n">
-        <v>6656716</v>
+        <v>6656889</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -24929,10 +24929,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>120076805</v>
+        <v>120076850</v>
       </c>
       <c r="B181" t="n">
-        <v>91335</v>
+        <v>91512</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -24941,37 +24941,29 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
@@ -24980,10 +24972,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>537663</v>
+        <v>537744</v>
       </c>
       <c r="R181" t="n">
-        <v>6656709</v>
+        <v>6656806</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -25040,22 +25032,17 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr"/>
@@ -25073,10 +25060,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>120076879</v>
+        <v>120076351</v>
       </c>
       <c r="B182" t="n">
-        <v>91335</v>
+        <v>86398</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -25085,30 +25072,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -25124,10 +25111,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>537784</v>
+        <v>537522</v>
       </c>
       <c r="R182" t="n">
-        <v>6656889</v>
+        <v>6656647</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -25162,6 +25149,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
@@ -25184,17 +25176,17 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr"/>
@@ -25212,10 +25204,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>120076850</v>
+        <v>120076829</v>
       </c>
       <c r="B183" t="n">
-        <v>91512</v>
+        <v>91335</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -25224,29 +25216,37 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4769</v>
+        <v>366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
@@ -25255,10 +25255,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>537744</v>
+        <v>537715</v>
       </c>
       <c r="R183" t="n">
-        <v>6656806</v>
+        <v>6656750</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -25315,17 +25315,17 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr"/>
@@ -25343,7 +25343,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>120076866</v>
+        <v>120076805</v>
       </c>
       <c r="B184" t="n">
         <v>91335</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -25394,10 +25394,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>537754</v>
+        <v>537663</v>
       </c>
       <c r="R184" t="n">
-        <v>6656827</v>
+        <v>6656709</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -25462,9 +25462,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # murken asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr"/>
@@ -25482,10 +25487,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>120076351</v>
+        <v>120076824</v>
       </c>
       <c r="B185" t="n">
-        <v>86398</v>
+        <v>91335</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -25494,30 +25499,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>248955</v>
+        <v>366</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -25533,10 +25538,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>537522</v>
+        <v>537719</v>
       </c>
       <c r="R185" t="n">
-        <v>6656647</v>
+        <v>6656716</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -25571,11 +25576,6 @@
           <t>2024-09-28</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
@@ -25598,17 +25598,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr"/>
@@ -25626,7 +25626,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>120076873</v>
+        <v>120076366</v>
       </c>
       <c r="B186" t="n">
         <v>91335</v>
@@ -25659,16 +25659,8 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
@@ -25677,10 +25669,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>537760</v>
+        <v>537677</v>
       </c>
       <c r="R186" t="n">
-        <v>6656840</v>
+        <v>6656730</v>
       </c>
       <c r="S186" t="n">
         <v>5</v>
@@ -25745,9 +25737,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr"/>
@@ -25765,7 +25762,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>120076366</v>
+        <v>120076866</v>
       </c>
       <c r="B187" t="n">
         <v>91335</v>
@@ -25798,8 +25795,16 @@
           <t>(Pers.) Jülich</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
@@ -25808,10 +25813,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>537677</v>
+        <v>537754</v>
       </c>
       <c r="R187" t="n">
-        <v>6656730</v>
+        <v>6656827</v>
       </c>
       <c r="S187" t="n">
         <v>5</v>
@@ -25876,14 +25881,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # grov asplåga # Populus tremula</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -26037,7 +26037,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076829</v>
+        <v>120076873</v>
       </c>
       <c r="B189" t="n">
         <v>91335</v>
@@ -26072,7 +26072,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -26088,10 +26088,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537715</v>
+        <v>537760</v>
       </c>
       <c r="R189" t="n">
-        <v>6656750</v>
+        <v>6656840</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236163</v>
+        <v>121236146</v>
       </c>
       <c r="B190" t="n">
-        <v>90652</v>
+        <v>57501</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,47 +26168,42 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537447</v>
+        <v>537687</v>
       </c>
       <c r="R190" t="n">
-        <v>6656508</v>
+        <v>6656879</v>
       </c>
       <c r="S190" t="n">
         <v>4</v>
@@ -26501,10 +26496,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236146</v>
+        <v>121236163</v>
       </c>
       <c r="B193" t="n">
-        <v>57501</v>
+        <v>90652</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,42 +26508,47 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537687</v>
+        <v>537447</v>
       </c>
       <c r="R193" t="n">
-        <v>6656879</v>
+        <v>6656508</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -29026,10 +29026,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236190</v>
+        <v>121236194</v>
       </c>
       <c r="B215" t="n">
-        <v>90687</v>
+        <v>90652</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29038,25 +29038,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -29075,13 +29075,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537476</v>
+        <v>537520</v>
       </c>
       <c r="R215" t="n">
-        <v>6656522</v>
+        <v>6656530</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29141,10 +29141,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236194</v>
+        <v>121236149</v>
       </c>
       <c r="B216" t="n">
-        <v>90652</v>
+        <v>98071</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29153,50 +29153,50 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537520</v>
+        <v>537712</v>
       </c>
       <c r="R216" t="n">
-        <v>6656530</v>
+        <v>6657066</v>
       </c>
       <c r="S216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29220,12 +29220,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29256,10 +29256,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236160</v>
+        <v>121236175</v>
       </c>
       <c r="B217" t="n">
-        <v>94594</v>
+        <v>98071</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29268,35 +29268,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29305,13 +29305,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537624</v>
+        <v>537491</v>
       </c>
       <c r="R217" t="n">
-        <v>6656708</v>
+        <v>6656738</v>
       </c>
       <c r="S217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29335,12 +29335,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29371,10 +29371,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236170</v>
+        <v>121236160</v>
       </c>
       <c r="B218" t="n">
-        <v>98071</v>
+        <v>94594</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29383,35 +29383,35 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -29420,10 +29420,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537452</v>
+        <v>537624</v>
       </c>
       <c r="R218" t="n">
-        <v>6656767</v>
+        <v>6656708</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29450,12 +29450,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29486,10 +29486,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236174</v>
+        <v>121236190</v>
       </c>
       <c r="B219" t="n">
-        <v>98071</v>
+        <v>90687</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,50 +29498,50 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537502</v>
+        <v>537476</v>
       </c>
       <c r="R219" t="n">
-        <v>6656738</v>
+        <v>6656522</v>
       </c>
       <c r="S219" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29601,7 +29601,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236172</v>
+        <v>121236170</v>
       </c>
       <c r="B220" t="n">
         <v>98071</v>
@@ -29650,10 +29650,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537513</v>
+        <v>537452</v>
       </c>
       <c r="R220" t="n">
-        <v>6656728</v>
+        <v>6656767</v>
       </c>
       <c r="S220" t="n">
         <v>4</v>
@@ -29716,7 +29716,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236149</v>
+        <v>121236174</v>
       </c>
       <c r="B221" t="n">
         <v>98071</v>
@@ -29751,7 +29751,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -29761,17 +29761,17 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537712</v>
+        <v>537502</v>
       </c>
       <c r="R221" t="n">
-        <v>6657066</v>
+        <v>6656738</v>
       </c>
       <c r="S221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29795,12 +29795,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29831,7 +29831,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236175</v>
+        <v>121236172</v>
       </c>
       <c r="B222" t="n">
         <v>98071</v>
@@ -29866,7 +29866,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29880,13 +29880,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537491</v>
+        <v>537513</v>
       </c>
       <c r="R222" t="n">
-        <v>6656738</v>
+        <v>6656728</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236135</v>
+        <v>121236186</v>
       </c>
       <c r="B226" t="n">
         <v>98071</v>
@@ -30340,13 +30340,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537439</v>
+        <v>537546</v>
       </c>
       <c r="R226" t="n">
-        <v>6656570</v>
+        <v>6656619</v>
       </c>
       <c r="S226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30370,12 +30370,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30406,7 +30406,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236186</v>
+        <v>121236135</v>
       </c>
       <c r="B227" t="n">
         <v>98071</v>
@@ -30455,13 +30455,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537546</v>
+        <v>537439</v>
       </c>
       <c r="R227" t="n">
-        <v>6656619</v>
+        <v>6656570</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30485,12 +30485,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -32024,10 +32024,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236168</v>
+        <v>121236178</v>
       </c>
       <c r="B241" t="n">
-        <v>79583</v>
+        <v>57501</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32036,35 +32036,30 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32073,13 +32068,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537571</v>
+        <v>537468</v>
       </c>
       <c r="R241" t="n">
-        <v>6656818</v>
+        <v>6656748</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -32139,10 +32134,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236178</v>
+        <v>121236164</v>
       </c>
       <c r="B242" t="n">
-        <v>57501</v>
+        <v>98071</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32151,30 +32146,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32183,13 +32183,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537468</v>
+        <v>537484</v>
       </c>
       <c r="R242" t="n">
-        <v>6656748</v>
+        <v>6656656</v>
       </c>
       <c r="S242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32249,10 +32249,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236141</v>
+        <v>121236168</v>
       </c>
       <c r="B243" t="n">
-        <v>98071</v>
+        <v>79583</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32261,35 +32261,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -32298,13 +32298,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537629</v>
+        <v>537571</v>
       </c>
       <c r="R243" t="n">
-        <v>6656969</v>
+        <v>6656818</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32328,12 +32328,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32364,7 +32364,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236164</v>
+        <v>121236141</v>
       </c>
       <c r="B244" t="n">
         <v>98071</v>
@@ -32399,7 +32399,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -32413,13 +32413,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537484</v>
+        <v>537629</v>
       </c>
       <c r="R244" t="n">
-        <v>6656656</v>
+        <v>6656969</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32443,12 +32443,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD244" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90233</v>
+        <v>90243</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90233</v>
+        <v>90243</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236146</v>
+        <v>121236194</v>
       </c>
       <c r="B190" t="n">
-        <v>57501</v>
+        <v>90662</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,45 +26168,50 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537687</v>
+        <v>537520</v>
       </c>
       <c r="R190" t="n">
-        <v>6656879</v>
+        <v>6656530</v>
       </c>
       <c r="S190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -26230,12 +26235,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26266,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236180</v>
+        <v>121236176</v>
       </c>
       <c r="B191" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26301,7 +26306,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -26315,10 +26320,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537443</v>
+        <v>537462</v>
       </c>
       <c r="R191" t="n">
-        <v>6656691</v>
+        <v>6656736</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -26381,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236195</v>
+        <v>121236145</v>
       </c>
       <c r="B192" t="n">
-        <v>57348</v>
+        <v>94484</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26393,25 +26398,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -26419,24 +26424,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537508</v>
+        <v>537686</v>
       </c>
       <c r="R192" t="n">
-        <v>6656516</v>
+        <v>6656878</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26460,12 +26465,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -26496,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236163</v>
+        <v>121236160</v>
       </c>
       <c r="B193" t="n">
-        <v>90652</v>
+        <v>94604</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26512,43 +26517,43 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537447</v>
+        <v>537624</v>
       </c>
       <c r="R193" t="n">
-        <v>6656508</v>
+        <v>6656708</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -26611,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236145</v>
+        <v>121236153</v>
       </c>
       <c r="B194" t="n">
-        <v>94474</v>
+        <v>91453</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26623,25 +26628,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2809</v>
+        <v>366</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -26651,7 +26656,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26660,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537686</v>
+        <v>537763</v>
       </c>
       <c r="R194" t="n">
-        <v>6656878</v>
+        <v>6656846</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26726,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236136</v>
+        <v>121236182</v>
       </c>
       <c r="B195" t="n">
-        <v>90634</v>
+        <v>90697</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26742,21 +26747,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26766,7 +26771,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -26775,13 +26780,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537697</v>
+        <v>537413</v>
       </c>
       <c r="R195" t="n">
-        <v>6656821</v>
+        <v>6656645</v>
       </c>
       <c r="S195" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -26805,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26841,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236147</v>
+        <v>121236137</v>
       </c>
       <c r="B196" t="n">
-        <v>90687</v>
+        <v>91312</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26853,25 +26858,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -26890,13 +26895,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537705</v>
+        <v>537682</v>
       </c>
       <c r="R196" t="n">
-        <v>6656899</v>
+        <v>6656810</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26956,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236150</v>
+        <v>121236188</v>
       </c>
       <c r="B197" t="n">
-        <v>105176</v>
+        <v>57367</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26968,25 +26973,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -26994,24 +26999,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537738</v>
+        <v>537594</v>
       </c>
       <c r="R197" t="n">
-        <v>6657048</v>
+        <v>6656653</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27035,12 +27047,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27071,10 +27083,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236153</v>
+        <v>121236144</v>
       </c>
       <c r="B198" t="n">
-        <v>91443</v>
+        <v>57367</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27087,21 +27099,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -27109,9 +27121,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27120,10 +27132,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537763</v>
+        <v>537672</v>
       </c>
       <c r="R198" t="n">
-        <v>6656846</v>
+        <v>6656897</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -27186,10 +27198,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236137</v>
+        <v>121236165</v>
       </c>
       <c r="B199" t="n">
-        <v>91302</v>
+        <v>8421</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27202,46 +27214,46 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537682</v>
+        <v>537568</v>
       </c>
       <c r="R199" t="n">
-        <v>6656810</v>
+        <v>6657060</v>
       </c>
       <c r="S199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27265,12 +27277,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27279,6 +27291,7 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -27301,10 +27314,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236187</v>
+        <v>121236149</v>
       </c>
       <c r="B200" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27336,7 +27349,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -27346,17 +27359,17 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537559</v>
+        <v>537712</v>
       </c>
       <c r="R200" t="n">
-        <v>6656606</v>
+        <v>6657066</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27380,12 +27393,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27416,10 +27429,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236159</v>
+        <v>121236180</v>
       </c>
       <c r="B201" t="n">
-        <v>91443</v>
+        <v>98081</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27428,35 +27441,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -27465,13 +27478,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537686</v>
+        <v>537443</v>
       </c>
       <c r="R201" t="n">
-        <v>6656739</v>
+        <v>6656691</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27495,12 +27508,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27531,10 +27544,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236184</v>
+        <v>121236154</v>
       </c>
       <c r="B202" t="n">
-        <v>91955</v>
+        <v>94496</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27543,35 +27556,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4361</v>
+        <v>2813</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -27580,13 +27593,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537431</v>
+        <v>537724</v>
       </c>
       <c r="R202" t="n">
-        <v>6656597</v>
+        <v>6656830</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27610,12 +27623,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27646,10 +27659,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236193</v>
+        <v>121236140</v>
       </c>
       <c r="B203" t="n">
-        <v>91998</v>
+        <v>90662</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27658,30 +27671,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27691,14 +27704,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537518</v>
+        <v>537634</v>
       </c>
       <c r="R203" t="n">
-        <v>6656512</v>
+        <v>6657019</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27725,12 +27738,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27761,10 +27774,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236166</v>
+        <v>121236167</v>
       </c>
       <c r="B204" t="n">
-        <v>91996</v>
+        <v>98081</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27773,35 +27786,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27810,10 +27823,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537531</v>
+        <v>537517</v>
       </c>
       <c r="R204" t="n">
-        <v>6657006</v>
+        <v>6656819</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -27876,10 +27889,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236152</v>
+        <v>121236166</v>
       </c>
       <c r="B205" t="n">
-        <v>91302</v>
+        <v>92006</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27892,26 +27905,26 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1339</v>
+        <v>5964</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -27921,17 +27934,17 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537756</v>
+        <v>537531</v>
       </c>
       <c r="R205" t="n">
-        <v>6656968</v>
+        <v>6657006</v>
       </c>
       <c r="S205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27955,12 +27968,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27991,10 +28004,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236169</v>
+        <v>121236162</v>
       </c>
       <c r="B206" t="n">
-        <v>98071</v>
+        <v>91312</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28003,35 +28016,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -28040,10 +28053,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537474</v>
+        <v>537631</v>
       </c>
       <c r="R206" t="n">
-        <v>6656770</v>
+        <v>6656665</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -28070,12 +28083,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28106,10 +28119,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236154</v>
+        <v>121236190</v>
       </c>
       <c r="B207" t="n">
-        <v>94486</v>
+        <v>90697</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28118,25 +28131,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28146,22 +28159,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537724</v>
+        <v>537476</v>
       </c>
       <c r="R207" t="n">
-        <v>6656830</v>
+        <v>6656522</v>
       </c>
       <c r="S207" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -28185,12 +28198,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28221,10 +28234,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236173</v>
+        <v>121236195</v>
       </c>
       <c r="B208" t="n">
-        <v>98071</v>
+        <v>57351</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28233,47 +28246,47 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537505</v>
+        <v>537508</v>
       </c>
       <c r="R208" t="n">
-        <v>6656739</v>
+        <v>6656516</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -28336,10 +28349,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236143</v>
+        <v>121236198</v>
       </c>
       <c r="B209" t="n">
-        <v>91620</v>
+        <v>90697</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28348,25 +28361,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -28381,17 +28394,17 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537674</v>
+        <v>537497</v>
       </c>
       <c r="R209" t="n">
-        <v>6656893</v>
+        <v>6656496</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -28415,12 +28428,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -28451,10 +28464,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236198</v>
+        <v>121236189</v>
       </c>
       <c r="B210" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28463,50 +28476,50 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
         <v>537497</v>
       </c>
       <c r="R210" t="n">
-        <v>6656496</v>
+        <v>6656581</v>
       </c>
       <c r="S210" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28566,10 +28579,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236142</v>
+        <v>121236143</v>
       </c>
       <c r="B211" t="n">
-        <v>90652</v>
+        <v>91630</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28582,21 +28595,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28615,13 +28628,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537687</v>
+        <v>537674</v>
       </c>
       <c r="R211" t="n">
-        <v>6656911</v>
+        <v>6656893</v>
       </c>
       <c r="S211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28681,10 +28694,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236181</v>
+        <v>121236139</v>
       </c>
       <c r="B212" t="n">
-        <v>98071</v>
+        <v>57367</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28693,50 +28706,57 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537438</v>
+        <v>537547</v>
       </c>
       <c r="R212" t="n">
-        <v>6656699</v>
+        <v>6656935</v>
       </c>
       <c r="S212" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28760,12 +28780,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28796,10 +28816,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236192</v>
+        <v>121236170</v>
       </c>
       <c r="B213" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28808,47 +28828,47 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537475</v>
+        <v>537452</v>
       </c>
       <c r="R213" t="n">
-        <v>6656526</v>
+        <v>6656767</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28911,10 +28931,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236155</v>
+        <v>121236173</v>
       </c>
       <c r="B214" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28923,35 +28943,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -28960,13 +28980,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537736</v>
+        <v>537505</v>
       </c>
       <c r="R214" t="n">
-        <v>6656837</v>
+        <v>6656739</v>
       </c>
       <c r="S214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -28990,12 +29010,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -29026,10 +29046,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236194</v>
+        <v>121236186</v>
       </c>
       <c r="B215" t="n">
-        <v>90652</v>
+        <v>98081</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29038,47 +29058,47 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537520</v>
+        <v>537546</v>
       </c>
       <c r="R215" t="n">
-        <v>6656530</v>
+        <v>6656619</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -29141,10 +29161,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236149</v>
+        <v>121236151</v>
       </c>
       <c r="B216" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29153,35 +29173,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29190,10 +29210,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537712</v>
+        <v>537730</v>
       </c>
       <c r="R216" t="n">
-        <v>6657066</v>
+        <v>6656998</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29256,10 +29276,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236175</v>
+        <v>121236147</v>
       </c>
       <c r="B217" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29268,35 +29288,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29305,10 +29325,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537491</v>
+        <v>537705</v>
       </c>
       <c r="R217" t="n">
-        <v>6656738</v>
+        <v>6656899</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29335,12 +29355,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29371,10 +29391,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236160</v>
+        <v>121236193</v>
       </c>
       <c r="B218" t="n">
-        <v>94594</v>
+        <v>92008</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29383,25 +29403,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -29411,22 +29431,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537624</v>
+        <v>537518</v>
       </c>
       <c r="R218" t="n">
-        <v>6656708</v>
+        <v>6656512</v>
       </c>
       <c r="S218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29450,12 +29470,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29486,10 +29506,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236190</v>
+        <v>121236171</v>
       </c>
       <c r="B219" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,50 +29518,50 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537476</v>
+        <v>537516</v>
       </c>
       <c r="R219" t="n">
-        <v>6656522</v>
+        <v>6656778</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29601,10 +29621,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236170</v>
+        <v>121236138</v>
       </c>
       <c r="B220" t="n">
-        <v>98071</v>
+        <v>94583</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29613,35 +29633,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29650,13 +29670,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537452</v>
+        <v>537620</v>
       </c>
       <c r="R220" t="n">
-        <v>6656767</v>
+        <v>6656858</v>
       </c>
       <c r="S220" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29680,12 +29700,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29716,10 +29736,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236174</v>
+        <v>121236187</v>
       </c>
       <c r="B221" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29751,7 +29771,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -29765,10 +29785,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537502</v>
+        <v>537559</v>
       </c>
       <c r="R221" t="n">
-        <v>6656738</v>
+        <v>6656606</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29831,10 +29851,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236172</v>
+        <v>121236141</v>
       </c>
       <c r="B222" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29866,7 +29886,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29880,10 +29900,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537513</v>
+        <v>537629</v>
       </c>
       <c r="R222" t="n">
-        <v>6656728</v>
+        <v>6656969</v>
       </c>
       <c r="S222" t="n">
         <v>4</v>
@@ -29910,12 +29930,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29946,10 +29966,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236182</v>
+        <v>121236157</v>
       </c>
       <c r="B223" t="n">
-        <v>90687</v>
+        <v>90747</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29958,25 +29978,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1202</v>
+        <v>5321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -29995,13 +30015,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537413</v>
+        <v>537695</v>
       </c>
       <c r="R223" t="n">
-        <v>6656645</v>
+        <v>6656728</v>
       </c>
       <c r="S223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30025,12 +30045,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30061,10 +30081,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236151</v>
+        <v>121236178</v>
       </c>
       <c r="B224" t="n">
-        <v>90687</v>
+        <v>57504</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30077,43 +30097,38 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537730</v>
+        <v>537468</v>
       </c>
       <c r="R224" t="n">
-        <v>6656998</v>
+        <v>6656748</v>
       </c>
       <c r="S224" t="n">
         <v>4</v>
@@ -30140,12 +30155,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30176,10 +30191,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236185</v>
+        <v>121236196</v>
       </c>
       <c r="B225" t="n">
-        <v>98071</v>
+        <v>91041</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30192,46 +30207,46 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537472</v>
+        <v>537490</v>
       </c>
       <c r="R225" t="n">
-        <v>6656651</v>
+        <v>6656495</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30291,10 +30306,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236186</v>
+        <v>121236184</v>
       </c>
       <c r="B226" t="n">
-        <v>98071</v>
+        <v>91965</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30303,35 +30318,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30340,10 +30355,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537546</v>
+        <v>537431</v>
       </c>
       <c r="R226" t="n">
-        <v>6656619</v>
+        <v>6656597</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -30406,10 +30421,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236135</v>
+        <v>121236155</v>
       </c>
       <c r="B227" t="n">
-        <v>98071</v>
+        <v>90697</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30418,35 +30433,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30455,10 +30470,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537439</v>
+        <v>537736</v>
       </c>
       <c r="R227" t="n">
-        <v>6656570</v>
+        <v>6656837</v>
       </c>
       <c r="S227" t="n">
         <v>4</v>
@@ -30521,10 +30536,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236157</v>
+        <v>121236169</v>
       </c>
       <c r="B228" t="n">
-        <v>90737</v>
+        <v>98081</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30533,35 +30548,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30570,13 +30585,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537695</v>
+        <v>537474</v>
       </c>
       <c r="R228" t="n">
-        <v>6656728</v>
+        <v>6656770</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30600,12 +30615,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30636,10 +30651,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236144</v>
+        <v>121236181</v>
       </c>
       <c r="B229" t="n">
-        <v>57364</v>
+        <v>98081</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30648,35 +30663,35 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -30685,13 +30700,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537672</v>
+        <v>537438</v>
       </c>
       <c r="R229" t="n">
-        <v>6656897</v>
+        <v>6656699</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30715,12 +30730,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30751,10 +30766,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236196</v>
+        <v>121236185</v>
       </c>
       <c r="B230" t="n">
-        <v>91031</v>
+        <v>98081</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30767,46 +30782,46 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537490</v>
+        <v>537472</v>
       </c>
       <c r="R230" t="n">
-        <v>6656495</v>
+        <v>6656651</v>
       </c>
       <c r="S230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30866,10 +30881,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236171</v>
+        <v>121236135</v>
       </c>
       <c r="B231" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30901,7 +30916,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -30915,10 +30930,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537516</v>
+        <v>537439</v>
       </c>
       <c r="R231" t="n">
-        <v>6656778</v>
+        <v>6656570</v>
       </c>
       <c r="S231" t="n">
         <v>4</v>
@@ -30945,12 +30960,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30981,10 +30996,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236188</v>
+        <v>121236192</v>
       </c>
       <c r="B232" t="n">
-        <v>57364</v>
+        <v>57351</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30997,16 +31012,16 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -31019,31 +31034,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537594</v>
+        <v>537475</v>
       </c>
       <c r="R232" t="n">
-        <v>6656653</v>
+        <v>6656526</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31103,10 +31111,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236165</v>
+        <v>121236177</v>
       </c>
       <c r="B233" t="n">
-        <v>8421</v>
+        <v>98081</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31115,50 +31123,50 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N233" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537568</v>
+        <v>537470</v>
       </c>
       <c r="R233" t="n">
-        <v>6657060</v>
+        <v>6656705</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -31196,7 +31204,6 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
-      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -31219,10 +31226,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236197</v>
+        <v>121236172</v>
       </c>
       <c r="B234" t="n">
-        <v>90973</v>
+        <v>98081</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31231,50 +31238,50 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537490</v>
+        <v>537513</v>
       </c>
       <c r="R234" t="n">
-        <v>6656487</v>
+        <v>6656728</v>
       </c>
       <c r="S234" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31334,10 +31341,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236140</v>
+        <v>121236150</v>
       </c>
       <c r="B235" t="n">
-        <v>90652</v>
+        <v>105186</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31350,21 +31357,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5447</v>
+        <v>221144</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -31374,22 +31381,22 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537634</v>
+        <v>537738</v>
       </c>
       <c r="R235" t="n">
-        <v>6657019</v>
+        <v>6657048</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31449,10 +31456,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236162</v>
+        <v>121236197</v>
       </c>
       <c r="B236" t="n">
-        <v>91302</v>
+        <v>90983</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31461,25 +31468,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -31494,17 +31501,17 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537631</v>
+        <v>537490</v>
       </c>
       <c r="R236" t="n">
-        <v>6656665</v>
+        <v>6656487</v>
       </c>
       <c r="S236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31528,12 +31535,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31564,10 +31571,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236189</v>
+        <v>121236142</v>
       </c>
       <c r="B237" t="n">
-        <v>98071</v>
+        <v>90662</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31576,35 +31583,35 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31613,13 +31620,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537497</v>
+        <v>537687</v>
       </c>
       <c r="R237" t="n">
-        <v>6656581</v>
+        <v>6656911</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31643,12 +31650,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31679,10 +31686,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236177</v>
+        <v>121236168</v>
       </c>
       <c r="B238" t="n">
-        <v>98071</v>
+        <v>79586</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31691,35 +31698,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31728,13 +31735,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537470</v>
+        <v>537571</v>
       </c>
       <c r="R238" t="n">
-        <v>6656705</v>
+        <v>6656818</v>
       </c>
       <c r="S238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -31794,10 +31801,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236167</v>
+        <v>121236164</v>
       </c>
       <c r="B239" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31829,7 +31836,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -31843,10 +31850,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537517</v>
+        <v>537484</v>
       </c>
       <c r="R239" t="n">
-        <v>6656819</v>
+        <v>6656656</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -31909,10 +31916,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236176</v>
+        <v>121236175</v>
       </c>
       <c r="B240" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31944,7 +31951,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -31958,10 +31965,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537462</v>
+        <v>537491</v>
       </c>
       <c r="R240" t="n">
-        <v>6656736</v>
+        <v>6656738</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -32024,10 +32031,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236178</v>
+        <v>121236159</v>
       </c>
       <c r="B241" t="n">
-        <v>57501</v>
+        <v>91453</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32040,26 +32047,31 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>103021</v>
+        <v>366</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32068,10 +32080,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537468</v>
+        <v>537686</v>
       </c>
       <c r="R241" t="n">
-        <v>6656748</v>
+        <v>6656739</v>
       </c>
       <c r="S241" t="n">
         <v>4</v>
@@ -32098,12 +32110,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32134,10 +32146,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236164</v>
+        <v>121236136</v>
       </c>
       <c r="B242" t="n">
-        <v>98071</v>
+        <v>90644</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32146,35 +32158,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32183,13 +32195,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537484</v>
+        <v>537697</v>
       </c>
       <c r="R242" t="n">
-        <v>6656656</v>
+        <v>6656821</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32213,12 +32225,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32249,10 +32261,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236168</v>
+        <v>121236163</v>
       </c>
       <c r="B243" t="n">
-        <v>79583</v>
+        <v>90662</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32265,21 +32277,21 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -32289,22 +32301,22 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537571</v>
+        <v>537447</v>
       </c>
       <c r="R243" t="n">
-        <v>6656818</v>
+        <v>6656508</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32328,12 +32340,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32364,10 +32376,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236141</v>
+        <v>121236146</v>
       </c>
       <c r="B244" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32376,35 +32388,30 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -32413,10 +32420,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537629</v>
+        <v>537687</v>
       </c>
       <c r="R244" t="n">
-        <v>6656969</v>
+        <v>6656879</v>
       </c>
       <c r="S244" t="n">
         <v>4</v>
@@ -32479,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236138</v>
+        <v>121236152</v>
       </c>
       <c r="B245" t="n">
-        <v>94573</v>
+        <v>91312</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32495,46 +32502,46 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>2667</v>
+        <v>1339</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537620</v>
+        <v>537756</v>
       </c>
       <c r="R245" t="n">
-        <v>6656858</v>
+        <v>6656968</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32594,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236139</v>
+        <v>121236174</v>
       </c>
       <c r="B246" t="n">
-        <v>57364</v>
+        <v>98081</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32606,57 +32613,50 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P246" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537547</v>
+        <v>537502</v>
       </c>
       <c r="R246" t="n">
-        <v>6656935</v>
+        <v>6656738</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -32716,10 +32716,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B247" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R247" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,10 +32831,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B248" t="n">
-        <v>94690</v>
+        <v>94700</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R248" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -27659,10 +27659,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236140</v>
+        <v>121236166</v>
       </c>
       <c r="B203" t="n">
-        <v>90662</v>
+        <v>92006</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27675,26 +27675,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27708,10 +27708,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537634</v>
+        <v>537531</v>
       </c>
       <c r="R203" t="n">
-        <v>6657019</v>
+        <v>6657006</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27738,12 +27738,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27774,10 +27774,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236167</v>
+        <v>121236140</v>
       </c>
       <c r="B204" t="n">
-        <v>98081</v>
+        <v>90662</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27786,35 +27786,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27823,10 +27823,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537517</v>
+        <v>537634</v>
       </c>
       <c r="R204" t="n">
-        <v>6656819</v>
+        <v>6657019</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -27853,12 +27853,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27889,10 +27889,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236166</v>
+        <v>121236167</v>
       </c>
       <c r="B205" t="n">
-        <v>92006</v>
+        <v>98081</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27901,35 +27901,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27938,10 +27938,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537531</v>
+        <v>537517</v>
       </c>
       <c r="R205" t="n">
-        <v>6657006</v>
+        <v>6656819</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -28579,10 +28579,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236143</v>
+        <v>121236151</v>
       </c>
       <c r="B211" t="n">
-        <v>91630</v>
+        <v>90697</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28591,25 +28591,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28624,17 +28624,17 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537674</v>
+        <v>537730</v>
       </c>
       <c r="R211" t="n">
-        <v>6656893</v>
+        <v>6656998</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28694,10 +28694,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236139</v>
+        <v>121236147</v>
       </c>
       <c r="B212" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28710,21 +28710,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -28732,31 +28732,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537547</v>
+        <v>537705</v>
       </c>
       <c r="R212" t="n">
-        <v>6656935</v>
+        <v>6656899</v>
       </c>
       <c r="S212" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28816,10 +28809,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236170</v>
+        <v>121236143</v>
       </c>
       <c r="B213" t="n">
-        <v>98081</v>
+        <v>91630</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28828,35 +28821,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28865,13 +28858,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537452</v>
+        <v>537674</v>
       </c>
       <c r="R213" t="n">
-        <v>6656767</v>
+        <v>6656893</v>
       </c>
       <c r="S213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28895,12 +28888,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28931,10 +28924,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236173</v>
+        <v>121236193</v>
       </c>
       <c r="B214" t="n">
-        <v>98081</v>
+        <v>92008</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28943,47 +28936,47 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537505</v>
+        <v>537518</v>
       </c>
       <c r="R214" t="n">
-        <v>6656739</v>
+        <v>6656512</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -29046,10 +29039,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236186</v>
+        <v>121236139</v>
       </c>
       <c r="B215" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29058,50 +29051,57 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537546</v>
+        <v>537547</v>
       </c>
       <c r="R215" t="n">
-        <v>6656619</v>
+        <v>6656935</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29125,12 +29125,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29161,10 +29161,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236151</v>
+        <v>121236170</v>
       </c>
       <c r="B216" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29173,47 +29173,47 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537730</v>
+        <v>537452</v>
       </c>
       <c r="R216" t="n">
-        <v>6656998</v>
+        <v>6656767</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29240,12 +29240,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29276,10 +29276,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236147</v>
+        <v>121236173</v>
       </c>
       <c r="B217" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29288,35 +29288,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29325,10 +29325,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537705</v>
+        <v>537505</v>
       </c>
       <c r="R217" t="n">
-        <v>6656899</v>
+        <v>6656739</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29355,12 +29355,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29391,10 +29391,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236193</v>
+        <v>121236186</v>
       </c>
       <c r="B218" t="n">
-        <v>92008</v>
+        <v>98081</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29403,47 +29403,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537518</v>
+        <v>537546</v>
       </c>
       <c r="R218" t="n">
-        <v>6656512</v>
+        <v>6656619</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -29506,10 +29506,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236171</v>
+        <v>121236138</v>
       </c>
       <c r="B219" t="n">
-        <v>98081</v>
+        <v>94583</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29518,35 +29518,35 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -29555,13 +29555,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537516</v>
+        <v>537620</v>
       </c>
       <c r="R219" t="n">
-        <v>6656778</v>
+        <v>6656858</v>
       </c>
       <c r="S219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29585,12 +29585,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29621,10 +29621,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236138</v>
+        <v>121236171</v>
       </c>
       <c r="B220" t="n">
-        <v>94583</v>
+        <v>98081</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29633,35 +29633,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29670,13 +29670,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537620</v>
+        <v>537516</v>
       </c>
       <c r="R220" t="n">
-        <v>6656858</v>
+        <v>6656778</v>
       </c>
       <c r="S220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29700,12 +29700,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -30081,10 +30081,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236178</v>
+        <v>121236196</v>
       </c>
       <c r="B224" t="n">
-        <v>57504</v>
+        <v>91041</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30093,42 +30093,47 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537468</v>
+        <v>537490</v>
       </c>
       <c r="R224" t="n">
-        <v>6656748</v>
+        <v>6656495</v>
       </c>
       <c r="S224" t="n">
         <v>4</v>
@@ -30191,10 +30196,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236196</v>
+        <v>121236178</v>
       </c>
       <c r="B225" t="n">
-        <v>91041</v>
+        <v>57504</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30203,47 +30208,42 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2062</v>
+        <v>103021</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J225" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537490</v>
+        <v>537468</v>
       </c>
       <c r="R225" t="n">
-        <v>6656495</v>
+        <v>6656748</v>
       </c>
       <c r="S225" t="n">
         <v>4</v>
@@ -32261,10 +32261,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236163</v>
+        <v>121236146</v>
       </c>
       <c r="B243" t="n">
-        <v>90662</v>
+        <v>57504</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32273,47 +32273,42 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537447</v>
+        <v>537687</v>
       </c>
       <c r="R243" t="n">
-        <v>6656508</v>
+        <v>6656879</v>
       </c>
       <c r="S243" t="n">
         <v>4</v>
@@ -32376,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236146</v>
+        <v>121236163</v>
       </c>
       <c r="B244" t="n">
-        <v>57504</v>
+        <v>90662</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32388,42 +32383,47 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537687</v>
+        <v>537447</v>
       </c>
       <c r="R244" t="n">
-        <v>6656879</v>
+        <v>6656508</v>
       </c>
       <c r="S244" t="n">
         <v>4</v>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236152</v>
+        <v>121236174</v>
       </c>
       <c r="B245" t="n">
-        <v>91312</v>
+        <v>98081</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537756</v>
+        <v>537502</v>
       </c>
       <c r="R245" t="n">
-        <v>6656968</v>
+        <v>6656738</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236174</v>
+        <v>121236152</v>
       </c>
       <c r="B246" t="n">
-        <v>98081</v>
+        <v>91312</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,50 +32613,50 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537502</v>
+        <v>537756</v>
       </c>
       <c r="R246" t="n">
-        <v>6656738</v>
+        <v>6656968</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD246" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236188</v>
+        <v>121236165</v>
       </c>
       <c r="B197" t="n">
-        <v>57367</v>
+        <v>8421</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,41 +26973,34 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -27017,10 +27010,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537594</v>
+        <v>537568</v>
       </c>
       <c r="R197" t="n">
-        <v>6656653</v>
+        <v>6657060</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -27061,6 +27054,7 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -27083,7 +27077,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236144</v>
+        <v>121236188</v>
       </c>
       <c r="B198" t="n">
         <v>57367</v>
@@ -27121,21 +27115,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537672</v>
+        <v>537594</v>
       </c>
       <c r="R198" t="n">
-        <v>6656897</v>
+        <v>6656653</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -27162,12 +27163,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27198,10 +27199,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236165</v>
+        <v>121236144</v>
       </c>
       <c r="B199" t="n">
-        <v>8421</v>
+        <v>57367</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27210,47 +27211,47 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537568</v>
+        <v>537672</v>
       </c>
       <c r="R199" t="n">
-        <v>6657060</v>
+        <v>6656897</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -27277,12 +27278,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27291,7 +27292,6 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -27659,10 +27659,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236166</v>
+        <v>121236140</v>
       </c>
       <c r="B203" t="n">
-        <v>92006</v>
+        <v>90662</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27675,26 +27675,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27708,10 +27708,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537531</v>
+        <v>537634</v>
       </c>
       <c r="R203" t="n">
-        <v>6657006</v>
+        <v>6657019</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27738,12 +27738,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27774,10 +27774,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236140</v>
+        <v>121236167</v>
       </c>
       <c r="B204" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27786,35 +27786,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27823,10 +27823,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537634</v>
+        <v>537517</v>
       </c>
       <c r="R204" t="n">
-        <v>6657019</v>
+        <v>6656819</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -27853,12 +27853,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27889,10 +27889,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236167</v>
+        <v>121236166</v>
       </c>
       <c r="B205" t="n">
-        <v>98081</v>
+        <v>92006</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27901,35 +27901,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27938,10 +27938,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537517</v>
+        <v>537531</v>
       </c>
       <c r="R205" t="n">
-        <v>6656819</v>
+        <v>6657006</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -28579,10 +28579,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236151</v>
+        <v>121236143</v>
       </c>
       <c r="B211" t="n">
-        <v>90697</v>
+        <v>91630</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28591,25 +28591,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28624,17 +28624,17 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537730</v>
+        <v>537674</v>
       </c>
       <c r="R211" t="n">
-        <v>6656998</v>
+        <v>6656893</v>
       </c>
       <c r="S211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28694,10 +28694,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236147</v>
+        <v>121236139</v>
       </c>
       <c r="B212" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28710,21 +28710,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -28732,24 +28732,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537705</v>
+        <v>537547</v>
       </c>
       <c r="R212" t="n">
-        <v>6656899</v>
+        <v>6656935</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28809,10 +28816,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236143</v>
+        <v>121236170</v>
       </c>
       <c r="B213" t="n">
-        <v>91630</v>
+        <v>98081</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28821,35 +28828,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28858,13 +28865,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537674</v>
+        <v>537452</v>
       </c>
       <c r="R213" t="n">
-        <v>6656893</v>
+        <v>6656767</v>
       </c>
       <c r="S213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28888,12 +28895,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28924,10 +28931,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236193</v>
+        <v>121236173</v>
       </c>
       <c r="B214" t="n">
-        <v>92008</v>
+        <v>98081</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28936,47 +28943,47 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537518</v>
+        <v>537505</v>
       </c>
       <c r="R214" t="n">
-        <v>6656512</v>
+        <v>6656739</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -29039,10 +29046,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236139</v>
+        <v>121236186</v>
       </c>
       <c r="B215" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29051,57 +29058,50 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537547</v>
+        <v>537546</v>
       </c>
       <c r="R215" t="n">
-        <v>6656935</v>
+        <v>6656619</v>
       </c>
       <c r="S215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29125,12 +29125,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29161,10 +29161,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236170</v>
+        <v>121236151</v>
       </c>
       <c r="B216" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29173,47 +29173,47 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537452</v>
+        <v>537730</v>
       </c>
       <c r="R216" t="n">
-        <v>6656767</v>
+        <v>6656998</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29240,12 +29240,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29276,10 +29276,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236173</v>
+        <v>121236147</v>
       </c>
       <c r="B217" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29288,35 +29288,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29325,10 +29325,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537505</v>
+        <v>537705</v>
       </c>
       <c r="R217" t="n">
-        <v>6656739</v>
+        <v>6656899</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29355,12 +29355,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29391,10 +29391,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236186</v>
+        <v>121236193</v>
       </c>
       <c r="B218" t="n">
-        <v>98081</v>
+        <v>92008</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29403,47 +29403,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537546</v>
+        <v>537518</v>
       </c>
       <c r="R218" t="n">
-        <v>6656619</v>
+        <v>6656512</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -30081,10 +30081,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236196</v>
+        <v>121236178</v>
       </c>
       <c r="B224" t="n">
-        <v>91041</v>
+        <v>57504</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30093,47 +30093,42 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2062</v>
+        <v>103021</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537490</v>
+        <v>537468</v>
       </c>
       <c r="R224" t="n">
-        <v>6656495</v>
+        <v>6656748</v>
       </c>
       <c r="S224" t="n">
         <v>4</v>
@@ -30196,10 +30191,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236178</v>
+        <v>121236196</v>
       </c>
       <c r="B225" t="n">
-        <v>57504</v>
+        <v>91041</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30208,42 +30203,47 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537468</v>
+        <v>537490</v>
       </c>
       <c r="R225" t="n">
-        <v>6656748</v>
+        <v>6656495</v>
       </c>
       <c r="S225" t="n">
         <v>4</v>
@@ -31801,10 +31801,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236164</v>
+        <v>121236159</v>
       </c>
       <c r="B239" t="n">
-        <v>98081</v>
+        <v>91453</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31813,35 +31813,35 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -31850,13 +31850,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537484</v>
+        <v>537686</v>
       </c>
       <c r="R239" t="n">
-        <v>6656656</v>
+        <v>6656739</v>
       </c>
       <c r="S239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31880,12 +31880,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31916,10 +31916,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236175</v>
+        <v>121236136</v>
       </c>
       <c r="B240" t="n">
-        <v>98081</v>
+        <v>90644</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31928,35 +31928,35 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -31965,13 +31965,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537491</v>
+        <v>537697</v>
       </c>
       <c r="R240" t="n">
-        <v>6656738</v>
+        <v>6656821</v>
       </c>
       <c r="S240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31995,12 +31995,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32031,10 +32031,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236159</v>
+        <v>121236164</v>
       </c>
       <c r="B241" t="n">
-        <v>91453</v>
+        <v>98081</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32043,35 +32043,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32080,13 +32080,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537686</v>
+        <v>537484</v>
       </c>
       <c r="R241" t="n">
-        <v>6656739</v>
+        <v>6656656</v>
       </c>
       <c r="S241" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -32110,12 +32110,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32146,10 +32146,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236136</v>
+        <v>121236175</v>
       </c>
       <c r="B242" t="n">
-        <v>90644</v>
+        <v>98081</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32158,35 +32158,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32195,13 +32195,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537697</v>
+        <v>537491</v>
       </c>
       <c r="R242" t="n">
-        <v>6656821</v>
+        <v>6656738</v>
       </c>
       <c r="S242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236174</v>
+        <v>121236152</v>
       </c>
       <c r="B245" t="n">
-        <v>98081</v>
+        <v>91312</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537502</v>
+        <v>537756</v>
       </c>
       <c r="R245" t="n">
-        <v>6656738</v>
+        <v>6656968</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236152</v>
+        <v>121236174</v>
       </c>
       <c r="B246" t="n">
-        <v>91312</v>
+        <v>98081</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,50 +32613,50 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537756</v>
+        <v>537502</v>
       </c>
       <c r="R246" t="n">
-        <v>6656968</v>
+        <v>6656738</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD246" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236194</v>
+        <v>121236144</v>
       </c>
       <c r="B190" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,25 +26168,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -26194,21 +26194,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537520</v>
+        <v>537672</v>
       </c>
       <c r="R190" t="n">
-        <v>6656530</v>
+        <v>6656897</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26235,12 +26235,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,7 +26271,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236176</v>
+        <v>121236149</v>
       </c>
       <c r="B191" t="n">
         <v>98081</v>
@@ -26316,17 +26316,17 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537462</v>
+        <v>537712</v>
       </c>
       <c r="R191" t="n">
-        <v>6656736</v>
+        <v>6657066</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236145</v>
+        <v>121236186</v>
       </c>
       <c r="B192" t="n">
-        <v>94484</v>
+        <v>98081</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,35 +26398,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -26435,13 +26435,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537686</v>
+        <v>537546</v>
       </c>
       <c r="R192" t="n">
-        <v>6656878</v>
+        <v>6656619</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26465,12 +26465,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -26501,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236160</v>
+        <v>121236193</v>
       </c>
       <c r="B193" t="n">
-        <v>94604</v>
+        <v>92008</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,25 +26513,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2818</v>
+        <v>5966</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -26541,22 +26541,22 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537624</v>
+        <v>537518</v>
       </c>
       <c r="R193" t="n">
-        <v>6656708</v>
+        <v>6656512</v>
       </c>
       <c r="S193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26580,12 +26580,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -26616,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236153</v>
+        <v>121236190</v>
       </c>
       <c r="B194" t="n">
-        <v>91453</v>
+        <v>90697</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26632,21 +26632,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -26661,17 +26661,17 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537763</v>
+        <v>537476</v>
       </c>
       <c r="R194" t="n">
-        <v>6656846</v>
+        <v>6656522</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26731,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236182</v>
+        <v>121236163</v>
       </c>
       <c r="B195" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,25 +26743,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26776,17 +26776,17 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537413</v>
+        <v>537447</v>
       </c>
       <c r="R195" t="n">
-        <v>6656645</v>
+        <v>6656508</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -26810,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236137</v>
+        <v>121236160</v>
       </c>
       <c r="B196" t="n">
-        <v>91312</v>
+        <v>94604</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26862,31 +26862,31 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537682</v>
+        <v>537624</v>
       </c>
       <c r="R196" t="n">
-        <v>6656810</v>
+        <v>6656708</v>
       </c>
       <c r="S196" t="n">
         <v>4</v>
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236165</v>
+        <v>121236174</v>
       </c>
       <c r="B197" t="n">
-        <v>8421</v>
+        <v>98081</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,47 +26973,47 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N197" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537568</v>
+        <v>537502</v>
       </c>
       <c r="R197" t="n">
-        <v>6657060</v>
+        <v>6656738</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -27054,7 +27054,6 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -27077,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236188</v>
+        <v>121236176</v>
       </c>
       <c r="B198" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27089,54 +27088,47 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537594</v>
+        <v>537462</v>
       </c>
       <c r="R198" t="n">
-        <v>6656653</v>
+        <v>6656736</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -27199,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236144</v>
+        <v>121236189</v>
       </c>
       <c r="B199" t="n">
-        <v>57367</v>
+        <v>98081</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27211,35 +27203,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -27248,10 +27240,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537672</v>
+        <v>537497</v>
       </c>
       <c r="R199" t="n">
-        <v>6656897</v>
+        <v>6656581</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -27278,12 +27270,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27314,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236149</v>
+        <v>121236155</v>
       </c>
       <c r="B200" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27326,47 +27318,47 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537712</v>
+        <v>537736</v>
       </c>
       <c r="R200" t="n">
-        <v>6657066</v>
+        <v>6656837</v>
       </c>
       <c r="S200" t="n">
         <v>4</v>
@@ -27429,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236180</v>
+        <v>121236150</v>
       </c>
       <c r="B201" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27441,30 +27433,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -27474,17 +27466,17 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537443</v>
+        <v>537738</v>
       </c>
       <c r="R201" t="n">
-        <v>6656691</v>
+        <v>6657048</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27508,12 +27500,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27659,7 +27651,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236140</v>
+        <v>121236142</v>
       </c>
       <c r="B203" t="n">
         <v>90662</v>
@@ -27708,13 +27700,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537634</v>
+        <v>537687</v>
       </c>
       <c r="R203" t="n">
-        <v>6657019</v>
+        <v>6656911</v>
       </c>
       <c r="S203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27774,7 +27766,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236167</v>
+        <v>121236169</v>
       </c>
       <c r="B204" t="n">
         <v>98081</v>
@@ -27809,7 +27801,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -27823,13 +27815,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537517</v>
+        <v>537474</v>
       </c>
       <c r="R204" t="n">
-        <v>6656819</v>
+        <v>6656770</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27889,10 +27881,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236166</v>
+        <v>121236170</v>
       </c>
       <c r="B205" t="n">
-        <v>92006</v>
+        <v>98081</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27901,35 +27893,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27938,13 +27930,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537531</v>
+        <v>537452</v>
       </c>
       <c r="R205" t="n">
-        <v>6657006</v>
+        <v>6656767</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -28004,10 +27996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236162</v>
+        <v>121236171</v>
       </c>
       <c r="B206" t="n">
-        <v>91312</v>
+        <v>98081</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28016,35 +28008,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -28053,10 +28045,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537631</v>
+        <v>537516</v>
       </c>
       <c r="R206" t="n">
-        <v>6656665</v>
+        <v>6656778</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -28083,12 +28075,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28119,10 +28111,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236190</v>
+        <v>121236157</v>
       </c>
       <c r="B207" t="n">
-        <v>90697</v>
+        <v>90747</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28131,25 +28123,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>5321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28164,17 +28156,17 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537476</v>
+        <v>537695</v>
       </c>
       <c r="R207" t="n">
-        <v>6656522</v>
+        <v>6656728</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -28198,12 +28190,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28234,10 +28226,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236195</v>
+        <v>121236185</v>
       </c>
       <c r="B208" t="n">
-        <v>57351</v>
+        <v>98081</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28246,47 +28238,47 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537508</v>
+        <v>537472</v>
       </c>
       <c r="R208" t="n">
-        <v>6656516</v>
+        <v>6656651</v>
       </c>
       <c r="S208" t="n">
         <v>5</v>
@@ -28349,10 +28341,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236198</v>
+        <v>121236177</v>
       </c>
       <c r="B209" t="n">
-        <v>90697</v>
+        <v>98081</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28361,50 +28353,50 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537497</v>
+        <v>537470</v>
       </c>
       <c r="R209" t="n">
-        <v>6656496</v>
+        <v>6656705</v>
       </c>
       <c r="S209" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -28464,7 +28456,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236189</v>
+        <v>121236180</v>
       </c>
       <c r="B210" t="n">
         <v>98081</v>
@@ -28499,7 +28491,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -28513,10 +28505,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537497</v>
+        <v>537443</v>
       </c>
       <c r="R210" t="n">
-        <v>6656581</v>
+        <v>6656691</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -28579,10 +28571,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236143</v>
+        <v>121236147</v>
       </c>
       <c r="B211" t="n">
-        <v>91630</v>
+        <v>90697</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28591,25 +28583,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28628,10 +28620,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537674</v>
+        <v>537705</v>
       </c>
       <c r="R211" t="n">
-        <v>6656893</v>
+        <v>6656899</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -28694,10 +28686,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236139</v>
+        <v>121236196</v>
       </c>
       <c r="B212" t="n">
-        <v>57367</v>
+        <v>91041</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28706,25 +28698,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -28732,28 +28724,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537547</v>
+        <v>537490</v>
       </c>
       <c r="R212" t="n">
-        <v>6656935</v>
+        <v>6656495</v>
       </c>
       <c r="S212" t="n">
         <v>4</v>
@@ -28780,12 +28765,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28816,10 +28801,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236170</v>
+        <v>121236162</v>
       </c>
       <c r="B213" t="n">
-        <v>98081</v>
+        <v>91312</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28828,35 +28813,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28865,10 +28850,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537452</v>
+        <v>537631</v>
       </c>
       <c r="R213" t="n">
-        <v>6656767</v>
+        <v>6656665</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28895,12 +28880,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28931,10 +28916,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236173</v>
+        <v>121236143</v>
       </c>
       <c r="B214" t="n">
-        <v>98081</v>
+        <v>91630</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28943,35 +28928,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -28980,10 +28965,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537505</v>
+        <v>537674</v>
       </c>
       <c r="R214" t="n">
-        <v>6656739</v>
+        <v>6656893</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -29010,12 +28995,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -29046,7 +29031,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236186</v>
+        <v>121236141</v>
       </c>
       <c r="B215" t="n">
         <v>98081</v>
@@ -29081,7 +29066,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -29095,13 +29080,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537546</v>
+        <v>537629</v>
       </c>
       <c r="R215" t="n">
-        <v>6656619</v>
+        <v>6656969</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29125,12 +29110,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29161,10 +29146,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236151</v>
+        <v>121236152</v>
       </c>
       <c r="B216" t="n">
-        <v>90697</v>
+        <v>91312</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29173,25 +29158,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -29210,10 +29195,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537730</v>
+        <v>537756</v>
       </c>
       <c r="R216" t="n">
-        <v>6656998</v>
+        <v>6656968</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29276,10 +29261,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236147</v>
+        <v>121236140</v>
       </c>
       <c r="B217" t="n">
-        <v>90697</v>
+        <v>90662</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29288,25 +29273,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -29325,10 +29310,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537705</v>
+        <v>537634</v>
       </c>
       <c r="R217" t="n">
-        <v>6656899</v>
+        <v>6657019</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29391,10 +29376,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236193</v>
+        <v>121236135</v>
       </c>
       <c r="B218" t="n">
-        <v>92008</v>
+        <v>98081</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29403,50 +29388,50 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537518</v>
+        <v>537439</v>
       </c>
       <c r="R218" t="n">
-        <v>6656512</v>
+        <v>6656570</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29470,12 +29455,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29506,10 +29491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236138</v>
+        <v>121236165</v>
       </c>
       <c r="B219" t="n">
-        <v>94583</v>
+        <v>8421</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29522,43 +29507,43 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2667</v>
+        <v>106554</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537620</v>
+        <v>537568</v>
       </c>
       <c r="R219" t="n">
-        <v>6656858</v>
+        <v>6657060</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -29585,12 +29570,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29599,6 +29584,7 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
+      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -29621,10 +29607,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236171</v>
+        <v>121236198</v>
       </c>
       <c r="B220" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29633,50 +29619,50 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537516</v>
+        <v>537497</v>
       </c>
       <c r="R220" t="n">
-        <v>6656778</v>
+        <v>6656496</v>
       </c>
       <c r="S220" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29736,10 +29722,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236187</v>
+        <v>121236182</v>
       </c>
       <c r="B221" t="n">
-        <v>98081</v>
+        <v>90697</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29748,35 +29734,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -29785,13 +29771,13 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537559</v>
+        <v>537413</v>
       </c>
       <c r="R221" t="n">
-        <v>6656606</v>
+        <v>6656645</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29851,7 +29837,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236141</v>
+        <v>121236175</v>
       </c>
       <c r="B222" t="n">
         <v>98081</v>
@@ -29886,7 +29872,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29900,13 +29886,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537629</v>
+        <v>537491</v>
       </c>
       <c r="R222" t="n">
-        <v>6656969</v>
+        <v>6656738</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29930,12 +29916,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29966,10 +29952,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236157</v>
+        <v>121236168</v>
       </c>
       <c r="B223" t="n">
-        <v>90747</v>
+        <v>79586</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29982,21 +29968,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5321</v>
+        <v>6456</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -30006,7 +29992,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -30015,10 +30001,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537695</v>
+        <v>537571</v>
       </c>
       <c r="R223" t="n">
-        <v>6656728</v>
+        <v>6656818</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -30045,12 +30031,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30081,10 +30067,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236178</v>
+        <v>121236187</v>
       </c>
       <c r="B224" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30093,30 +30079,35 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -30125,13 +30116,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537468</v>
+        <v>537559</v>
       </c>
       <c r="R224" t="n">
-        <v>6656748</v>
+        <v>6656606</v>
       </c>
       <c r="S224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30191,10 +30182,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236196</v>
+        <v>121236167</v>
       </c>
       <c r="B225" t="n">
-        <v>91041</v>
+        <v>98081</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30207,46 +30198,46 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537490</v>
+        <v>537517</v>
       </c>
       <c r="R225" t="n">
-        <v>6656495</v>
+        <v>6656819</v>
       </c>
       <c r="S225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30306,10 +30297,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236184</v>
+        <v>121236145</v>
       </c>
       <c r="B226" t="n">
-        <v>91965</v>
+        <v>94484</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30318,35 +30309,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>2809</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30355,13 +30346,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537431</v>
+        <v>537686</v>
       </c>
       <c r="R226" t="n">
-        <v>6656597</v>
+        <v>6656878</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30385,12 +30376,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30421,10 +30412,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236155</v>
+        <v>121236195</v>
       </c>
       <c r="B227" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30437,21 +30428,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -30459,24 +30450,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537736</v>
+        <v>537508</v>
       </c>
       <c r="R227" t="n">
-        <v>6656837</v>
+        <v>6656516</v>
       </c>
       <c r="S227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30500,12 +30491,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30536,10 +30527,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236169</v>
+        <v>121236178</v>
       </c>
       <c r="B228" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30548,35 +30539,30 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30585,10 +30571,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537474</v>
+        <v>537468</v>
       </c>
       <c r="R228" t="n">
-        <v>6656770</v>
+        <v>6656748</v>
       </c>
       <c r="S228" t="n">
         <v>4</v>
@@ -30651,10 +30637,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236181</v>
+        <v>121236197</v>
       </c>
       <c r="B229" t="n">
-        <v>98081</v>
+        <v>90983</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30663,50 +30649,50 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537438</v>
+        <v>537490</v>
       </c>
       <c r="R229" t="n">
-        <v>6656699</v>
+        <v>6656487</v>
       </c>
       <c r="S229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30766,10 +30752,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236185</v>
+        <v>121236138</v>
       </c>
       <c r="B230" t="n">
-        <v>98081</v>
+        <v>94583</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30778,35 +30764,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30815,10 +30801,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537472</v>
+        <v>537620</v>
       </c>
       <c r="R230" t="n">
-        <v>6656651</v>
+        <v>6656858</v>
       </c>
       <c r="S230" t="n">
         <v>5</v>
@@ -30845,12 +30831,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30881,10 +30867,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236135</v>
+        <v>121236153</v>
       </c>
       <c r="B231" t="n">
-        <v>98081</v>
+        <v>91453</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30893,35 +30879,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -30930,13 +30916,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537439</v>
+        <v>537763</v>
       </c>
       <c r="R231" t="n">
-        <v>6656570</v>
+        <v>6656846</v>
       </c>
       <c r="S231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30996,10 +30982,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236192</v>
+        <v>121236151</v>
       </c>
       <c r="B232" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31012,21 +30998,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31034,21 +31020,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537475</v>
+        <v>537730</v>
       </c>
       <c r="R232" t="n">
-        <v>6656526</v>
+        <v>6656998</v>
       </c>
       <c r="S232" t="n">
         <v>4</v>
@@ -31075,12 +31061,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -31111,10 +31097,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236177</v>
+        <v>121236166</v>
       </c>
       <c r="B233" t="n">
-        <v>98081</v>
+        <v>92006</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31123,35 +31109,35 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -31160,13 +31146,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537470</v>
+        <v>537531</v>
       </c>
       <c r="R233" t="n">
-        <v>6656705</v>
+        <v>6657006</v>
       </c>
       <c r="S233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -31226,10 +31212,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236172</v>
+        <v>121236188</v>
       </c>
       <c r="B234" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31238,50 +31224,57 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537513</v>
+        <v>537594</v>
       </c>
       <c r="R234" t="n">
-        <v>6656728</v>
+        <v>6656653</v>
       </c>
       <c r="S234" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31341,10 +31334,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236150</v>
+        <v>121236192</v>
       </c>
       <c r="B235" t="n">
-        <v>105186</v>
+        <v>57351</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31353,25 +31346,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -31379,21 +31372,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537738</v>
+        <v>537475</v>
       </c>
       <c r="R235" t="n">
-        <v>6657048</v>
+        <v>6656526</v>
       </c>
       <c r="S235" t="n">
         <v>4</v>
@@ -31420,12 +31413,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31456,10 +31449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236197</v>
+        <v>121236173</v>
       </c>
       <c r="B236" t="n">
-        <v>90983</v>
+        <v>98081</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31468,47 +31461,47 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537490</v>
+        <v>537505</v>
       </c>
       <c r="R236" t="n">
-        <v>6656487</v>
+        <v>6656739</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -31571,10 +31564,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236142</v>
+        <v>121236159</v>
       </c>
       <c r="B237" t="n">
-        <v>90662</v>
+        <v>91453</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31583,25 +31576,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5447</v>
+        <v>366</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -31620,10 +31613,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537687</v>
+        <v>537686</v>
       </c>
       <c r="R237" t="n">
-        <v>6656911</v>
+        <v>6656739</v>
       </c>
       <c r="S237" t="n">
         <v>4</v>
@@ -31686,10 +31679,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236168</v>
+        <v>121236184</v>
       </c>
       <c r="B238" t="n">
-        <v>79586</v>
+        <v>91965</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31698,35 +31691,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31735,10 +31728,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537571</v>
+        <v>537431</v>
       </c>
       <c r="R238" t="n">
-        <v>6656818</v>
+        <v>6656597</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -31801,10 +31794,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236159</v>
+        <v>121236139</v>
       </c>
       <c r="B239" t="n">
-        <v>91453</v>
+        <v>57367</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31817,21 +31810,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>366</v>
+        <v>100049</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -31839,21 +31832,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537686</v>
+        <v>537547</v>
       </c>
       <c r="R239" t="n">
-        <v>6656739</v>
+        <v>6656935</v>
       </c>
       <c r="S239" t="n">
         <v>4</v>
@@ -31916,10 +31916,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236136</v>
+        <v>121236181</v>
       </c>
       <c r="B240" t="n">
-        <v>90644</v>
+        <v>98081</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31928,35 +31928,35 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -31965,13 +31965,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537697</v>
+        <v>537438</v>
       </c>
       <c r="R240" t="n">
-        <v>6656821</v>
+        <v>6656699</v>
       </c>
       <c r="S240" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31995,12 +31995,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32031,10 +32031,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236164</v>
+        <v>121236137</v>
       </c>
       <c r="B241" t="n">
-        <v>98081</v>
+        <v>91312</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32043,35 +32043,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32080,13 +32080,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537484</v>
+        <v>537682</v>
       </c>
       <c r="R241" t="n">
-        <v>6656656</v>
+        <v>6656810</v>
       </c>
       <c r="S241" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -32110,12 +32110,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32146,10 +32146,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236175</v>
+        <v>121236136</v>
       </c>
       <c r="B242" t="n">
-        <v>98081</v>
+        <v>90644</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32158,35 +32158,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32195,13 +32195,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537491</v>
+        <v>537697</v>
       </c>
       <c r="R242" t="n">
-        <v>6656738</v>
+        <v>6656821</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32225,12 +32225,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32261,10 +32261,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236146</v>
+        <v>121236194</v>
       </c>
       <c r="B243" t="n">
-        <v>57504</v>
+        <v>90662</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32273,45 +32273,50 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537687</v>
+        <v>537520</v>
       </c>
       <c r="R243" t="n">
-        <v>6656879</v>
+        <v>6656530</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32335,12 +32340,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32376,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236163</v>
+        <v>121236146</v>
       </c>
       <c r="B244" t="n">
-        <v>90662</v>
+        <v>57504</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,47 +32388,42 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537447</v>
+        <v>537687</v>
       </c>
       <c r="R244" t="n">
-        <v>6656508</v>
+        <v>6656879</v>
       </c>
       <c r="S244" t="n">
         <v>4</v>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236152</v>
+        <v>121236164</v>
       </c>
       <c r="B245" t="n">
-        <v>91312</v>
+        <v>98081</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537756</v>
+        <v>537484</v>
       </c>
       <c r="R245" t="n">
-        <v>6656968</v>
+        <v>6656656</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,7 +32601,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236174</v>
+        <v>121236172</v>
       </c>
       <c r="B246" t="n">
         <v>98081</v>
@@ -32650,13 +32650,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537502</v>
+        <v>537513</v>
       </c>
       <c r="R246" t="n">
-        <v>6656738</v>
+        <v>6656728</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -27421,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236150</v>
+        <v>121236154</v>
       </c>
       <c r="B201" t="n">
-        <v>105186</v>
+        <v>94496</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27437,21 +27437,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>221144</v>
+        <v>2813</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -27461,19 +27461,19 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537738</v>
+        <v>537724</v>
       </c>
       <c r="R201" t="n">
-        <v>6657048</v>
+        <v>6656830</v>
       </c>
       <c r="S201" t="n">
         <v>4</v>
@@ -27536,10 +27536,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236154</v>
+        <v>121236142</v>
       </c>
       <c r="B202" t="n">
-        <v>94496</v>
+        <v>90662</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27552,21 +27552,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2813</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -27585,10 +27585,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537724</v>
+        <v>537687</v>
       </c>
       <c r="R202" t="n">
-        <v>6656830</v>
+        <v>6656911</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -27651,10 +27651,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236142</v>
+        <v>121236169</v>
       </c>
       <c r="B203" t="n">
-        <v>90662</v>
+        <v>98081</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27663,35 +27663,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27700,10 +27700,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537687</v>
+        <v>537474</v>
       </c>
       <c r="R203" t="n">
-        <v>6656911</v>
+        <v>6656770</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -27730,12 +27730,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27766,7 +27766,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236169</v>
+        <v>121236170</v>
       </c>
       <c r="B204" t="n">
         <v>98081</v>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -27815,10 +27815,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537474</v>
+        <v>537452</v>
       </c>
       <c r="R204" t="n">
-        <v>6656770</v>
+        <v>6656767</v>
       </c>
       <c r="S204" t="n">
         <v>4</v>
@@ -27881,7 +27881,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236170</v>
+        <v>121236171</v>
       </c>
       <c r="B205" t="n">
         <v>98081</v>
@@ -27916,7 +27916,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -27930,10 +27930,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537452</v>
+        <v>537516</v>
       </c>
       <c r="R205" t="n">
-        <v>6656767</v>
+        <v>6656778</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -27996,10 +27996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236171</v>
+        <v>121236150</v>
       </c>
       <c r="B206" t="n">
-        <v>98081</v>
+        <v>105186</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28008,30 +28008,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -28041,14 +28041,14 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537516</v>
+        <v>537738</v>
       </c>
       <c r="R206" t="n">
-        <v>6656778</v>
+        <v>6657048</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -28075,12 +28075,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -29491,10 +29491,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236165</v>
+        <v>121236198</v>
       </c>
       <c r="B219" t="n">
-        <v>8421</v>
+        <v>90697</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29503,50 +29503,50 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537568</v>
+        <v>537497</v>
       </c>
       <c r="R219" t="n">
-        <v>6657060</v>
+        <v>6656496</v>
       </c>
       <c r="S219" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29584,7 +29584,6 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
@@ -29607,7 +29606,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236198</v>
+        <v>121236182</v>
       </c>
       <c r="B220" t="n">
         <v>90697</v>
@@ -29652,14 +29651,14 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537497</v>
+        <v>537413</v>
       </c>
       <c r="R220" t="n">
-        <v>6656496</v>
+        <v>6656645</v>
       </c>
       <c r="S220" t="n">
         <v>6</v>
@@ -29722,10 +29721,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236182</v>
+        <v>121236165</v>
       </c>
       <c r="B221" t="n">
-        <v>90697</v>
+        <v>8421</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29734,50 +29733,50 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537413</v>
+        <v>537568</v>
       </c>
       <c r="R221" t="n">
-        <v>6656645</v>
+        <v>6657060</v>
       </c>
       <c r="S221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29815,6 +29814,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -30527,10 +30527,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236178</v>
+        <v>121236197</v>
       </c>
       <c r="B228" t="n">
-        <v>57504</v>
+        <v>90983</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30543,41 +30543,46 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537468</v>
+        <v>537490</v>
       </c>
       <c r="R228" t="n">
-        <v>6656748</v>
+        <v>6656487</v>
       </c>
       <c r="S228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30637,10 +30642,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236197</v>
+        <v>121236138</v>
       </c>
       <c r="B229" t="n">
-        <v>90983</v>
+        <v>94583</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30649,47 +30654,47 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>658</v>
+        <v>2667</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537490</v>
+        <v>537620</v>
       </c>
       <c r="R229" t="n">
-        <v>6656487</v>
+        <v>6656858</v>
       </c>
       <c r="S229" t="n">
         <v>5</v>
@@ -30716,12 +30721,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30752,10 +30757,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236138</v>
+        <v>121236178</v>
       </c>
       <c r="B230" t="n">
-        <v>94583</v>
+        <v>57504</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30764,35 +30769,30 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2667</v>
+        <v>103021</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30801,13 +30801,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537620</v>
+        <v>537468</v>
       </c>
       <c r="R230" t="n">
-        <v>6656858</v>
+        <v>6656748</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30831,12 +30831,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD230" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90243</v>
+        <v>90255</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
+          <t>Helena Björnström, Olavi Niemelä, Uno Skog, Janolof Hermansson, Maria Hindemo, Andreas Öster</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90243</v>
+        <v>90255</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236144</v>
+        <v>121236180</v>
       </c>
       <c r="B190" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,35 +26168,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -26205,10 +26205,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537672</v>
+        <v>537443</v>
       </c>
       <c r="R190" t="n">
-        <v>6656897</v>
+        <v>6656691</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26235,12 +26235,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236149</v>
+        <v>121236152</v>
       </c>
       <c r="B191" t="n">
-        <v>98081</v>
+        <v>91324</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,35 +26283,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -26320,10 +26320,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537712</v>
+        <v>537756</v>
       </c>
       <c r="R191" t="n">
-        <v>6657066</v>
+        <v>6656968</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236186</v>
+        <v>121236163</v>
       </c>
       <c r="B192" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,50 +26398,50 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537546</v>
+        <v>537447</v>
       </c>
       <c r="R192" t="n">
-        <v>6656619</v>
+        <v>6656508</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26465,12 +26465,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -26501,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236193</v>
+        <v>121236141</v>
       </c>
       <c r="B193" t="n">
-        <v>92008</v>
+        <v>98094</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,50 +26513,50 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537518</v>
+        <v>537629</v>
       </c>
       <c r="R193" t="n">
-        <v>6656512</v>
+        <v>6656969</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26580,12 +26580,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -26616,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236190</v>
+        <v>121236170</v>
       </c>
       <c r="B194" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26628,50 +26628,50 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537476</v>
+        <v>537452</v>
       </c>
       <c r="R194" t="n">
-        <v>6656522</v>
+        <v>6656767</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236163</v>
+        <v>121236149</v>
       </c>
       <c r="B195" t="n">
-        <v>90662</v>
+        <v>98094</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,47 +26743,47 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537447</v>
+        <v>537712</v>
       </c>
       <c r="R195" t="n">
-        <v>6656508</v>
+        <v>6657066</v>
       </c>
       <c r="S195" t="n">
         <v>4</v>
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236160</v>
+        <v>121236175</v>
       </c>
       <c r="B196" t="n">
-        <v>94604</v>
+        <v>98094</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,35 +26858,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26895,13 +26895,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537624</v>
+        <v>537491</v>
       </c>
       <c r="R196" t="n">
-        <v>6656708</v>
+        <v>6656738</v>
       </c>
       <c r="S196" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26925,12 +26925,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236174</v>
+        <v>121236192</v>
       </c>
       <c r="B197" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,50 +26973,50 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537502</v>
+        <v>537475</v>
       </c>
       <c r="R197" t="n">
-        <v>6656738</v>
+        <v>6656526</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27076,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236176</v>
+        <v>121236182</v>
       </c>
       <c r="B198" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27088,35 +27088,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27125,13 +27125,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537462</v>
+        <v>537413</v>
       </c>
       <c r="R198" t="n">
-        <v>6656736</v>
+        <v>6656645</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27191,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236189</v>
+        <v>121236147</v>
       </c>
       <c r="B199" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27203,35 +27203,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -27240,10 +27240,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537497</v>
+        <v>537705</v>
       </c>
       <c r="R199" t="n">
-        <v>6656581</v>
+        <v>6656899</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -27270,12 +27270,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27306,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236155</v>
+        <v>121236195</v>
       </c>
       <c r="B200" t="n">
-        <v>90697</v>
+        <v>57351</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27322,21 +27322,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -27344,24 +27344,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537736</v>
+        <v>537508</v>
       </c>
       <c r="R200" t="n">
-        <v>6656837</v>
+        <v>6656516</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27385,12 +27385,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27421,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236154</v>
+        <v>121236181</v>
       </c>
       <c r="B201" t="n">
-        <v>94496</v>
+        <v>98094</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27433,35 +27433,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -27470,13 +27470,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537724</v>
+        <v>537438</v>
       </c>
       <c r="R201" t="n">
-        <v>6656830</v>
+        <v>6656699</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27500,12 +27500,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27536,10 +27536,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236142</v>
+        <v>121236136</v>
       </c>
       <c r="B202" t="n">
-        <v>90662</v>
+        <v>90656</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27548,25 +27548,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -27585,10 +27585,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537687</v>
+        <v>537697</v>
       </c>
       <c r="R202" t="n">
-        <v>6656911</v>
+        <v>6656821</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -27651,10 +27651,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236169</v>
+        <v>121236137</v>
       </c>
       <c r="B203" t="n">
-        <v>98081</v>
+        <v>91324</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27663,35 +27663,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27700,10 +27700,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537474</v>
+        <v>537682</v>
       </c>
       <c r="R203" t="n">
-        <v>6656770</v>
+        <v>6656810</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -27730,12 +27730,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27766,10 +27766,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236170</v>
+        <v>121236197</v>
       </c>
       <c r="B204" t="n">
-        <v>98081</v>
+        <v>90995</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27778,50 +27778,50 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537452</v>
+        <v>537490</v>
       </c>
       <c r="R204" t="n">
-        <v>6656767</v>
+        <v>6656487</v>
       </c>
       <c r="S204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27881,10 +27881,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236171</v>
+        <v>121236154</v>
       </c>
       <c r="B205" t="n">
-        <v>98081</v>
+        <v>94508</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27893,35 +27893,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27930,10 +27930,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537516</v>
+        <v>537724</v>
       </c>
       <c r="R205" t="n">
-        <v>6656778</v>
+        <v>6656830</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -27960,12 +27960,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27996,10 +27996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236150</v>
+        <v>121236193</v>
       </c>
       <c r="B206" t="n">
-        <v>105186</v>
+        <v>92020</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28008,50 +28008,50 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221144</v>
+        <v>5966</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537738</v>
+        <v>537518</v>
       </c>
       <c r="R206" t="n">
-        <v>6657048</v>
+        <v>6656512</v>
       </c>
       <c r="S206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28075,12 +28075,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28111,10 +28111,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236157</v>
+        <v>121236196</v>
       </c>
       <c r="B207" t="n">
-        <v>90747</v>
+        <v>91053</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28123,25 +28123,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5321</v>
+        <v>2062</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28156,17 +28156,17 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537695</v>
+        <v>537490</v>
       </c>
       <c r="R207" t="n">
-        <v>6656728</v>
+        <v>6656495</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -28190,12 +28190,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28226,10 +28226,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236185</v>
+        <v>121236198</v>
       </c>
       <c r="B208" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28238,50 +28238,50 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537472</v>
+        <v>537497</v>
       </c>
       <c r="R208" t="n">
-        <v>6656651</v>
+        <v>6656496</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28341,10 +28341,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236177</v>
+        <v>121236138</v>
       </c>
       <c r="B209" t="n">
-        <v>98081</v>
+        <v>94595</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28353,35 +28353,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -28390,13 +28390,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537470</v>
+        <v>537620</v>
       </c>
       <c r="R209" t="n">
-        <v>6656705</v>
+        <v>6656858</v>
       </c>
       <c r="S209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -28420,12 +28420,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -28456,10 +28456,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236180</v>
+        <v>121236166</v>
       </c>
       <c r="B210" t="n">
-        <v>98081</v>
+        <v>92018</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28468,35 +28468,35 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -28505,10 +28505,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537443</v>
+        <v>537531</v>
       </c>
       <c r="R210" t="n">
-        <v>6656691</v>
+        <v>6657006</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -28571,10 +28571,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236147</v>
+        <v>121236172</v>
       </c>
       <c r="B211" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28583,35 +28583,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28620,13 +28620,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537705</v>
+        <v>537513</v>
       </c>
       <c r="R211" t="n">
-        <v>6656899</v>
+        <v>6656728</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28650,12 +28650,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28686,10 +28686,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236196</v>
+        <v>121236168</v>
       </c>
       <c r="B212" t="n">
-        <v>91041</v>
+        <v>79589</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28698,25 +28698,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -28726,22 +28726,22 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537490</v>
+        <v>537571</v>
       </c>
       <c r="R212" t="n">
-        <v>6656495</v>
+        <v>6656818</v>
       </c>
       <c r="S212" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28801,10 +28801,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236162</v>
+        <v>121236151</v>
       </c>
       <c r="B213" t="n">
-        <v>91312</v>
+        <v>90709</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28813,25 +28813,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -28846,14 +28846,14 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537631</v>
+        <v>537730</v>
       </c>
       <c r="R213" t="n">
-        <v>6656665</v>
+        <v>6656998</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28916,10 +28916,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236143</v>
+        <v>121236194</v>
       </c>
       <c r="B214" t="n">
-        <v>91630</v>
+        <v>90674</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28932,21 +28932,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28961,14 +28961,14 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537674</v>
+        <v>537520</v>
       </c>
       <c r="R214" t="n">
-        <v>6656893</v>
+        <v>6656530</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -28995,12 +28995,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -29031,10 +29031,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236141</v>
+        <v>121236146</v>
       </c>
       <c r="B215" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29043,35 +29043,30 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29080,10 +29075,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537629</v>
+        <v>537687</v>
       </c>
       <c r="R215" t="n">
-        <v>6656969</v>
+        <v>6656879</v>
       </c>
       <c r="S215" t="n">
         <v>4</v>
@@ -29146,10 +29141,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236152</v>
+        <v>121236143</v>
       </c>
       <c r="B216" t="n">
-        <v>91312</v>
+        <v>91642</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29162,21 +29157,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1339</v>
+        <v>4769</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -29191,17 +29186,17 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537756</v>
+        <v>537674</v>
       </c>
       <c r="R216" t="n">
-        <v>6656968</v>
+        <v>6656893</v>
       </c>
       <c r="S216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29261,10 +29256,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236140</v>
+        <v>121236184</v>
       </c>
       <c r="B217" t="n">
-        <v>90662</v>
+        <v>91977</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29273,30 +29268,30 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -29310,10 +29305,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537634</v>
+        <v>537431</v>
       </c>
       <c r="R217" t="n">
-        <v>6657019</v>
+        <v>6656597</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29340,12 +29335,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29376,10 +29371,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236135</v>
+        <v>121236142</v>
       </c>
       <c r="B218" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29388,35 +29383,35 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -29425,10 +29420,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537439</v>
+        <v>537687</v>
       </c>
       <c r="R218" t="n">
-        <v>6656570</v>
+        <v>6656911</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29491,10 +29486,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236198</v>
+        <v>121236150</v>
       </c>
       <c r="B219" t="n">
-        <v>90697</v>
+        <v>105199</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29503,25 +29498,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29531,22 +29526,22 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537497</v>
+        <v>537738</v>
       </c>
       <c r="R219" t="n">
-        <v>6656496</v>
+        <v>6657048</v>
       </c>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29570,12 +29565,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29606,10 +29601,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236182</v>
+        <v>121236173</v>
       </c>
       <c r="B220" t="n">
-        <v>90697</v>
+        <v>98094</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29618,35 +29613,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29655,13 +29650,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537413</v>
+        <v>537505</v>
       </c>
       <c r="R220" t="n">
-        <v>6656645</v>
+        <v>6656739</v>
       </c>
       <c r="S220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29721,10 +29716,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236165</v>
+        <v>121236185</v>
       </c>
       <c r="B221" t="n">
-        <v>8421</v>
+        <v>98094</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29733,47 +29728,47 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537568</v>
+        <v>537472</v>
       </c>
       <c r="R221" t="n">
-        <v>6657060</v>
+        <v>6656651</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29814,7 +29809,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -29837,10 +29831,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236175</v>
+        <v>121236169</v>
       </c>
       <c r="B222" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29886,13 +29880,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537491</v>
+        <v>537474</v>
       </c>
       <c r="R222" t="n">
-        <v>6656738</v>
+        <v>6656770</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29952,10 +29946,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236168</v>
+        <v>121236187</v>
       </c>
       <c r="B223" t="n">
-        <v>79586</v>
+        <v>98094</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29964,35 +29958,35 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -30001,10 +29995,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537571</v>
+        <v>537559</v>
       </c>
       <c r="R223" t="n">
-        <v>6656818</v>
+        <v>6656606</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -30067,10 +30061,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236187</v>
+        <v>121236164</v>
       </c>
       <c r="B224" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30116,10 +30110,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537559</v>
+        <v>537484</v>
       </c>
       <c r="R224" t="n">
-        <v>6656606</v>
+        <v>6656656</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -30182,10 +30176,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236167</v>
+        <v>121236140</v>
       </c>
       <c r="B225" t="n">
-        <v>98081</v>
+        <v>90674</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30194,35 +30188,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -30231,10 +30225,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537517</v>
+        <v>537634</v>
       </c>
       <c r="R225" t="n">
-        <v>6656819</v>
+        <v>6657019</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -30261,12 +30255,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30297,10 +30291,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236145</v>
+        <v>121236176</v>
       </c>
       <c r="B226" t="n">
-        <v>94484</v>
+        <v>98094</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30309,35 +30303,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30346,13 +30340,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537686</v>
+        <v>537462</v>
       </c>
       <c r="R226" t="n">
-        <v>6656878</v>
+        <v>6656736</v>
       </c>
       <c r="S226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30376,12 +30370,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30412,10 +30406,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236195</v>
+        <v>121236144</v>
       </c>
       <c r="B227" t="n">
-        <v>57351</v>
+        <v>57367</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30428,16 +30422,16 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -30452,19 +30446,19 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537508</v>
+        <v>537672</v>
       </c>
       <c r="R227" t="n">
-        <v>6656516</v>
+        <v>6656897</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -30491,12 +30485,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30527,10 +30521,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236197</v>
+        <v>121236188</v>
       </c>
       <c r="B228" t="n">
-        <v>90983</v>
+        <v>57367</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30543,21 +30537,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -30565,21 +30559,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537490</v>
+        <v>537594</v>
       </c>
       <c r="R228" t="n">
-        <v>6656487</v>
+        <v>6656653</v>
       </c>
       <c r="S228" t="n">
         <v>5</v>
@@ -30642,10 +30643,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236138</v>
+        <v>121236190</v>
       </c>
       <c r="B229" t="n">
-        <v>94583</v>
+        <v>90709</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30654,50 +30655,50 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537620</v>
+        <v>537476</v>
       </c>
       <c r="R229" t="n">
-        <v>6656858</v>
+        <v>6656522</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30721,12 +30722,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30757,10 +30758,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236178</v>
+        <v>121236167</v>
       </c>
       <c r="B230" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30769,30 +30770,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30801,13 +30807,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537468</v>
+        <v>537517</v>
       </c>
       <c r="R230" t="n">
-        <v>6656748</v>
+        <v>6656819</v>
       </c>
       <c r="S230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30867,10 +30873,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236153</v>
+        <v>121236135</v>
       </c>
       <c r="B231" t="n">
-        <v>91453</v>
+        <v>98094</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30879,35 +30885,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -30916,13 +30922,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537763</v>
+        <v>537439</v>
       </c>
       <c r="R231" t="n">
-        <v>6656846</v>
+        <v>6656570</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30982,10 +30988,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236151</v>
+        <v>121236157</v>
       </c>
       <c r="B232" t="n">
-        <v>90697</v>
+        <v>90759</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30994,25 +31000,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1202</v>
+        <v>5321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31027,17 +31033,17 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537730</v>
+        <v>537695</v>
       </c>
       <c r="R232" t="n">
-        <v>6656998</v>
+        <v>6656728</v>
       </c>
       <c r="S232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31097,10 +31103,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236166</v>
+        <v>121236145</v>
       </c>
       <c r="B233" t="n">
-        <v>92006</v>
+        <v>94496</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31113,31 +31119,31 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5964</v>
+        <v>2809</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -31146,13 +31152,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537531</v>
+        <v>537686</v>
       </c>
       <c r="R233" t="n">
-        <v>6657006</v>
+        <v>6656878</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -31176,12 +31182,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -31212,10 +31218,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236188</v>
+        <v>121236186</v>
       </c>
       <c r="B234" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31224,54 +31230,47 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537594</v>
+        <v>537546</v>
       </c>
       <c r="R234" t="n">
-        <v>6656653</v>
+        <v>6656619</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -31334,10 +31333,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236192</v>
+        <v>121236165</v>
       </c>
       <c r="B235" t="n">
-        <v>57351</v>
+        <v>8421</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31346,50 +31345,50 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>100109</v>
+        <v>106554</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537475</v>
+        <v>537568</v>
       </c>
       <c r="R235" t="n">
-        <v>6656526</v>
+        <v>6657060</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31427,6 +31426,7 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
+      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -31449,10 +31449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236173</v>
+        <v>121236177</v>
       </c>
       <c r="B236" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -31498,13 +31498,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537505</v>
+        <v>537470</v>
       </c>
       <c r="R236" t="n">
-        <v>6656739</v>
+        <v>6656705</v>
       </c>
       <c r="S236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31564,10 +31564,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236159</v>
+        <v>121236153</v>
       </c>
       <c r="B237" t="n">
-        <v>91453</v>
+        <v>91465</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31613,13 +31613,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537686</v>
+        <v>537763</v>
       </c>
       <c r="R237" t="n">
-        <v>6656739</v>
+        <v>6656846</v>
       </c>
       <c r="S237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31679,10 +31679,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236184</v>
+        <v>121236159</v>
       </c>
       <c r="B238" t="n">
-        <v>91965</v>
+        <v>91465</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31695,26 +31695,26 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4361</v>
+        <v>366</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -31728,13 +31728,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537431</v>
+        <v>537686</v>
       </c>
       <c r="R238" t="n">
-        <v>6656597</v>
+        <v>6656739</v>
       </c>
       <c r="S238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -31758,12 +31758,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31794,10 +31794,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236139</v>
+        <v>121236178</v>
       </c>
       <c r="B239" t="n">
-        <v>57367</v>
+        <v>57504</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31810,50 +31810,38 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537547</v>
+        <v>537468</v>
       </c>
       <c r="R239" t="n">
-        <v>6656935</v>
+        <v>6656748</v>
       </c>
       <c r="S239" t="n">
         <v>4</v>
@@ -31880,12 +31868,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31916,10 +31904,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236181</v>
+        <v>121236155</v>
       </c>
       <c r="B240" t="n">
-        <v>98081</v>
+        <v>90709</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31928,35 +31916,35 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -31965,13 +31953,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537438</v>
+        <v>537736</v>
       </c>
       <c r="R240" t="n">
-        <v>6656699</v>
+        <v>6656837</v>
       </c>
       <c r="S240" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31995,12 +31983,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32031,10 +32019,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236137</v>
+        <v>121236160</v>
       </c>
       <c r="B241" t="n">
-        <v>91312</v>
+        <v>94616</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32047,31 +32035,31 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32080,10 +32068,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537682</v>
+        <v>537624</v>
       </c>
       <c r="R241" t="n">
-        <v>6656810</v>
+        <v>6656708</v>
       </c>
       <c r="S241" t="n">
         <v>4</v>
@@ -32146,10 +32134,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236136</v>
+        <v>121236162</v>
       </c>
       <c r="B242" t="n">
-        <v>90644</v>
+        <v>91324</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32158,25 +32146,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>112</v>
+        <v>1339</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -32186,7 +32174,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32195,10 +32183,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537697</v>
+        <v>537631</v>
       </c>
       <c r="R242" t="n">
-        <v>6656821</v>
+        <v>6656665</v>
       </c>
       <c r="S242" t="n">
         <v>4</v>
@@ -32261,10 +32249,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236194</v>
+        <v>121236139</v>
       </c>
       <c r="B243" t="n">
-        <v>90662</v>
+        <v>57367</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32273,25 +32261,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -32299,24 +32287,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537520</v>
+        <v>537547</v>
       </c>
       <c r="R243" t="n">
-        <v>6656530</v>
+        <v>6656935</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32340,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32376,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236146</v>
+        <v>121236174</v>
       </c>
       <c r="B244" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32388,30 +32383,35 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537687</v>
+        <v>537502</v>
       </c>
       <c r="R244" t="n">
-        <v>6656879</v>
+        <v>6656738</v>
       </c>
       <c r="S244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32450,12 +32450,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236164</v>
+        <v>121236171</v>
       </c>
       <c r="B245" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32535,13 +32535,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537484</v>
+        <v>537516</v>
       </c>
       <c r="R245" t="n">
-        <v>6656656</v>
+        <v>6656778</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236172</v>
+        <v>121236189</v>
       </c>
       <c r="B246" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -32650,13 +32650,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537513</v>
+        <v>537497</v>
       </c>
       <c r="R246" t="n">
-        <v>6656728</v>
+        <v>6656581</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32716,10 +32716,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B247" t="n">
-        <v>94700</v>
+        <v>94712</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R247" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,10 +32831,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B248" t="n">
-        <v>94700</v>
+        <v>94712</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R248" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90255</v>
+        <v>90256</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Helena Björnström, Olavi Niemelä, Uno Skog, Janolof Hermansson, Maria Hindemo, Andreas Öster</t>
+          <t>Andreas Öster, Maria Hindemo, Janolof Hermansson, Uno Skog, Olavi Niemelä, Helena Björnström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90255</v>
+        <v>90256</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236180</v>
+        <v>121236195</v>
       </c>
       <c r="B190" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,47 +26168,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537443</v>
+        <v>537508</v>
       </c>
       <c r="R190" t="n">
-        <v>6656691</v>
+        <v>6656516</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236152</v>
+        <v>121236165</v>
       </c>
       <c r="B191" t="n">
-        <v>91324</v>
+        <v>8421</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26287,46 +26287,46 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1339</v>
+        <v>106554</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537756</v>
+        <v>537568</v>
       </c>
       <c r="R191" t="n">
-        <v>6656968</v>
+        <v>6657060</v>
       </c>
       <c r="S191" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -26364,6 +26364,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -26386,10 +26387,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236163</v>
+        <v>121236142</v>
       </c>
       <c r="B192" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26431,14 +26432,14 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537447</v>
+        <v>537687</v>
       </c>
       <c r="R192" t="n">
-        <v>6656508</v>
+        <v>6656911</v>
       </c>
       <c r="S192" t="n">
         <v>4</v>
@@ -26501,10 +26502,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236141</v>
+        <v>121236135</v>
       </c>
       <c r="B193" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26536,7 +26537,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -26550,10 +26551,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537629</v>
+        <v>537439</v>
       </c>
       <c r="R193" t="n">
-        <v>6656969</v>
+        <v>6656570</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -26616,10 +26617,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236170</v>
+        <v>121236144</v>
       </c>
       <c r="B194" t="n">
-        <v>98094</v>
+        <v>57367</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26628,35 +26629,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26665,13 +26666,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537452</v>
+        <v>537672</v>
       </c>
       <c r="R194" t="n">
-        <v>6656767</v>
+        <v>6656897</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26695,12 +26696,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26731,10 +26732,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236149</v>
+        <v>121236192</v>
       </c>
       <c r="B195" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,47 +26744,47 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537712</v>
+        <v>537475</v>
       </c>
       <c r="R195" t="n">
-        <v>6657066</v>
+        <v>6656526</v>
       </c>
       <c r="S195" t="n">
         <v>4</v>
@@ -26810,12 +26811,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26847,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236175</v>
+        <v>121236194</v>
       </c>
       <c r="B196" t="n">
-        <v>98094</v>
+        <v>90675</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,47 +26859,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537491</v>
+        <v>537520</v>
       </c>
       <c r="R196" t="n">
-        <v>6656738</v>
+        <v>6656530</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26961,10 +26962,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236192</v>
+        <v>121236143</v>
       </c>
       <c r="B197" t="n">
-        <v>57351</v>
+        <v>91643</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,25 +26974,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -26999,24 +27000,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537475</v>
+        <v>537674</v>
       </c>
       <c r="R197" t="n">
-        <v>6656526</v>
+        <v>6656893</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27040,12 +27041,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27077,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236182</v>
+        <v>121236138</v>
       </c>
       <c r="B198" t="n">
-        <v>90709</v>
+        <v>94596</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27088,35 +27089,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1202</v>
+        <v>2667</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27125,13 +27126,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537413</v>
+        <v>537620</v>
       </c>
       <c r="R198" t="n">
-        <v>6656645</v>
+        <v>6656858</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27155,12 +27156,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27191,10 +27192,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236147</v>
+        <v>121236193</v>
       </c>
       <c r="B199" t="n">
-        <v>90709</v>
+        <v>92021</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27207,26 +27208,26 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -27236,14 +27237,14 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537705</v>
+        <v>537518</v>
       </c>
       <c r="R199" t="n">
-        <v>6656899</v>
+        <v>6656512</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -27270,12 +27271,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27306,10 +27307,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236195</v>
+        <v>121236189</v>
       </c>
       <c r="B200" t="n">
-        <v>57351</v>
+        <v>98095</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27318,47 +27319,47 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537508</v>
+        <v>537497</v>
       </c>
       <c r="R200" t="n">
-        <v>6656516</v>
+        <v>6656581</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -27421,10 +27422,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236181</v>
+        <v>121236154</v>
       </c>
       <c r="B201" t="n">
-        <v>98094</v>
+        <v>94509</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27433,35 +27434,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -27470,13 +27471,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537438</v>
+        <v>537724</v>
       </c>
       <c r="R201" t="n">
-        <v>6656699</v>
+        <v>6656830</v>
       </c>
       <c r="S201" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27500,12 +27501,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27536,10 +27537,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236136</v>
+        <v>121236172</v>
       </c>
       <c r="B202" t="n">
-        <v>90656</v>
+        <v>98095</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27548,35 +27549,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -27585,10 +27586,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537697</v>
+        <v>537513</v>
       </c>
       <c r="R202" t="n">
-        <v>6656821</v>
+        <v>6656728</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -27615,12 +27616,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27651,10 +27652,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236137</v>
+        <v>121236188</v>
       </c>
       <c r="B203" t="n">
-        <v>91324</v>
+        <v>57367</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27663,25 +27664,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -27689,24 +27690,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537682</v>
+        <v>537594</v>
       </c>
       <c r="R203" t="n">
-        <v>6656810</v>
+        <v>6656653</v>
       </c>
       <c r="S203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27730,12 +27738,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27766,10 +27774,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236197</v>
+        <v>121236150</v>
       </c>
       <c r="B204" t="n">
-        <v>90995</v>
+        <v>105200</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27778,25 +27786,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>658</v>
+        <v>221144</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -27806,22 +27814,22 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537490</v>
+        <v>537738</v>
       </c>
       <c r="R204" t="n">
-        <v>6656487</v>
+        <v>6657048</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27845,12 +27853,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27881,10 +27889,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236154</v>
+        <v>121236190</v>
       </c>
       <c r="B205" t="n">
-        <v>94508</v>
+        <v>90710</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27893,25 +27901,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2813</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -27921,22 +27929,22 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537724</v>
+        <v>537476</v>
       </c>
       <c r="R205" t="n">
-        <v>6656830</v>
+        <v>6656522</v>
       </c>
       <c r="S205" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27960,12 +27968,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27996,10 +28004,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236193</v>
+        <v>121236140</v>
       </c>
       <c r="B206" t="n">
-        <v>92020</v>
+        <v>90675</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28008,30 +28016,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -28041,14 +28049,14 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537518</v>
+        <v>537634</v>
       </c>
       <c r="R206" t="n">
-        <v>6656512</v>
+        <v>6657019</v>
       </c>
       <c r="S206" t="n">
         <v>5</v>
@@ -28075,12 +28083,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28111,10 +28119,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236196</v>
+        <v>121236173</v>
       </c>
       <c r="B207" t="n">
-        <v>91053</v>
+        <v>98095</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28127,46 +28135,46 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537490</v>
+        <v>537505</v>
       </c>
       <c r="R207" t="n">
-        <v>6656495</v>
+        <v>6656739</v>
       </c>
       <c r="S207" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -28226,10 +28234,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236198</v>
+        <v>121236164</v>
       </c>
       <c r="B208" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28238,50 +28246,50 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537497</v>
+        <v>537484</v>
       </c>
       <c r="R208" t="n">
-        <v>6656496</v>
+        <v>6656656</v>
       </c>
       <c r="S208" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28341,10 +28349,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236138</v>
+        <v>121236180</v>
       </c>
       <c r="B209" t="n">
-        <v>94595</v>
+        <v>98095</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28353,35 +28361,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -28390,10 +28398,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537620</v>
+        <v>537443</v>
       </c>
       <c r="R209" t="n">
-        <v>6656858</v>
+        <v>6656691</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28420,12 +28428,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -28456,10 +28464,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236166</v>
+        <v>121236149</v>
       </c>
       <c r="B210" t="n">
-        <v>92018</v>
+        <v>98095</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28468,50 +28476,50 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537531</v>
+        <v>537712</v>
       </c>
       <c r="R210" t="n">
-        <v>6657006</v>
+        <v>6657066</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28535,12 +28543,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28571,10 +28579,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236172</v>
+        <v>121236136</v>
       </c>
       <c r="B211" t="n">
-        <v>98094</v>
+        <v>90657</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28583,35 +28591,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28620,10 +28628,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537513</v>
+        <v>537697</v>
       </c>
       <c r="R211" t="n">
-        <v>6656728</v>
+        <v>6656821</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
@@ -28650,12 +28658,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28801,10 +28809,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236151</v>
+        <v>121236159</v>
       </c>
       <c r="B213" t="n">
-        <v>90709</v>
+        <v>91466</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28817,21 +28825,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -28846,14 +28854,14 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537730</v>
+        <v>537686</v>
       </c>
       <c r="R213" t="n">
-        <v>6656998</v>
+        <v>6656739</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28916,10 +28924,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236194</v>
+        <v>121236196</v>
       </c>
       <c r="B214" t="n">
-        <v>90674</v>
+        <v>91054</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28928,25 +28936,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28965,13 +28973,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537520</v>
+        <v>537490</v>
       </c>
       <c r="R214" t="n">
-        <v>6656530</v>
+        <v>6656495</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -29031,10 +29039,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236146</v>
+        <v>121236167</v>
       </c>
       <c r="B215" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29043,30 +29051,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29075,13 +29088,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537687</v>
+        <v>537517</v>
       </c>
       <c r="R215" t="n">
-        <v>6656879</v>
+        <v>6656819</v>
       </c>
       <c r="S215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29105,12 +29118,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29141,10 +29154,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236143</v>
+        <v>121236175</v>
       </c>
       <c r="B216" t="n">
-        <v>91642</v>
+        <v>98095</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29153,35 +29166,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29190,10 +29203,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537674</v>
+        <v>537491</v>
       </c>
       <c r="R216" t="n">
-        <v>6656893</v>
+        <v>6656738</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -29220,12 +29233,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29256,10 +29269,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236184</v>
+        <v>121236147</v>
       </c>
       <c r="B217" t="n">
-        <v>91977</v>
+        <v>90710</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29272,26 +29285,26 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -29305,10 +29318,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537431</v>
+        <v>537705</v>
       </c>
       <c r="R217" t="n">
-        <v>6656597</v>
+        <v>6656899</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29335,12 +29348,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29371,10 +29384,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236142</v>
+        <v>121236186</v>
       </c>
       <c r="B218" t="n">
-        <v>90674</v>
+        <v>98095</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29383,35 +29396,35 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -29420,13 +29433,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537687</v>
+        <v>537546</v>
       </c>
       <c r="R218" t="n">
-        <v>6656911</v>
+        <v>6656619</v>
       </c>
       <c r="S218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29450,12 +29463,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29486,10 +29499,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236150</v>
+        <v>121236182</v>
       </c>
       <c r="B219" t="n">
-        <v>105199</v>
+        <v>90710</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,25 +29511,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29526,22 +29539,22 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537738</v>
+        <v>537413</v>
       </c>
       <c r="R219" t="n">
-        <v>6657048</v>
+        <v>6656645</v>
       </c>
       <c r="S219" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29565,12 +29578,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29601,10 +29614,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236173</v>
+        <v>121236197</v>
       </c>
       <c r="B220" t="n">
-        <v>98094</v>
+        <v>90996</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29613,47 +29626,47 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537505</v>
+        <v>537490</v>
       </c>
       <c r="R220" t="n">
-        <v>6656739</v>
+        <v>6656487</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29716,10 +29729,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236185</v>
+        <v>121236184</v>
       </c>
       <c r="B221" t="n">
-        <v>98094</v>
+        <v>91978</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29728,35 +29741,35 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -29765,10 +29778,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537472</v>
+        <v>537431</v>
       </c>
       <c r="R221" t="n">
-        <v>6656651</v>
+        <v>6656597</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29831,10 +29844,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236169</v>
+        <v>121236157</v>
       </c>
       <c r="B222" t="n">
-        <v>98094</v>
+        <v>90760</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29843,35 +29856,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -29880,13 +29893,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537474</v>
+        <v>537695</v>
       </c>
       <c r="R222" t="n">
-        <v>6656770</v>
+        <v>6656728</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29910,12 +29923,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29946,10 +29959,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236187</v>
+        <v>121236171</v>
       </c>
       <c r="B223" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29995,13 +30008,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537559</v>
+        <v>537516</v>
       </c>
       <c r="R223" t="n">
-        <v>6656606</v>
+        <v>6656778</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30061,10 +30074,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236164</v>
+        <v>121236181</v>
       </c>
       <c r="B224" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30096,7 +30109,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -30110,13 +30123,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537484</v>
+        <v>537438</v>
       </c>
       <c r="R224" t="n">
-        <v>6656656</v>
+        <v>6656699</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30176,10 +30189,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236140</v>
+        <v>121236137</v>
       </c>
       <c r="B225" t="n">
-        <v>90674</v>
+        <v>91325</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30192,21 +30205,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -30225,13 +30238,13 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537634</v>
+        <v>537682</v>
       </c>
       <c r="R225" t="n">
-        <v>6657019</v>
+        <v>6656810</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30291,10 +30304,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236176</v>
+        <v>121236160</v>
       </c>
       <c r="B226" t="n">
-        <v>98094</v>
+        <v>94617</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30303,35 +30316,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30340,13 +30353,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537462</v>
+        <v>537624</v>
       </c>
       <c r="R226" t="n">
-        <v>6656736</v>
+        <v>6656708</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30370,12 +30383,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30406,7 +30419,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236144</v>
+        <v>121236139</v>
       </c>
       <c r="B227" t="n">
         <v>57367</v>
@@ -30444,24 +30457,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537672</v>
+        <v>537547</v>
       </c>
       <c r="R227" t="n">
-        <v>6656897</v>
+        <v>6656935</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30521,10 +30541,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236188</v>
+        <v>121236155</v>
       </c>
       <c r="B228" t="n">
-        <v>57367</v>
+        <v>90710</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30537,21 +30557,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -30559,31 +30579,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537594</v>
+        <v>537736</v>
       </c>
       <c r="R228" t="n">
-        <v>6656653</v>
+        <v>6656837</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30607,12 +30620,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30643,10 +30656,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236190</v>
+        <v>121236198</v>
       </c>
       <c r="B229" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30692,13 +30705,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537476</v>
+        <v>537497</v>
       </c>
       <c r="R229" t="n">
-        <v>6656522</v>
+        <v>6656496</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30758,10 +30771,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236167</v>
+        <v>121236166</v>
       </c>
       <c r="B230" t="n">
-        <v>98094</v>
+        <v>92019</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30770,35 +30783,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30807,10 +30820,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537517</v>
+        <v>537531</v>
       </c>
       <c r="R230" t="n">
-        <v>6656819</v>
+        <v>6657006</v>
       </c>
       <c r="S230" t="n">
         <v>5</v>
@@ -30873,10 +30886,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236135</v>
+        <v>121236170</v>
       </c>
       <c r="B231" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30908,7 +30921,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -30922,10 +30935,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537439</v>
+        <v>537452</v>
       </c>
       <c r="R231" t="n">
-        <v>6656570</v>
+        <v>6656767</v>
       </c>
       <c r="S231" t="n">
         <v>4</v>
@@ -30952,12 +30965,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30988,10 +31001,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236157</v>
+        <v>121236162</v>
       </c>
       <c r="B232" t="n">
-        <v>90759</v>
+        <v>91325</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31004,21 +31017,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5321</v>
+        <v>1339</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31037,13 +31050,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537695</v>
+        <v>537631</v>
       </c>
       <c r="R232" t="n">
-        <v>6656728</v>
+        <v>6656665</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31103,10 +31116,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236145</v>
+        <v>121236163</v>
       </c>
       <c r="B233" t="n">
-        <v>94496</v>
+        <v>90675</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31119,21 +31132,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -31143,19 +31156,19 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537686</v>
+        <v>537447</v>
       </c>
       <c r="R233" t="n">
-        <v>6656878</v>
+        <v>6656508</v>
       </c>
       <c r="S233" t="n">
         <v>4</v>
@@ -31218,10 +31231,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236186</v>
+        <v>121236187</v>
       </c>
       <c r="B234" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31253,7 +31266,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -31267,10 +31280,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537546</v>
+        <v>537559</v>
       </c>
       <c r="R234" t="n">
-        <v>6656619</v>
+        <v>6656606</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -31333,10 +31346,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236165</v>
+        <v>121236145</v>
       </c>
       <c r="B235" t="n">
-        <v>8421</v>
+        <v>94497</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31349,46 +31362,46 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>106554</v>
+        <v>2809</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr"/>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537568</v>
+        <v>537686</v>
       </c>
       <c r="R235" t="n">
-        <v>6657060</v>
+        <v>6656878</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31412,12 +31425,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31426,7 +31439,6 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -31449,10 +31461,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236177</v>
+        <v>121236174</v>
       </c>
       <c r="B236" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31484,7 +31496,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -31498,13 +31510,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537470</v>
+        <v>537502</v>
       </c>
       <c r="R236" t="n">
-        <v>6656705</v>
+        <v>6656738</v>
       </c>
       <c r="S236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31564,10 +31576,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236153</v>
+        <v>121236176</v>
       </c>
       <c r="B237" t="n">
-        <v>91465</v>
+        <v>98095</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31576,35 +31588,35 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31613,10 +31625,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537763</v>
+        <v>537462</v>
       </c>
       <c r="R237" t="n">
-        <v>6656846</v>
+        <v>6656736</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -31643,12 +31655,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31679,10 +31691,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236159</v>
+        <v>121236178</v>
       </c>
       <c r="B238" t="n">
-        <v>91465</v>
+        <v>57504</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31695,31 +31707,26 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>366</v>
+        <v>103021</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31728,10 +31735,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537686</v>
+        <v>537468</v>
       </c>
       <c r="R238" t="n">
-        <v>6656739</v>
+        <v>6656748</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31758,12 +31765,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31794,10 +31801,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236178</v>
+        <v>121236152</v>
       </c>
       <c r="B239" t="n">
-        <v>57504</v>
+        <v>91325</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31806,42 +31813,47 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537468</v>
+        <v>537756</v>
       </c>
       <c r="R239" t="n">
-        <v>6656748</v>
+        <v>6656968</v>
       </c>
       <c r="S239" t="n">
         <v>4</v>
@@ -31868,12 +31880,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31904,10 +31916,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236155</v>
+        <v>121236185</v>
       </c>
       <c r="B240" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31916,35 +31928,35 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -31953,13 +31965,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537736</v>
+        <v>537472</v>
       </c>
       <c r="R240" t="n">
-        <v>6656837</v>
+        <v>6656651</v>
       </c>
       <c r="S240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31983,12 +31995,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32019,10 +32031,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236160</v>
+        <v>121236141</v>
       </c>
       <c r="B241" t="n">
-        <v>94616</v>
+        <v>98095</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32031,35 +32043,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32068,10 +32080,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537624</v>
+        <v>537629</v>
       </c>
       <c r="R241" t="n">
-        <v>6656708</v>
+        <v>6656969</v>
       </c>
       <c r="S241" t="n">
         <v>4</v>
@@ -32134,10 +32146,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236162</v>
+        <v>121236146</v>
       </c>
       <c r="B242" t="n">
-        <v>91324</v>
+        <v>57504</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32146,35 +32158,30 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32183,10 +32190,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537631</v>
+        <v>537687</v>
       </c>
       <c r="R242" t="n">
-        <v>6656665</v>
+        <v>6656879</v>
       </c>
       <c r="S242" t="n">
         <v>4</v>
@@ -32249,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236139</v>
+        <v>121236177</v>
       </c>
       <c r="B243" t="n">
-        <v>57367</v>
+        <v>98095</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32261,54 +32268,47 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537547</v>
+        <v>537470</v>
       </c>
       <c r="R243" t="n">
-        <v>6656935</v>
+        <v>6656705</v>
       </c>
       <c r="S243" t="n">
         <v>4</v>
@@ -32335,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236174</v>
+        <v>121236169</v>
       </c>
       <c r="B244" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537502</v>
+        <v>537474</v>
       </c>
       <c r="R244" t="n">
-        <v>6656738</v>
+        <v>6656770</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236171</v>
+        <v>121236153</v>
       </c>
       <c r="B245" t="n">
-        <v>98094</v>
+        <v>91466</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,35 +32498,35 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -32535,13 +32535,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537516</v>
+        <v>537763</v>
       </c>
       <c r="R245" t="n">
-        <v>6656778</v>
+        <v>6656846</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236189</v>
+        <v>121236151</v>
       </c>
       <c r="B246" t="n">
-        <v>98094</v>
+        <v>90710</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,50 +32613,50 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537497</v>
+        <v>537730</v>
       </c>
       <c r="R246" t="n">
-        <v>6656581</v>
+        <v>6656998</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -32719,7 +32719,7 @@
         <v>121236134</v>
       </c>
       <c r="B247" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>121236156</v>
       </c>
       <c r="B248" t="n">
-        <v>94712</v>
+        <v>94713</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90256</v>
+        <v>90259</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90256</v>
+        <v>90259</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236195</v>
+        <v>121236185</v>
       </c>
       <c r="B190" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,47 +26168,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537508</v>
+        <v>537472</v>
       </c>
       <c r="R190" t="n">
-        <v>6656516</v>
+        <v>6656651</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236165</v>
+        <v>121236196</v>
       </c>
       <c r="B191" t="n">
-        <v>8421</v>
+        <v>91057</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,50 +26283,50 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>106554</v>
+        <v>2062</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537568</v>
+        <v>537490</v>
       </c>
       <c r="R191" t="n">
-        <v>6657060</v>
+        <v>6656495</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -26364,7 +26364,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -26387,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236142</v>
+        <v>121236171</v>
       </c>
       <c r="B192" t="n">
-        <v>90675</v>
+        <v>98098</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26399,35 +26398,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -26436,10 +26435,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537687</v>
+        <v>537516</v>
       </c>
       <c r="R192" t="n">
-        <v>6656911</v>
+        <v>6656778</v>
       </c>
       <c r="S192" t="n">
         <v>4</v>
@@ -26466,12 +26465,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -26502,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236135</v>
+        <v>121236166</v>
       </c>
       <c r="B193" t="n">
-        <v>98095</v>
+        <v>92022</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26514,35 +26513,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -26551,13 +26550,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537439</v>
+        <v>537531</v>
       </c>
       <c r="R193" t="n">
-        <v>6656570</v>
+        <v>6657006</v>
       </c>
       <c r="S193" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26581,12 +26580,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -26617,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236144</v>
+        <v>121236159</v>
       </c>
       <c r="B194" t="n">
-        <v>57367</v>
+        <v>91469</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26633,21 +26632,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -26655,9 +26654,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26666,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537672</v>
+        <v>537686</v>
       </c>
       <c r="R194" t="n">
-        <v>6656897</v>
+        <v>6656739</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26732,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236192</v>
+        <v>121236154</v>
       </c>
       <c r="B195" t="n">
-        <v>57351</v>
+        <v>94512</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26744,25 +26743,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>2813</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26770,21 +26769,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537475</v>
+        <v>537724</v>
       </c>
       <c r="R195" t="n">
-        <v>6656526</v>
+        <v>6656830</v>
       </c>
       <c r="S195" t="n">
         <v>4</v>
@@ -26811,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26847,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236194</v>
+        <v>121236163</v>
       </c>
       <c r="B196" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26896,13 +26895,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537520</v>
+        <v>537447</v>
       </c>
       <c r="R196" t="n">
-        <v>6656530</v>
+        <v>6656508</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26926,12 +26925,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26962,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236143</v>
+        <v>121236140</v>
       </c>
       <c r="B197" t="n">
-        <v>91643</v>
+        <v>90678</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26978,21 +26977,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -27011,10 +27010,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537674</v>
+        <v>537634</v>
       </c>
       <c r="R197" t="n">
-        <v>6656893</v>
+        <v>6657019</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -27077,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236138</v>
+        <v>121236175</v>
       </c>
       <c r="B198" t="n">
-        <v>94596</v>
+        <v>98098</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27089,35 +27088,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27126,10 +27125,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537620</v>
+        <v>537491</v>
       </c>
       <c r="R198" t="n">
-        <v>6656858</v>
+        <v>6656738</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -27156,12 +27155,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27192,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236193</v>
+        <v>121236147</v>
       </c>
       <c r="B199" t="n">
-        <v>92021</v>
+        <v>90713</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27208,26 +27207,26 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -27237,14 +27236,14 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537518</v>
+        <v>537705</v>
       </c>
       <c r="R199" t="n">
-        <v>6656512</v>
+        <v>6656899</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -27271,12 +27270,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27307,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236189</v>
+        <v>121236162</v>
       </c>
       <c r="B200" t="n">
-        <v>98095</v>
+        <v>91328</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27319,35 +27318,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -27356,13 +27355,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537497</v>
+        <v>537631</v>
       </c>
       <c r="R200" t="n">
-        <v>6656581</v>
+        <v>6656665</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27386,12 +27385,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27422,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236154</v>
+        <v>121236164</v>
       </c>
       <c r="B201" t="n">
-        <v>94509</v>
+        <v>98098</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27434,35 +27433,35 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -27471,13 +27470,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537724</v>
+        <v>537484</v>
       </c>
       <c r="R201" t="n">
-        <v>6656830</v>
+        <v>6656656</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27501,12 +27500,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27537,10 +27536,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236172</v>
+        <v>121236152</v>
       </c>
       <c r="B202" t="n">
-        <v>98095</v>
+        <v>91328</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27549,47 +27548,47 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537513</v>
+        <v>537756</v>
       </c>
       <c r="R202" t="n">
-        <v>6656728</v>
+        <v>6656968</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -27616,12 +27615,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27652,10 +27651,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236188</v>
+        <v>121236192</v>
       </c>
       <c r="B203" t="n">
-        <v>57367</v>
+        <v>57354</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27668,16 +27667,16 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -27690,31 +27689,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N203" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537594</v>
+        <v>537475</v>
       </c>
       <c r="R203" t="n">
-        <v>6656653</v>
+        <v>6656526</v>
       </c>
       <c r="S203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27774,10 +27766,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236150</v>
+        <v>121236181</v>
       </c>
       <c r="B204" t="n">
-        <v>105200</v>
+        <v>98098</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27786,30 +27778,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -27819,17 +27811,17 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537738</v>
+        <v>537438</v>
       </c>
       <c r="R204" t="n">
-        <v>6657048</v>
+        <v>6656699</v>
       </c>
       <c r="S204" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27853,12 +27845,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27889,10 +27881,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236190</v>
+        <v>121236167</v>
       </c>
       <c r="B205" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27901,50 +27893,50 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537476</v>
+        <v>537517</v>
       </c>
       <c r="R205" t="n">
-        <v>6656522</v>
+        <v>6656819</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -28004,10 +27996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236140</v>
+        <v>121236172</v>
       </c>
       <c r="B206" t="n">
-        <v>90675</v>
+        <v>98098</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28016,35 +28008,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -28053,13 +28045,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537634</v>
+        <v>537513</v>
       </c>
       <c r="R206" t="n">
-        <v>6657019</v>
+        <v>6656728</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28083,12 +28075,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28119,10 +28111,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236173</v>
+        <v>121236197</v>
       </c>
       <c r="B207" t="n">
-        <v>98095</v>
+        <v>90999</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28131,47 +28123,47 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537505</v>
+        <v>537490</v>
       </c>
       <c r="R207" t="n">
-        <v>6656739</v>
+        <v>6656487</v>
       </c>
       <c r="S207" t="n">
         <v>5</v>
@@ -28234,10 +28226,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236164</v>
+        <v>121236142</v>
       </c>
       <c r="B208" t="n">
-        <v>98095</v>
+        <v>90678</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28246,35 +28238,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -28283,13 +28275,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537484</v>
+        <v>537687</v>
       </c>
       <c r="R208" t="n">
-        <v>6656656</v>
+        <v>6656911</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28313,12 +28305,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -28349,10 +28341,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236180</v>
+        <v>121236182</v>
       </c>
       <c r="B209" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28361,35 +28353,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -28398,13 +28390,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537443</v>
+        <v>537413</v>
       </c>
       <c r="R209" t="n">
-        <v>6656691</v>
+        <v>6656645</v>
       </c>
       <c r="S209" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -28464,10 +28456,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236149</v>
+        <v>121236153</v>
       </c>
       <c r="B210" t="n">
-        <v>98095</v>
+        <v>91469</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28476,50 +28468,50 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537712</v>
+        <v>537763</v>
       </c>
       <c r="R210" t="n">
-        <v>6657066</v>
+        <v>6656846</v>
       </c>
       <c r="S210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28579,10 +28571,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236136</v>
+        <v>121236160</v>
       </c>
       <c r="B211" t="n">
-        <v>90657</v>
+        <v>94620</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28591,35 +28583,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>112</v>
+        <v>2818</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28628,10 +28620,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537697</v>
+        <v>537624</v>
       </c>
       <c r="R211" t="n">
-        <v>6656821</v>
+        <v>6656708</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
@@ -28694,10 +28686,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236168</v>
+        <v>121236184</v>
       </c>
       <c r="B212" t="n">
-        <v>79589</v>
+        <v>91981</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28706,35 +28698,35 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -28743,10 +28735,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537571</v>
+        <v>537431</v>
       </c>
       <c r="R212" t="n">
-        <v>6656818</v>
+        <v>6656597</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -28809,10 +28801,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236159</v>
+        <v>121236178</v>
       </c>
       <c r="B213" t="n">
-        <v>91466</v>
+        <v>57507</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28825,31 +28817,26 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>366</v>
+        <v>103021</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28858,10 +28845,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537686</v>
+        <v>537468</v>
       </c>
       <c r="R213" t="n">
-        <v>6656739</v>
+        <v>6656748</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28888,12 +28875,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28924,10 +28911,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236196</v>
+        <v>121236176</v>
       </c>
       <c r="B214" t="n">
-        <v>91054</v>
+        <v>98098</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28940,46 +28927,46 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537490</v>
+        <v>537462</v>
       </c>
       <c r="R214" t="n">
-        <v>6656495</v>
+        <v>6656736</v>
       </c>
       <c r="S214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -29039,10 +29026,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236167</v>
+        <v>121236143</v>
       </c>
       <c r="B215" t="n">
-        <v>98095</v>
+        <v>91646</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29051,35 +29038,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29088,10 +29075,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537517</v>
+        <v>537674</v>
       </c>
       <c r="R215" t="n">
-        <v>6656819</v>
+        <v>6656893</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -29118,12 +29105,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29154,10 +29141,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236175</v>
+        <v>121236168</v>
       </c>
       <c r="B216" t="n">
-        <v>98095</v>
+        <v>79592</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29166,35 +29153,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29203,10 +29190,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537491</v>
+        <v>537571</v>
       </c>
       <c r="R216" t="n">
-        <v>6656738</v>
+        <v>6656818</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -29269,10 +29256,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236147</v>
+        <v>121236187</v>
       </c>
       <c r="B217" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29281,35 +29268,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29318,10 +29305,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537705</v>
+        <v>537559</v>
       </c>
       <c r="R217" t="n">
-        <v>6656899</v>
+        <v>6656606</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -29348,12 +29335,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29384,10 +29371,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236186</v>
+        <v>121236193</v>
       </c>
       <c r="B218" t="n">
-        <v>98095</v>
+        <v>92024</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29396,47 +29383,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537546</v>
+        <v>537518</v>
       </c>
       <c r="R218" t="n">
-        <v>6656619</v>
+        <v>6656512</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -29499,10 +29486,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236182</v>
+        <v>121236198</v>
       </c>
       <c r="B219" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29544,14 +29531,14 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537413</v>
+        <v>537497</v>
       </c>
       <c r="R219" t="n">
-        <v>6656645</v>
+        <v>6656496</v>
       </c>
       <c r="S219" t="n">
         <v>6</v>
@@ -29614,10 +29601,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236197</v>
+        <v>121236157</v>
       </c>
       <c r="B220" t="n">
-        <v>90996</v>
+        <v>90763</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29626,25 +29613,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>658</v>
+        <v>5321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -29659,14 +29646,14 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537490</v>
+        <v>537695</v>
       </c>
       <c r="R220" t="n">
-        <v>6656487</v>
+        <v>6656728</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29693,12 +29680,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29729,10 +29716,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236184</v>
+        <v>121236194</v>
       </c>
       <c r="B221" t="n">
-        <v>91978</v>
+        <v>90678</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29741,30 +29728,30 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -29774,14 +29761,14 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537431</v>
+        <v>537520</v>
       </c>
       <c r="R221" t="n">
-        <v>6656597</v>
+        <v>6656530</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29844,10 +29831,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236157</v>
+        <v>121236141</v>
       </c>
       <c r="B222" t="n">
-        <v>90760</v>
+        <v>98098</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29856,35 +29843,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -29893,13 +29880,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537695</v>
+        <v>537629</v>
       </c>
       <c r="R222" t="n">
-        <v>6656728</v>
+        <v>6656969</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29959,10 +29946,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236171</v>
+        <v>121236138</v>
       </c>
       <c r="B223" t="n">
-        <v>98095</v>
+        <v>94599</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29971,35 +29958,35 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -30008,13 +29995,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537516</v>
+        <v>537620</v>
       </c>
       <c r="R223" t="n">
-        <v>6656778</v>
+        <v>6656858</v>
       </c>
       <c r="S223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30038,12 +30025,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30074,10 +30061,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236181</v>
+        <v>121236146</v>
       </c>
       <c r="B224" t="n">
-        <v>98095</v>
+        <v>57507</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30086,35 +30073,30 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J224" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -30123,13 +30105,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537438</v>
+        <v>537687</v>
       </c>
       <c r="R224" t="n">
-        <v>6656699</v>
+        <v>6656879</v>
       </c>
       <c r="S224" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30153,12 +30135,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30189,10 +30171,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236137</v>
+        <v>121236150</v>
       </c>
       <c r="B225" t="n">
-        <v>91325</v>
+        <v>105203</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30205,21 +30187,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1339</v>
+        <v>221144</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -30229,19 +30211,19 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537682</v>
+        <v>537738</v>
       </c>
       <c r="R225" t="n">
-        <v>6656810</v>
+        <v>6657048</v>
       </c>
       <c r="S225" t="n">
         <v>4</v>
@@ -30304,10 +30286,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236160</v>
+        <v>121236155</v>
       </c>
       <c r="B226" t="n">
-        <v>94617</v>
+        <v>90713</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30316,35 +30298,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30353,10 +30335,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537624</v>
+        <v>537736</v>
       </c>
       <c r="R226" t="n">
-        <v>6656708</v>
+        <v>6656837</v>
       </c>
       <c r="S226" t="n">
         <v>4</v>
@@ -30419,10 +30401,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236139</v>
+        <v>121236145</v>
       </c>
       <c r="B227" t="n">
-        <v>57367</v>
+        <v>94500</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30431,25 +30413,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -30457,28 +30439,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537547</v>
+        <v>537686</v>
       </c>
       <c r="R227" t="n">
-        <v>6656935</v>
+        <v>6656878</v>
       </c>
       <c r="S227" t="n">
         <v>4</v>
@@ -30541,10 +30516,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236155</v>
+        <v>121236144</v>
       </c>
       <c r="B228" t="n">
-        <v>90710</v>
+        <v>57370</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30557,21 +30532,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -30579,9 +30554,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30590,13 +30565,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537736</v>
+        <v>537672</v>
       </c>
       <c r="R228" t="n">
-        <v>6656837</v>
+        <v>6656897</v>
       </c>
       <c r="S228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30656,10 +30631,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236198</v>
+        <v>121236139</v>
       </c>
       <c r="B229" t="n">
-        <v>90710</v>
+        <v>57370</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30672,21 +30647,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -30694,24 +30669,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537497</v>
+        <v>537547</v>
       </c>
       <c r="R229" t="n">
-        <v>6656496</v>
+        <v>6656935</v>
       </c>
       <c r="S229" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30735,12 +30717,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30771,10 +30753,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236166</v>
+        <v>121236177</v>
       </c>
       <c r="B230" t="n">
-        <v>92019</v>
+        <v>98098</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30783,35 +30765,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30820,13 +30802,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537531</v>
+        <v>537470</v>
       </c>
       <c r="R230" t="n">
-        <v>6657006</v>
+        <v>6656705</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30886,10 +30868,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236170</v>
+        <v>121236190</v>
       </c>
       <c r="B231" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30898,50 +30880,50 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537452</v>
+        <v>537476</v>
       </c>
       <c r="R231" t="n">
-        <v>6656767</v>
+        <v>6656522</v>
       </c>
       <c r="S231" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -31001,10 +30983,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236162</v>
+        <v>121236188</v>
       </c>
       <c r="B232" t="n">
-        <v>91325</v>
+        <v>57370</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31013,25 +30995,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1339</v>
+        <v>100049</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31039,24 +31021,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537631</v>
+        <v>537594</v>
       </c>
       <c r="R232" t="n">
-        <v>6656665</v>
+        <v>6656653</v>
       </c>
       <c r="S232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31080,12 +31069,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -31116,10 +31105,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236163</v>
+        <v>121236195</v>
       </c>
       <c r="B233" t="n">
-        <v>90675</v>
+        <v>57354</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31128,25 +31117,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -31154,9 +31143,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -31165,13 +31154,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537447</v>
+        <v>537508</v>
       </c>
       <c r="R233" t="n">
-        <v>6656508</v>
+        <v>6656516</v>
       </c>
       <c r="S233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -31195,12 +31184,12 @@
       </c>
       <c r="Y233" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -31231,10 +31220,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236187</v>
+        <v>121236165</v>
       </c>
       <c r="B234" t="n">
-        <v>98095</v>
+        <v>8424</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31243,47 +31232,47 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537559</v>
+        <v>537568</v>
       </c>
       <c r="R234" t="n">
-        <v>6656606</v>
+        <v>6657060</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -31324,6 +31313,7 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
+      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -31346,10 +31336,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236145</v>
+        <v>121236135</v>
       </c>
       <c r="B235" t="n">
-        <v>94497</v>
+        <v>98098</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31358,35 +31348,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -31395,10 +31385,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537686</v>
+        <v>537439</v>
       </c>
       <c r="R235" t="n">
-        <v>6656878</v>
+        <v>6656570</v>
       </c>
       <c r="S235" t="n">
         <v>4</v>
@@ -31461,10 +31451,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236174</v>
+        <v>121236151</v>
       </c>
       <c r="B236" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31473,50 +31463,50 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537502</v>
+        <v>537730</v>
       </c>
       <c r="R236" t="n">
-        <v>6656738</v>
+        <v>6656998</v>
       </c>
       <c r="S236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31540,12 +31530,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31576,10 +31566,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236176</v>
+        <v>121236169</v>
       </c>
       <c r="B237" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31611,7 +31601,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -31625,13 +31615,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537462</v>
+        <v>537474</v>
       </c>
       <c r="R237" t="n">
-        <v>6656736</v>
+        <v>6656770</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31691,10 +31681,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236178</v>
+        <v>121236149</v>
       </c>
       <c r="B238" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31703,42 +31693,47 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537468</v>
+        <v>537712</v>
       </c>
       <c r="R238" t="n">
-        <v>6656748</v>
+        <v>6657066</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31765,12 +31760,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31801,10 +31796,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236152</v>
+        <v>121236174</v>
       </c>
       <c r="B239" t="n">
-        <v>91325</v>
+        <v>98098</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31813,50 +31808,50 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537756</v>
+        <v>537502</v>
       </c>
       <c r="R239" t="n">
-        <v>6656968</v>
+        <v>6656738</v>
       </c>
       <c r="S239" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31880,12 +31875,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31916,10 +31911,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236185</v>
+        <v>121236180</v>
       </c>
       <c r="B240" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31951,7 +31946,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -31965,10 +31960,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537472</v>
+        <v>537443</v>
       </c>
       <c r="R240" t="n">
-        <v>6656651</v>
+        <v>6656691</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -32031,10 +32026,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236141</v>
+        <v>121236189</v>
       </c>
       <c r="B241" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32066,7 +32061,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -32080,13 +32075,13 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537629</v>
+        <v>537497</v>
       </c>
       <c r="R241" t="n">
-        <v>6656969</v>
+        <v>6656581</v>
       </c>
       <c r="S241" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -32110,12 +32105,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32146,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236146</v>
+        <v>121236173</v>
       </c>
       <c r="B242" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32158,30 +32153,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32190,13 +32190,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537687</v>
+        <v>537505</v>
       </c>
       <c r="R242" t="n">
-        <v>6656879</v>
+        <v>6656739</v>
       </c>
       <c r="S242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32220,12 +32220,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236177</v>
+        <v>121236170</v>
       </c>
       <c r="B243" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -32305,10 +32305,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537470</v>
+        <v>537452</v>
       </c>
       <c r="R243" t="n">
-        <v>6656705</v>
+        <v>6656767</v>
       </c>
       <c r="S243" t="n">
         <v>4</v>
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236169</v>
+        <v>121236186</v>
       </c>
       <c r="B244" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537474</v>
+        <v>537546</v>
       </c>
       <c r="R244" t="n">
-        <v>6656770</v>
+        <v>6656619</v>
       </c>
       <c r="S244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236153</v>
+        <v>121236137</v>
       </c>
       <c r="B245" t="n">
-        <v>91466</v>
+        <v>91328</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,25 +32498,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>366</v>
+        <v>1339</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -32535,13 +32535,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537763</v>
+        <v>537682</v>
       </c>
       <c r="R245" t="n">
-        <v>6656846</v>
+        <v>6656810</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236151</v>
+        <v>121236136</v>
       </c>
       <c r="B246" t="n">
-        <v>90710</v>
+        <v>90660</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32617,21 +32617,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -32641,19 +32641,19 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537730</v>
+        <v>537697</v>
       </c>
       <c r="R246" t="n">
-        <v>6656998</v>
+        <v>6656821</v>
       </c>
       <c r="S246" t="n">
         <v>4</v>
@@ -32716,10 +32716,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B247" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R247" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,10 +32831,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B248" t="n">
-        <v>94713</v>
+        <v>94716</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R248" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236185</v>
+        <v>121236139</v>
       </c>
       <c r="B190" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,50 +26168,57 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537472</v>
+        <v>537547</v>
       </c>
       <c r="R190" t="n">
-        <v>6656651</v>
+        <v>6656935</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -26235,12 +26242,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,10 +26278,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236196</v>
+        <v>121236178</v>
       </c>
       <c r="B191" t="n">
-        <v>91057</v>
+        <v>57507</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,47 +26290,42 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2062</v>
+        <v>103021</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537490</v>
+        <v>537468</v>
       </c>
       <c r="R191" t="n">
-        <v>6656495</v>
+        <v>6656748</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -26386,7 +26388,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236171</v>
+        <v>121236164</v>
       </c>
       <c r="B192" t="n">
         <v>98098</v>
@@ -26435,13 +26437,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537516</v>
+        <v>537484</v>
       </c>
       <c r="R192" t="n">
-        <v>6656778</v>
+        <v>6656656</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,10 +26503,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236166</v>
+        <v>121236168</v>
       </c>
       <c r="B193" t="n">
-        <v>92022</v>
+        <v>79592</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26517,31 +26519,31 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -26550,10 +26552,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537531</v>
+        <v>537571</v>
       </c>
       <c r="R193" t="n">
-        <v>6657006</v>
+        <v>6656818</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -26616,10 +26618,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236159</v>
+        <v>121236138</v>
       </c>
       <c r="B194" t="n">
-        <v>91469</v>
+        <v>94599</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26628,35 +26630,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>366</v>
+        <v>2667</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26665,13 +26667,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537686</v>
+        <v>537620</v>
       </c>
       <c r="R194" t="n">
-        <v>6656739</v>
+        <v>6656858</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,10 +26733,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236154</v>
+        <v>121236195</v>
       </c>
       <c r="B195" t="n">
-        <v>94512</v>
+        <v>57354</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,25 +26745,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26769,24 +26771,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537724</v>
+        <v>537508</v>
       </c>
       <c r="R195" t="n">
-        <v>6656830</v>
+        <v>6656516</v>
       </c>
       <c r="S195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -26810,12 +26812,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26848,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236163</v>
+        <v>121236181</v>
       </c>
       <c r="B196" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,50 +26860,50 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537447</v>
+        <v>537438</v>
       </c>
       <c r="R196" t="n">
-        <v>6656508</v>
+        <v>6656699</v>
       </c>
       <c r="S196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26925,12 +26927,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26961,10 +26963,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236140</v>
+        <v>121236171</v>
       </c>
       <c r="B197" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,35 +26975,35 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -27010,13 +27012,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537634</v>
+        <v>537516</v>
       </c>
       <c r="R197" t="n">
-        <v>6657019</v>
+        <v>6656778</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27040,12 +27042,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27078,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236175</v>
+        <v>121236193</v>
       </c>
       <c r="B198" t="n">
-        <v>98098</v>
+        <v>92024</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27088,47 +27090,47 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537491</v>
+        <v>537518</v>
       </c>
       <c r="R198" t="n">
-        <v>6656738</v>
+        <v>6656512</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -27191,10 +27193,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236147</v>
+        <v>121236162</v>
       </c>
       <c r="B199" t="n">
-        <v>90713</v>
+        <v>91328</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27203,25 +27205,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -27240,13 +27242,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537705</v>
+        <v>537631</v>
       </c>
       <c r="R199" t="n">
-        <v>6656899</v>
+        <v>6656665</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27306,10 +27308,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236162</v>
+        <v>121236145</v>
       </c>
       <c r="B200" t="n">
-        <v>91328</v>
+        <v>94500</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27322,21 +27324,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1339</v>
+        <v>2809</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -27346,7 +27348,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -27355,10 +27357,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537631</v>
+        <v>537686</v>
       </c>
       <c r="R200" t="n">
-        <v>6656665</v>
+        <v>6656878</v>
       </c>
       <c r="S200" t="n">
         <v>4</v>
@@ -27421,7 +27423,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236164</v>
+        <v>121236176</v>
       </c>
       <c r="B201" t="n">
         <v>98098</v>
@@ -27456,7 +27458,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -27470,10 +27472,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537484</v>
+        <v>537462</v>
       </c>
       <c r="R201" t="n">
-        <v>6656656</v>
+        <v>6656736</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -27536,10 +27538,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236152</v>
+        <v>121236194</v>
       </c>
       <c r="B202" t="n">
-        <v>91328</v>
+        <v>90678</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27552,21 +27554,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27581,17 +27583,17 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537756</v>
+        <v>537520</v>
       </c>
       <c r="R202" t="n">
-        <v>6656968</v>
+        <v>6656530</v>
       </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27615,12 +27617,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27651,10 +27653,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236192</v>
+        <v>121236166</v>
       </c>
       <c r="B203" t="n">
-        <v>57354</v>
+        <v>92022</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27663,50 +27665,50 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537475</v>
+        <v>537531</v>
       </c>
       <c r="R203" t="n">
-        <v>6656526</v>
+        <v>6657006</v>
       </c>
       <c r="S203" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27766,10 +27768,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236181</v>
+        <v>121236155</v>
       </c>
       <c r="B204" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27778,35 +27780,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27815,13 +27817,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537438</v>
+        <v>537736</v>
       </c>
       <c r="R204" t="n">
-        <v>6656699</v>
+        <v>6656837</v>
       </c>
       <c r="S204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27845,12 +27847,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27881,10 +27883,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236167</v>
+        <v>121236142</v>
       </c>
       <c r="B205" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27893,35 +27895,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27930,13 +27932,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537517</v>
+        <v>537687</v>
       </c>
       <c r="R205" t="n">
-        <v>6656819</v>
+        <v>6656911</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27960,12 +27962,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -27996,10 +27998,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236172</v>
+        <v>121236197</v>
       </c>
       <c r="B206" t="n">
-        <v>98098</v>
+        <v>90999</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28008,50 +28010,50 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537513</v>
+        <v>537490</v>
       </c>
       <c r="R206" t="n">
-        <v>6656728</v>
+        <v>6656487</v>
       </c>
       <c r="S206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28111,10 +28113,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236197</v>
+        <v>121236154</v>
       </c>
       <c r="B207" t="n">
-        <v>90999</v>
+        <v>94512</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28123,25 +28125,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28151,22 +28153,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537490</v>
+        <v>537724</v>
       </c>
       <c r="R207" t="n">
-        <v>6656487</v>
+        <v>6656830</v>
       </c>
       <c r="S207" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -28190,12 +28192,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28226,10 +28228,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236142</v>
+        <v>121236192</v>
       </c>
       <c r="B208" t="n">
-        <v>90678</v>
+        <v>57354</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28238,25 +28240,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -28264,21 +28266,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537687</v>
+        <v>537475</v>
       </c>
       <c r="R208" t="n">
-        <v>6656911</v>
+        <v>6656526</v>
       </c>
       <c r="S208" t="n">
         <v>4</v>
@@ -28305,12 +28307,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -28341,10 +28343,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236182</v>
+        <v>121236167</v>
       </c>
       <c r="B209" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28353,35 +28355,35 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -28390,13 +28392,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537413</v>
+        <v>537517</v>
       </c>
       <c r="R209" t="n">
-        <v>6656645</v>
+        <v>6656819</v>
       </c>
       <c r="S209" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -28456,10 +28458,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236153</v>
+        <v>121236180</v>
       </c>
       <c r="B210" t="n">
-        <v>91469</v>
+        <v>98098</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28468,35 +28470,35 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -28505,10 +28507,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537763</v>
+        <v>537443</v>
       </c>
       <c r="R210" t="n">
-        <v>6656846</v>
+        <v>6656691</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -28535,12 +28537,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28571,10 +28573,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236160</v>
+        <v>121236147</v>
       </c>
       <c r="B211" t="n">
-        <v>94620</v>
+        <v>90713</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28583,35 +28585,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28620,13 +28622,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537624</v>
+        <v>537705</v>
       </c>
       <c r="R211" t="n">
-        <v>6656708</v>
+        <v>6656899</v>
       </c>
       <c r="S211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28801,10 +28803,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236178</v>
+        <v>121236186</v>
       </c>
       <c r="B213" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28813,30 +28815,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28845,13 +28852,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537468</v>
+        <v>537546</v>
       </c>
       <c r="R213" t="n">
-        <v>6656748</v>
+        <v>6656619</v>
       </c>
       <c r="S213" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28911,10 +28918,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236176</v>
+        <v>121236143</v>
       </c>
       <c r="B214" t="n">
-        <v>98098</v>
+        <v>91646</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28923,35 +28930,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -28960,10 +28967,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537462</v>
+        <v>537674</v>
       </c>
       <c r="R214" t="n">
-        <v>6656736</v>
+        <v>6656893</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -28990,12 +28997,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -29026,10 +29033,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236143</v>
+        <v>121236187</v>
       </c>
       <c r="B215" t="n">
-        <v>91646</v>
+        <v>98098</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29038,35 +29045,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29075,10 +29082,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537674</v>
+        <v>537559</v>
       </c>
       <c r="R215" t="n">
-        <v>6656893</v>
+        <v>6656606</v>
       </c>
       <c r="S215" t="n">
         <v>5</v>
@@ -29105,12 +29112,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29141,10 +29148,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236168</v>
+        <v>121236136</v>
       </c>
       <c r="B216" t="n">
-        <v>79592</v>
+        <v>90660</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29153,25 +29160,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6456</v>
+        <v>112</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -29190,13 +29197,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537571</v>
+        <v>537697</v>
       </c>
       <c r="R216" t="n">
-        <v>6656818</v>
+        <v>6656821</v>
       </c>
       <c r="S216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29220,12 +29227,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29256,10 +29263,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236187</v>
+        <v>121236151</v>
       </c>
       <c r="B217" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29268,50 +29275,50 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537559</v>
+        <v>537730</v>
       </c>
       <c r="R217" t="n">
-        <v>6656606</v>
+        <v>6656998</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29335,12 +29342,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29371,10 +29378,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236193</v>
+        <v>121236160</v>
       </c>
       <c r="B218" t="n">
-        <v>92024</v>
+        <v>94620</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29383,25 +29390,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5966</v>
+        <v>2818</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -29411,22 +29418,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537518</v>
+        <v>537624</v>
       </c>
       <c r="R218" t="n">
-        <v>6656512</v>
+        <v>6656708</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -29450,12 +29457,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29486,10 +29493,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236198</v>
+        <v>121236152</v>
       </c>
       <c r="B219" t="n">
-        <v>90713</v>
+        <v>91328</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,25 +29505,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29531,17 +29538,17 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537497</v>
+        <v>537756</v>
       </c>
       <c r="R219" t="n">
-        <v>6656496</v>
+        <v>6656968</v>
       </c>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29565,12 +29572,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29601,10 +29608,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236157</v>
+        <v>121236165</v>
       </c>
       <c r="B220" t="n">
-        <v>90763</v>
+        <v>8424</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29617,43 +29624,43 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5321</v>
+        <v>106554</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537695</v>
+        <v>537568</v>
       </c>
       <c r="R220" t="n">
-        <v>6656728</v>
+        <v>6657060</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29680,12 +29687,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29694,6 +29701,7 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
+      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -29716,10 +29724,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236194</v>
+        <v>121236175</v>
       </c>
       <c r="B221" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29728,47 +29736,47 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537520</v>
+        <v>537491</v>
       </c>
       <c r="R221" t="n">
-        <v>6656530</v>
+        <v>6656738</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29831,7 +29839,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236141</v>
+        <v>121236135</v>
       </c>
       <c r="B222" t="n">
         <v>98098</v>
@@ -29866,7 +29874,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29880,10 +29888,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537629</v>
+        <v>537439</v>
       </c>
       <c r="R222" t="n">
-        <v>6656969</v>
+        <v>6656570</v>
       </c>
       <c r="S222" t="n">
         <v>4</v>
@@ -29946,10 +29954,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236138</v>
+        <v>121236170</v>
       </c>
       <c r="B223" t="n">
-        <v>94599</v>
+        <v>98098</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29958,35 +29966,35 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -29995,13 +30003,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537620</v>
+        <v>537452</v>
       </c>
       <c r="R223" t="n">
-        <v>6656858</v>
+        <v>6656767</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30025,12 +30033,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30061,10 +30069,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236146</v>
+        <v>121236149</v>
       </c>
       <c r="B224" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30073,42 +30081,47 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537687</v>
+        <v>537712</v>
       </c>
       <c r="R224" t="n">
-        <v>6656879</v>
+        <v>6657066</v>
       </c>
       <c r="S224" t="n">
         <v>4</v>
@@ -30171,10 +30184,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236150</v>
+        <v>121236185</v>
       </c>
       <c r="B225" t="n">
-        <v>105203</v>
+        <v>98098</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30183,30 +30196,30 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -30216,17 +30229,17 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537738</v>
+        <v>537472</v>
       </c>
       <c r="R225" t="n">
-        <v>6657048</v>
+        <v>6656651</v>
       </c>
       <c r="S225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30250,12 +30263,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30286,10 +30299,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236155</v>
+        <v>121236146</v>
       </c>
       <c r="B226" t="n">
-        <v>90713</v>
+        <v>57507</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30302,31 +30315,26 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30335,10 +30343,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537736</v>
+        <v>537687</v>
       </c>
       <c r="R226" t="n">
-        <v>6656837</v>
+        <v>6656879</v>
       </c>
       <c r="S226" t="n">
         <v>4</v>
@@ -30401,10 +30409,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236145</v>
+        <v>121236189</v>
       </c>
       <c r="B227" t="n">
-        <v>94500</v>
+        <v>98098</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30413,35 +30421,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30450,13 +30458,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537686</v>
+        <v>537497</v>
       </c>
       <c r="R227" t="n">
-        <v>6656878</v>
+        <v>6656581</v>
       </c>
       <c r="S227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30480,12 +30488,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30516,10 +30524,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236144</v>
+        <v>121236137</v>
       </c>
       <c r="B228" t="n">
-        <v>57370</v>
+        <v>91328</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30528,25 +30536,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>1339</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -30554,9 +30562,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30565,13 +30573,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537672</v>
+        <v>537682</v>
       </c>
       <c r="R228" t="n">
-        <v>6656897</v>
+        <v>6656810</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30631,10 +30639,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236139</v>
+        <v>121236190</v>
       </c>
       <c r="B229" t="n">
-        <v>57370</v>
+        <v>90713</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30647,21 +30655,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -30669,31 +30677,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537547</v>
+        <v>537476</v>
       </c>
       <c r="R229" t="n">
-        <v>6656935</v>
+        <v>6656522</v>
       </c>
       <c r="S229" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30717,12 +30718,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30753,10 +30754,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236177</v>
+        <v>121236198</v>
       </c>
       <c r="B230" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30765,50 +30766,50 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537470</v>
+        <v>537497</v>
       </c>
       <c r="R230" t="n">
-        <v>6656705</v>
+        <v>6656496</v>
       </c>
       <c r="S230" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30868,10 +30869,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236190</v>
+        <v>121236153</v>
       </c>
       <c r="B231" t="n">
-        <v>90713</v>
+        <v>91469</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30884,21 +30885,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -30913,17 +30914,17 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537476</v>
+        <v>537763</v>
       </c>
       <c r="R231" t="n">
-        <v>6656522</v>
+        <v>6656846</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30947,12 +30948,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30983,10 +30984,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236188</v>
+        <v>121236196</v>
       </c>
       <c r="B232" t="n">
-        <v>57370</v>
+        <v>91057</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30995,25 +30996,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31021,31 +31022,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537594</v>
+        <v>537490</v>
       </c>
       <c r="R232" t="n">
-        <v>6656653</v>
+        <v>6656495</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31105,10 +31099,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236195</v>
+        <v>121236174</v>
       </c>
       <c r="B233" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31117,47 +31111,47 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537508</v>
+        <v>537502</v>
       </c>
       <c r="R233" t="n">
-        <v>6656516</v>
+        <v>6656738</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31220,10 +31214,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236165</v>
+        <v>121236141</v>
       </c>
       <c r="B234" t="n">
-        <v>8424</v>
+        <v>98098</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31232,50 +31226,50 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537568</v>
+        <v>537629</v>
       </c>
       <c r="R234" t="n">
-        <v>6657060</v>
+        <v>6656969</v>
       </c>
       <c r="S234" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31299,12 +31293,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -31313,7 +31307,6 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
-      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -31336,10 +31329,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236135</v>
+        <v>121236140</v>
       </c>
       <c r="B235" t="n">
-        <v>98098</v>
+        <v>90678</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31348,35 +31341,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -31385,13 +31378,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537439</v>
+        <v>537634</v>
       </c>
       <c r="R235" t="n">
-        <v>6656570</v>
+        <v>6657019</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31451,10 +31444,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236151</v>
+        <v>121236163</v>
       </c>
       <c r="B236" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31463,25 +31456,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -31496,14 +31489,14 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537730</v>
+        <v>537447</v>
       </c>
       <c r="R236" t="n">
-        <v>6656998</v>
+        <v>6656508</v>
       </c>
       <c r="S236" t="n">
         <v>4</v>
@@ -31566,10 +31559,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236169</v>
+        <v>121236159</v>
       </c>
       <c r="B237" t="n">
-        <v>98098</v>
+        <v>91469</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31578,35 +31571,35 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31615,10 +31608,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537474</v>
+        <v>537686</v>
       </c>
       <c r="R237" t="n">
-        <v>6656770</v>
+        <v>6656739</v>
       </c>
       <c r="S237" t="n">
         <v>4</v>
@@ -31645,12 +31638,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31681,7 +31674,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236149</v>
+        <v>121236177</v>
       </c>
       <c r="B238" t="n">
         <v>98098</v>
@@ -31726,14 +31719,14 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537712</v>
+        <v>537470</v>
       </c>
       <c r="R238" t="n">
-        <v>6657066</v>
+        <v>6656705</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31760,12 +31753,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31796,10 +31789,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236174</v>
+        <v>121236157</v>
       </c>
       <c r="B239" t="n">
-        <v>98098</v>
+        <v>90763</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31808,35 +31801,35 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -31845,10 +31838,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537502</v>
+        <v>537695</v>
       </c>
       <c r="R239" t="n">
-        <v>6656738</v>
+        <v>6656728</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -31875,12 +31868,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31911,10 +31904,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236180</v>
+        <v>121236188</v>
       </c>
       <c r="B240" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31923,47 +31916,54 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537443</v>
+        <v>537594</v>
       </c>
       <c r="R240" t="n">
-        <v>6656691</v>
+        <v>6656653</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -32026,10 +32026,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236189</v>
+        <v>121236144</v>
       </c>
       <c r="B241" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32038,35 +32038,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32075,10 +32075,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537497</v>
+        <v>537672</v>
       </c>
       <c r="R241" t="n">
-        <v>6656581</v>
+        <v>6656897</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32105,12 +32105,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32141,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236173</v>
+        <v>121236182</v>
       </c>
       <c r="B242" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32153,35 +32153,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32190,13 +32190,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537505</v>
+        <v>537413</v>
       </c>
       <c r="R242" t="n">
-        <v>6656739</v>
+        <v>6656645</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236170</v>
+        <v>121236150</v>
       </c>
       <c r="B243" t="n">
-        <v>98098</v>
+        <v>105203</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32268,30 +32268,30 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -32301,14 +32301,14 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537452</v>
+        <v>537738</v>
       </c>
       <c r="R243" t="n">
-        <v>6656767</v>
+        <v>6657048</v>
       </c>
       <c r="S243" t="n">
         <v>4</v>
@@ -32335,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,7 +32371,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236186</v>
+        <v>121236169</v>
       </c>
       <c r="B244" t="n">
         <v>98098</v>
@@ -32406,7 +32406,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537546</v>
+        <v>537474</v>
       </c>
       <c r="R244" t="n">
-        <v>6656619</v>
+        <v>6656770</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236137</v>
+        <v>121236173</v>
       </c>
       <c r="B245" t="n">
-        <v>91328</v>
+        <v>98098</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,35 +32498,35 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
@@ -32535,13 +32535,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537682</v>
+        <v>537505</v>
       </c>
       <c r="R245" t="n">
-        <v>6656810</v>
+        <v>6656739</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236136</v>
+        <v>121236172</v>
       </c>
       <c r="B246" t="n">
-        <v>90660</v>
+        <v>98098</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,35 +32613,35 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -32650,10 +32650,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537697</v>
+        <v>537513</v>
       </c>
       <c r="R246" t="n">
-        <v>6656821</v>
+        <v>6656728</v>
       </c>
       <c r="S246" t="n">
         <v>4</v>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -32716,7 +32716,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B247" t="n">
         <v>94716</v>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R247" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B248" t="n">
         <v>94716</v>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R248" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26503,10 +26503,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236168</v>
+        <v>121236181</v>
       </c>
       <c r="B193" t="n">
-        <v>79592</v>
+        <v>98098</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26515,35 +26515,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537571</v>
+        <v>537438</v>
       </c>
       <c r="R193" t="n">
-        <v>6656818</v>
+        <v>6656699</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26618,10 +26618,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236138</v>
+        <v>121236171</v>
       </c>
       <c r="B194" t="n">
-        <v>94599</v>
+        <v>98098</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26630,35 +26630,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26667,13 +26667,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537620</v>
+        <v>537516</v>
       </c>
       <c r="R194" t="n">
-        <v>6656858</v>
+        <v>6656778</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26697,12 +26697,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26733,10 +26733,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236195</v>
+        <v>121236168</v>
       </c>
       <c r="B195" t="n">
-        <v>57354</v>
+        <v>79592</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26745,25 +26745,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26771,21 +26771,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537508</v>
+        <v>537571</v>
       </c>
       <c r="R195" t="n">
-        <v>6656516</v>
+        <v>6656818</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -26848,10 +26848,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236181</v>
+        <v>121236138</v>
       </c>
       <c r="B196" t="n">
-        <v>98098</v>
+        <v>94599</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26860,35 +26860,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26897,13 +26897,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537438</v>
+        <v>537620</v>
       </c>
       <c r="R196" t="n">
-        <v>6656699</v>
+        <v>6656858</v>
       </c>
       <c r="S196" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26927,12 +26927,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26963,10 +26963,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236171</v>
+        <v>121236195</v>
       </c>
       <c r="B197" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26975,50 +26975,50 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537516</v>
+        <v>537508</v>
       </c>
       <c r="R197" t="n">
-        <v>6656778</v>
+        <v>6656516</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27538,10 +27538,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236194</v>
+        <v>121236155</v>
       </c>
       <c r="B202" t="n">
-        <v>90678</v>
+        <v>90713</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27550,25 +27550,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27583,17 +27583,17 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537520</v>
+        <v>537736</v>
       </c>
       <c r="R202" t="n">
-        <v>6656530</v>
+        <v>6656837</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27617,12 +27617,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27653,10 +27653,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236166</v>
+        <v>121236194</v>
       </c>
       <c r="B203" t="n">
-        <v>92022</v>
+        <v>90678</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27669,26 +27669,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27698,14 +27698,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537531</v>
+        <v>537520</v>
       </c>
       <c r="R203" t="n">
-        <v>6657006</v>
+        <v>6656530</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27768,10 +27768,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236155</v>
+        <v>121236166</v>
       </c>
       <c r="B204" t="n">
-        <v>90713</v>
+        <v>92022</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27780,30 +27780,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -27817,13 +27817,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537736</v>
+        <v>537531</v>
       </c>
       <c r="R204" t="n">
-        <v>6656837</v>
+        <v>6657006</v>
       </c>
       <c r="S204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27847,12 +27847,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD204" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26503,10 +26503,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236181</v>
+        <v>121236168</v>
       </c>
       <c r="B193" t="n">
-        <v>98098</v>
+        <v>79592</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26515,35 +26515,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -26552,13 +26552,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537438</v>
+        <v>537571</v>
       </c>
       <c r="R193" t="n">
-        <v>6656699</v>
+        <v>6656818</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26618,10 +26618,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236171</v>
+        <v>121236138</v>
       </c>
       <c r="B194" t="n">
-        <v>98098</v>
+        <v>94599</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26630,35 +26630,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>2667</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26667,13 +26667,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537516</v>
+        <v>537620</v>
       </c>
       <c r="R194" t="n">
-        <v>6656778</v>
+        <v>6656858</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26697,12 +26697,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26733,10 +26733,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236168</v>
+        <v>121236195</v>
       </c>
       <c r="B195" t="n">
-        <v>79592</v>
+        <v>57354</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26745,25 +26745,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26771,21 +26771,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537571</v>
+        <v>537508</v>
       </c>
       <c r="R195" t="n">
-        <v>6656818</v>
+        <v>6656516</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -26848,10 +26848,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236138</v>
+        <v>121236181</v>
       </c>
       <c r="B196" t="n">
-        <v>94599</v>
+        <v>98098</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26860,35 +26860,35 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26897,13 +26897,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537620</v>
+        <v>537438</v>
       </c>
       <c r="R196" t="n">
-        <v>6656858</v>
+        <v>6656699</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26927,12 +26927,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26963,10 +26963,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236195</v>
+        <v>121236171</v>
       </c>
       <c r="B197" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26975,50 +26975,50 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537508</v>
+        <v>537516</v>
       </c>
       <c r="R197" t="n">
-        <v>6656516</v>
+        <v>6656778</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27538,10 +27538,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236155</v>
+        <v>121236194</v>
       </c>
       <c r="B202" t="n">
-        <v>90713</v>
+        <v>90678</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27550,25 +27550,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27583,17 +27583,17 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537736</v>
+        <v>537520</v>
       </c>
       <c r="R202" t="n">
-        <v>6656837</v>
+        <v>6656530</v>
       </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27617,12 +27617,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27653,10 +27653,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236194</v>
+        <v>121236166</v>
       </c>
       <c r="B203" t="n">
-        <v>90678</v>
+        <v>92022</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27669,26 +27669,26 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27698,14 +27698,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537520</v>
+        <v>537531</v>
       </c>
       <c r="R203" t="n">
-        <v>6656530</v>
+        <v>6657006</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27768,10 +27768,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236166</v>
+        <v>121236155</v>
       </c>
       <c r="B204" t="n">
-        <v>92022</v>
+        <v>90713</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27780,30 +27780,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -27817,13 +27817,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537531</v>
+        <v>537736</v>
       </c>
       <c r="R204" t="n">
-        <v>6657006</v>
+        <v>6656837</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27847,12 +27847,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27998,10 +27998,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236197</v>
+        <v>121236154</v>
       </c>
       <c r="B206" t="n">
-        <v>90999</v>
+        <v>94512</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28010,25 +28010,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>658</v>
+        <v>2813</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -28038,22 +28038,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537490</v>
+        <v>537724</v>
       </c>
       <c r="R206" t="n">
-        <v>6656487</v>
+        <v>6656830</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28077,12 +28077,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28113,10 +28113,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236154</v>
+        <v>121236192</v>
       </c>
       <c r="B207" t="n">
-        <v>94512</v>
+        <v>57354</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28125,25 +28125,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2813</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28151,21 +28151,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>m²</t>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537724</v>
+        <v>537475</v>
       </c>
       <c r="R207" t="n">
-        <v>6656830</v>
+        <v>6656526</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28192,12 +28192,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28228,10 +28228,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236192</v>
+        <v>121236167</v>
       </c>
       <c r="B208" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28240,50 +28240,50 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537475</v>
+        <v>537517</v>
       </c>
       <c r="R208" t="n">
-        <v>6656526</v>
+        <v>6656819</v>
       </c>
       <c r="S208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236167</v>
+        <v>121236180</v>
       </c>
       <c r="B209" t="n">
         <v>98098</v>
@@ -28378,7 +28378,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -28392,10 +28392,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537517</v>
+        <v>537443</v>
       </c>
       <c r="R209" t="n">
-        <v>6656819</v>
+        <v>6656691</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28458,10 +28458,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236180</v>
+        <v>121236197</v>
       </c>
       <c r="B210" t="n">
-        <v>98098</v>
+        <v>90999</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28470,47 +28470,47 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537443</v>
+        <v>537490</v>
       </c>
       <c r="R210" t="n">
-        <v>6656691</v>
+        <v>6656487</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -30299,10 +30299,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236146</v>
+        <v>121236137</v>
       </c>
       <c r="B226" t="n">
-        <v>57507</v>
+        <v>91328</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30311,30 +30311,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30343,10 +30348,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537687</v>
+        <v>537682</v>
       </c>
       <c r="R226" t="n">
-        <v>6656879</v>
+        <v>6656810</v>
       </c>
       <c r="S226" t="n">
         <v>4</v>
@@ -30409,10 +30414,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236189</v>
+        <v>121236146</v>
       </c>
       <c r="B227" t="n">
-        <v>98098</v>
+        <v>57507</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30421,35 +30426,30 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30458,13 +30458,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537497</v>
+        <v>537687</v>
       </c>
       <c r="R227" t="n">
-        <v>6656581</v>
+        <v>6656879</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30488,12 +30488,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30524,10 +30524,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236137</v>
+        <v>121236189</v>
       </c>
       <c r="B228" t="n">
-        <v>91328</v>
+        <v>98098</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30536,35 +30536,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30573,13 +30573,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537682</v>
+        <v>537497</v>
       </c>
       <c r="R228" t="n">
-        <v>6656810</v>
+        <v>6656581</v>
       </c>
       <c r="S228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30603,12 +30603,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -31329,10 +31329,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236140</v>
+        <v>121236177</v>
       </c>
       <c r="B235" t="n">
-        <v>90678</v>
+        <v>98098</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31341,35 +31341,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -31378,13 +31378,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537634</v>
+        <v>537470</v>
       </c>
       <c r="R235" t="n">
-        <v>6657019</v>
+        <v>6656705</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31408,12 +31408,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31444,7 +31444,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236163</v>
+        <v>121236140</v>
       </c>
       <c r="B236" t="n">
         <v>90678</v>
@@ -31489,17 +31489,17 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537447</v>
+        <v>537634</v>
       </c>
       <c r="R236" t="n">
-        <v>6656508</v>
+        <v>6657019</v>
       </c>
       <c r="S236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31559,10 +31559,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236159</v>
+        <v>121236163</v>
       </c>
       <c r="B237" t="n">
-        <v>91469</v>
+        <v>90678</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31571,25 +31571,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>366</v>
+        <v>5447</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -31604,14 +31604,14 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537686</v>
+        <v>537447</v>
       </c>
       <c r="R237" t="n">
-        <v>6656739</v>
+        <v>6656508</v>
       </c>
       <c r="S237" t="n">
         <v>4</v>
@@ -31674,10 +31674,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236177</v>
+        <v>121236159</v>
       </c>
       <c r="B238" t="n">
-        <v>98098</v>
+        <v>91469</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31686,35 +31686,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31723,10 +31723,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537470</v>
+        <v>537686</v>
       </c>
       <c r="R238" t="n">
-        <v>6656705</v>
+        <v>6656739</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31753,12 +31753,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD238" t="b">

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90259</v>
+        <v>90265</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90259</v>
+        <v>90265</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236139</v>
+        <v>121236157</v>
       </c>
       <c r="B190" t="n">
-        <v>57370</v>
+        <v>90769</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,25 +26168,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -26194,31 +26194,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537547</v>
+        <v>537695</v>
       </c>
       <c r="R190" t="n">
-        <v>6656935</v>
+        <v>6656728</v>
       </c>
       <c r="S190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -26278,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236178</v>
+        <v>121236151</v>
       </c>
       <c r="B191" t="n">
-        <v>57507</v>
+        <v>90719</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26294,38 +26287,43 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537468</v>
+        <v>537730</v>
       </c>
       <c r="R191" t="n">
-        <v>6656748</v>
+        <v>6656998</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -26352,12 +26350,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -26388,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236164</v>
+        <v>121236198</v>
       </c>
       <c r="B192" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26400,50 +26398,50 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537484</v>
+        <v>537497</v>
       </c>
       <c r="R192" t="n">
-        <v>6656656</v>
+        <v>6656496</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26506,7 +26504,7 @@
         <v>121236168</v>
       </c>
       <c r="B193" t="n">
-        <v>79592</v>
+        <v>79593</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26618,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236138</v>
+        <v>121236162</v>
       </c>
       <c r="B194" t="n">
-        <v>94599</v>
+        <v>91334</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26634,31 +26632,31 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2667</v>
+        <v>1339</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26667,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537620</v>
+        <v>537631</v>
       </c>
       <c r="R194" t="n">
-        <v>6656858</v>
+        <v>6656665</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26733,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236195</v>
+        <v>121236144</v>
       </c>
       <c r="B195" t="n">
-        <v>57354</v>
+        <v>57371</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26749,16 +26747,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -26773,19 +26771,19 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537508</v>
+        <v>537672</v>
       </c>
       <c r="R195" t="n">
-        <v>6656516</v>
+        <v>6656897</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -26812,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26848,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236181</v>
+        <v>121236164</v>
       </c>
       <c r="B196" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26883,7 +26881,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -26897,13 +26895,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537438</v>
+        <v>537484</v>
       </c>
       <c r="R196" t="n">
-        <v>6656699</v>
+        <v>6656656</v>
       </c>
       <c r="S196" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -26963,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236171</v>
+        <v>121236170</v>
       </c>
       <c r="B197" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26998,7 +26996,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -27012,10 +27010,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537516</v>
+        <v>537452</v>
       </c>
       <c r="R197" t="n">
-        <v>6656778</v>
+        <v>6656767</v>
       </c>
       <c r="S197" t="n">
         <v>4</v>
@@ -27078,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236193</v>
+        <v>121236150</v>
       </c>
       <c r="B198" t="n">
-        <v>92024</v>
+        <v>105209</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27090,50 +27088,50 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5966</v>
+        <v>221144</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537518</v>
+        <v>537738</v>
       </c>
       <c r="R198" t="n">
-        <v>6656512</v>
+        <v>6657048</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27157,12 +27155,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27193,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236162</v>
+        <v>121236154</v>
       </c>
       <c r="B199" t="n">
-        <v>91328</v>
+        <v>94518</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27209,21 +27207,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1339</v>
+        <v>2813</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -27233,7 +27231,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -27242,10 +27240,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537631</v>
+        <v>537724</v>
       </c>
       <c r="R199" t="n">
-        <v>6656665</v>
+        <v>6656830</v>
       </c>
       <c r="S199" t="n">
         <v>4</v>
@@ -27308,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236145</v>
+        <v>121236146</v>
       </c>
       <c r="B200" t="n">
-        <v>94500</v>
+        <v>57508</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27320,35 +27318,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -27357,10 +27350,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537686</v>
+        <v>537687</v>
       </c>
       <c r="R200" t="n">
-        <v>6656878</v>
+        <v>6656879</v>
       </c>
       <c r="S200" t="n">
         <v>4</v>
@@ -27423,10 +27416,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236176</v>
+        <v>121236192</v>
       </c>
       <c r="B201" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27435,50 +27428,50 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537462</v>
+        <v>537475</v>
       </c>
       <c r="R201" t="n">
-        <v>6656736</v>
+        <v>6656526</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27538,10 +27531,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236194</v>
+        <v>121236181</v>
       </c>
       <c r="B202" t="n">
-        <v>90678</v>
+        <v>98104</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27550,50 +27543,50 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537520</v>
+        <v>537438</v>
       </c>
       <c r="R202" t="n">
-        <v>6656530</v>
+        <v>6656699</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27653,10 +27646,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236166</v>
+        <v>121236173</v>
       </c>
       <c r="B203" t="n">
-        <v>92022</v>
+        <v>98104</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27665,35 +27658,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27702,10 +27695,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537531</v>
+        <v>537505</v>
       </c>
       <c r="R203" t="n">
-        <v>6657006</v>
+        <v>6656739</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27768,10 +27761,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236155</v>
+        <v>121236176</v>
       </c>
       <c r="B204" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27780,35 +27773,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27817,13 +27810,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537736</v>
+        <v>537462</v>
       </c>
       <c r="R204" t="n">
-        <v>6656837</v>
+        <v>6656736</v>
       </c>
       <c r="S204" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27847,12 +27840,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27883,10 +27876,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236142</v>
+        <v>121236153</v>
       </c>
       <c r="B205" t="n">
-        <v>90678</v>
+        <v>91475</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27895,25 +27888,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5447</v>
+        <v>366</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -27932,13 +27925,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537687</v>
+        <v>537763</v>
       </c>
       <c r="R205" t="n">
-        <v>6656911</v>
+        <v>6656846</v>
       </c>
       <c r="S205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27998,10 +27991,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236154</v>
+        <v>121236196</v>
       </c>
       <c r="B206" t="n">
-        <v>94512</v>
+        <v>91063</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28010,25 +28003,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2813</v>
+        <v>2062</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -28038,19 +28031,19 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537724</v>
+        <v>537490</v>
       </c>
       <c r="R206" t="n">
-        <v>6656830</v>
+        <v>6656495</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -28077,12 +28070,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28113,10 +28106,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236192</v>
+        <v>121236152</v>
       </c>
       <c r="B207" t="n">
-        <v>57354</v>
+        <v>91334</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28125,25 +28118,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>1339</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28151,21 +28144,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537475</v>
+        <v>537756</v>
       </c>
       <c r="R207" t="n">
-        <v>6656526</v>
+        <v>6656968</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28192,12 +28185,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28228,10 +28221,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236167</v>
+        <v>121236145</v>
       </c>
       <c r="B208" t="n">
-        <v>98098</v>
+        <v>94506</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28240,35 +28233,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -28277,13 +28270,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537517</v>
+        <v>537686</v>
       </c>
       <c r="R208" t="n">
-        <v>6656819</v>
+        <v>6656878</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28307,12 +28300,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -28343,10 +28336,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236180</v>
+        <v>121236167</v>
       </c>
       <c r="B209" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28378,7 +28371,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -28392,10 +28385,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537443</v>
+        <v>537517</v>
       </c>
       <c r="R209" t="n">
-        <v>6656691</v>
+        <v>6656819</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28458,10 +28451,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236197</v>
+        <v>121236172</v>
       </c>
       <c r="B210" t="n">
-        <v>90999</v>
+        <v>98104</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28470,50 +28463,50 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537490</v>
+        <v>537513</v>
       </c>
       <c r="R210" t="n">
-        <v>6656487</v>
+        <v>6656728</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28573,10 +28566,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236147</v>
+        <v>121236185</v>
       </c>
       <c r="B211" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28585,35 +28578,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28622,10 +28615,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537705</v>
+        <v>537472</v>
       </c>
       <c r="R211" t="n">
-        <v>6656899</v>
+        <v>6656651</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -28652,12 +28645,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28688,10 +28681,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236184</v>
+        <v>121236190</v>
       </c>
       <c r="B212" t="n">
-        <v>91981</v>
+        <v>90719</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28704,26 +28697,26 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -28733,17 +28726,17 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537431</v>
+        <v>537476</v>
       </c>
       <c r="R212" t="n">
-        <v>6656597</v>
+        <v>6656522</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28803,10 +28796,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236186</v>
+        <v>121236155</v>
       </c>
       <c r="B213" t="n">
-        <v>98098</v>
+        <v>90719</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28815,35 +28808,35 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28852,13 +28845,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537546</v>
+        <v>537736</v>
       </c>
       <c r="R213" t="n">
-        <v>6656619</v>
+        <v>6656837</v>
       </c>
       <c r="S213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28882,12 +28875,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28918,10 +28911,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236143</v>
+        <v>121236147</v>
       </c>
       <c r="B214" t="n">
-        <v>91646</v>
+        <v>90719</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28930,25 +28923,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28967,10 +28960,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537674</v>
+        <v>537705</v>
       </c>
       <c r="R214" t="n">
-        <v>6656893</v>
+        <v>6656899</v>
       </c>
       <c r="S214" t="n">
         <v>5</v>
@@ -29033,10 +29026,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236187</v>
+        <v>121236149</v>
       </c>
       <c r="B215" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29068,7 +29061,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -29078,17 +29071,17 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537559</v>
+        <v>537712</v>
       </c>
       <c r="R215" t="n">
-        <v>6656606</v>
+        <v>6657066</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29112,12 +29105,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29148,10 +29141,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236136</v>
+        <v>121236184</v>
       </c>
       <c r="B216" t="n">
-        <v>90660</v>
+        <v>91987</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29164,31 +29157,31 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>112</v>
+        <v>4361</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29197,13 +29190,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537697</v>
+        <v>537431</v>
       </c>
       <c r="R216" t="n">
-        <v>6656821</v>
+        <v>6656597</v>
       </c>
       <c r="S216" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29227,12 +29220,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29263,10 +29256,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236151</v>
+        <v>121236163</v>
       </c>
       <c r="B217" t="n">
-        <v>90713</v>
+        <v>90684</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29275,25 +29268,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -29308,14 +29301,14 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537730</v>
+        <v>537447</v>
       </c>
       <c r="R217" t="n">
-        <v>6656998</v>
+        <v>6656508</v>
       </c>
       <c r="S217" t="n">
         <v>4</v>
@@ -29381,7 +29374,7 @@
         <v>121236160</v>
       </c>
       <c r="B218" t="n">
-        <v>94620</v>
+        <v>94626</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29493,10 +29486,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236152</v>
+        <v>121236142</v>
       </c>
       <c r="B219" t="n">
-        <v>91328</v>
+        <v>90684</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29509,21 +29502,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29538,14 +29531,14 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537756</v>
+        <v>537687</v>
       </c>
       <c r="R219" t="n">
-        <v>6656968</v>
+        <v>6656911</v>
       </c>
       <c r="S219" t="n">
         <v>4</v>
@@ -29608,10 +29601,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236165</v>
+        <v>121236138</v>
       </c>
       <c r="B220" t="n">
-        <v>8424</v>
+        <v>94605</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29624,43 +29617,43 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>106554</v>
+        <v>2667</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
-      <c r="K220" t="inlineStr"/>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N220" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537568</v>
+        <v>537620</v>
       </c>
       <c r="R220" t="n">
-        <v>6657060</v>
+        <v>6656858</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29687,12 +29680,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29701,7 +29694,6 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
@@ -29724,10 +29716,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236175</v>
+        <v>121236139</v>
       </c>
       <c r="B221" t="n">
-        <v>98098</v>
+        <v>57371</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29736,50 +29728,57 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537491</v>
+        <v>537547</v>
       </c>
       <c r="R221" t="n">
-        <v>6656738</v>
+        <v>6656935</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29803,12 +29802,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29839,10 +29838,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236135</v>
+        <v>121236197</v>
       </c>
       <c r="B222" t="n">
-        <v>98098</v>
+        <v>91005</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29851,50 +29850,50 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537439</v>
+        <v>537490</v>
       </c>
       <c r="R222" t="n">
-        <v>6656570</v>
+        <v>6656487</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29918,12 +29917,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29954,10 +29953,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236170</v>
+        <v>121236193</v>
       </c>
       <c r="B223" t="n">
-        <v>98098</v>
+        <v>92030</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29966,50 +29965,50 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537452</v>
+        <v>537518</v>
       </c>
       <c r="R223" t="n">
-        <v>6656767</v>
+        <v>6656512</v>
       </c>
       <c r="S223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30069,10 +30068,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236149</v>
+        <v>121236187</v>
       </c>
       <c r="B224" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30104,7 +30103,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -30114,17 +30113,17 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537712</v>
+        <v>537559</v>
       </c>
       <c r="R224" t="n">
-        <v>6657066</v>
+        <v>6656606</v>
       </c>
       <c r="S224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30148,12 +30147,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30184,10 +30183,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236185</v>
+        <v>121236180</v>
       </c>
       <c r="B225" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30219,7 +30218,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -30233,10 +30232,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537472</v>
+        <v>537443</v>
       </c>
       <c r="R225" t="n">
-        <v>6656651</v>
+        <v>6656691</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -30299,10 +30298,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236137</v>
+        <v>121236159</v>
       </c>
       <c r="B226" t="n">
-        <v>91328</v>
+        <v>91475</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30311,25 +30310,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>1339</v>
+        <v>366</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -30348,10 +30347,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537682</v>
+        <v>537686</v>
       </c>
       <c r="R226" t="n">
-        <v>6656810</v>
+        <v>6656739</v>
       </c>
       <c r="S226" t="n">
         <v>4</v>
@@ -30414,10 +30413,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236146</v>
+        <v>121236177</v>
       </c>
       <c r="B227" t="n">
-        <v>57507</v>
+        <v>98104</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30426,30 +30425,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30458,10 +30462,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537687</v>
+        <v>537470</v>
       </c>
       <c r="R227" t="n">
-        <v>6656879</v>
+        <v>6656705</v>
       </c>
       <c r="S227" t="n">
         <v>4</v>
@@ -30488,12 +30492,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30524,10 +30528,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236189</v>
+        <v>121236171</v>
       </c>
       <c r="B228" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30573,13 +30577,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537497</v>
+        <v>537516</v>
       </c>
       <c r="R228" t="n">
-        <v>6656581</v>
+        <v>6656778</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30639,10 +30643,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236190</v>
+        <v>121236141</v>
       </c>
       <c r="B229" t="n">
-        <v>90713</v>
+        <v>98104</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30651,50 +30655,50 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537476</v>
+        <v>537629</v>
       </c>
       <c r="R229" t="n">
-        <v>6656522</v>
+        <v>6656969</v>
       </c>
       <c r="S229" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30718,12 +30722,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30754,10 +30758,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236198</v>
+        <v>121236166</v>
       </c>
       <c r="B230" t="n">
-        <v>90713</v>
+        <v>92028</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30766,30 +30770,30 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -30799,17 +30803,17 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537497</v>
+        <v>537531</v>
       </c>
       <c r="R230" t="n">
-        <v>6656496</v>
+        <v>6657006</v>
       </c>
       <c r="S230" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30869,10 +30873,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236153</v>
+        <v>121236135</v>
       </c>
       <c r="B231" t="n">
-        <v>91469</v>
+        <v>98104</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30881,35 +30885,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -30918,13 +30922,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537763</v>
+        <v>537439</v>
       </c>
       <c r="R231" t="n">
-        <v>6656846</v>
+        <v>6656570</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30984,10 +30988,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236196</v>
+        <v>121236182</v>
       </c>
       <c r="B232" t="n">
-        <v>91057</v>
+        <v>90719</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30996,25 +31000,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31029,17 +31033,17 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537490</v>
+        <v>537413</v>
       </c>
       <c r="R232" t="n">
-        <v>6656495</v>
+        <v>6656645</v>
       </c>
       <c r="S232" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31099,10 +31103,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236174</v>
+        <v>121236195</v>
       </c>
       <c r="B233" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31111,47 +31115,47 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J233" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537502</v>
+        <v>537508</v>
       </c>
       <c r="R233" t="n">
-        <v>6656738</v>
+        <v>6656516</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31214,10 +31218,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236141</v>
+        <v>121236137</v>
       </c>
       <c r="B234" t="n">
-        <v>98098</v>
+        <v>91334</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31226,35 +31230,35 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -31263,10 +31267,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537629</v>
+        <v>537682</v>
       </c>
       <c r="R234" t="n">
-        <v>6656969</v>
+        <v>6656810</v>
       </c>
       <c r="S234" t="n">
         <v>4</v>
@@ -31329,10 +31333,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236177</v>
+        <v>121236175</v>
       </c>
       <c r="B235" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31364,7 +31368,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -31378,13 +31382,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537470</v>
+        <v>537491</v>
       </c>
       <c r="R235" t="n">
-        <v>6656705</v>
+        <v>6656738</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31444,10 +31448,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236140</v>
+        <v>121236136</v>
       </c>
       <c r="B236" t="n">
-        <v>90678</v>
+        <v>90666</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31456,25 +31460,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -31484,7 +31488,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -31493,13 +31497,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537634</v>
+        <v>537697</v>
       </c>
       <c r="R236" t="n">
-        <v>6657019</v>
+        <v>6656821</v>
       </c>
       <c r="S236" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31559,10 +31563,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236163</v>
+        <v>121236143</v>
       </c>
       <c r="B237" t="n">
-        <v>90678</v>
+        <v>91652</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31575,21 +31579,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -31604,17 +31608,17 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537447</v>
+        <v>537674</v>
       </c>
       <c r="R237" t="n">
-        <v>6656508</v>
+        <v>6656893</v>
       </c>
       <c r="S237" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31674,10 +31678,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236159</v>
+        <v>121236186</v>
       </c>
       <c r="B238" t="n">
-        <v>91469</v>
+        <v>98104</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31686,35 +31690,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31723,13 +31727,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537686</v>
+        <v>537546</v>
       </c>
       <c r="R238" t="n">
-        <v>6656739</v>
+        <v>6656619</v>
       </c>
       <c r="S238" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -31753,12 +31757,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31789,10 +31793,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236157</v>
+        <v>121236188</v>
       </c>
       <c r="B239" t="n">
-        <v>90763</v>
+        <v>57371</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31801,25 +31805,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5321</v>
+        <v>100049</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -31827,21 +31831,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537695</v>
+        <v>537594</v>
       </c>
       <c r="R239" t="n">
-        <v>6656728</v>
+        <v>6656653</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -31868,12 +31879,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31904,10 +31915,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236188</v>
+        <v>121236140</v>
       </c>
       <c r="B240" t="n">
-        <v>57370</v>
+        <v>90684</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31916,25 +31927,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -31942,28 +31953,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537594</v>
+        <v>537634</v>
       </c>
       <c r="R240" t="n">
-        <v>6656653</v>
+        <v>6657019</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -31990,12 +31994,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32026,10 +32030,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236144</v>
+        <v>121236165</v>
       </c>
       <c r="B241" t="n">
-        <v>57370</v>
+        <v>8424</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32038,47 +32042,47 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537672</v>
+        <v>537568</v>
       </c>
       <c r="R241" t="n">
-        <v>6656897</v>
+        <v>6657060</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32105,12 +32109,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32119,6 +32123,7 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
+      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
@@ -32141,10 +32146,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236182</v>
+        <v>121236178</v>
       </c>
       <c r="B242" t="n">
-        <v>90713</v>
+        <v>57508</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32157,31 +32162,26 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32190,13 +32190,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537413</v>
+        <v>537468</v>
       </c>
       <c r="R242" t="n">
-        <v>6656645</v>
+        <v>6656748</v>
       </c>
       <c r="S242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236150</v>
+        <v>121236174</v>
       </c>
       <c r="B243" t="n">
-        <v>105203</v>
+        <v>98104</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32268,30 +32268,30 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -32301,17 +32301,17 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537738</v>
+        <v>537502</v>
       </c>
       <c r="R243" t="n">
-        <v>6657048</v>
+        <v>6656738</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32335,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236169</v>
+        <v>121236194</v>
       </c>
       <c r="B244" t="n">
-        <v>98098</v>
+        <v>90684</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,50 +32383,50 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537474</v>
+        <v>537520</v>
       </c>
       <c r="R244" t="n">
-        <v>6656770</v>
+        <v>6656530</v>
       </c>
       <c r="S244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236173</v>
+        <v>121236169</v>
       </c>
       <c r="B245" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -32535,13 +32535,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537505</v>
+        <v>537474</v>
       </c>
       <c r="R245" t="n">
-        <v>6656739</v>
+        <v>6656770</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236172</v>
+        <v>121236189</v>
       </c>
       <c r="B246" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -32650,13 +32650,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537513</v>
+        <v>537497</v>
       </c>
       <c r="R246" t="n">
-        <v>6656728</v>
+        <v>6656581</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32716,10 +32716,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B247" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R247" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,10 +32831,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B248" t="n">
-        <v>94716</v>
+        <v>94722</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R248" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -29486,10 +29486,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236142</v>
+        <v>121236139</v>
       </c>
       <c r="B219" t="n">
-        <v>90684</v>
+        <v>57371</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,25 +29498,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29524,21 +29524,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537687</v>
+        <v>537547</v>
       </c>
       <c r="R219" t="n">
-        <v>6656911</v>
+        <v>6656935</v>
       </c>
       <c r="S219" t="n">
         <v>4</v>
@@ -29601,10 +29608,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236138</v>
+        <v>121236142</v>
       </c>
       <c r="B220" t="n">
-        <v>94605</v>
+        <v>90684</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29617,31 +29624,31 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2667</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29650,13 +29657,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537620</v>
+        <v>537687</v>
       </c>
       <c r="R220" t="n">
-        <v>6656858</v>
+        <v>6656911</v>
       </c>
       <c r="S220" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29716,10 +29723,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236139</v>
+        <v>121236138</v>
       </c>
       <c r="B221" t="n">
-        <v>57371</v>
+        <v>94605</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29728,57 +29735,50 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>2667</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537547</v>
+        <v>537620</v>
       </c>
       <c r="R221" t="n">
-        <v>6656935</v>
+        <v>6656858</v>
       </c>
       <c r="S221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29838,10 +29838,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236197</v>
+        <v>121236187</v>
       </c>
       <c r="B222" t="n">
-        <v>91005</v>
+        <v>98104</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29850,47 +29850,47 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537490</v>
+        <v>537559</v>
       </c>
       <c r="R222" t="n">
-        <v>6656487</v>
+        <v>6656606</v>
       </c>
       <c r="S222" t="n">
         <v>5</v>
@@ -29953,10 +29953,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236193</v>
+        <v>121236180</v>
       </c>
       <c r="B223" t="n">
-        <v>92030</v>
+        <v>98104</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29965,47 +29965,47 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537518</v>
+        <v>537443</v>
       </c>
       <c r="R223" t="n">
-        <v>6656512</v>
+        <v>6656691</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -30068,10 +30068,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236187</v>
+        <v>121236197</v>
       </c>
       <c r="B224" t="n">
-        <v>98104</v>
+        <v>91005</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30080,47 +30080,47 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537559</v>
+        <v>537490</v>
       </c>
       <c r="R224" t="n">
-        <v>6656606</v>
+        <v>6656487</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -30183,10 +30183,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236180</v>
+        <v>121236193</v>
       </c>
       <c r="B225" t="n">
-        <v>98104</v>
+        <v>92030</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30195,47 +30195,47 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537443</v>
+        <v>537518</v>
       </c>
       <c r="R225" t="n">
-        <v>6656691</v>
+        <v>6656512</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -16105,7 +16105,7 @@
         <v>95605602</v>
       </c>
       <c r="B117" t="n">
-        <v>90265</v>
+        <v>90266</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -20293,7 +20293,7 @@
         <v>1660907</v>
       </c>
       <c r="B147" t="n">
-        <v>90265</v>
+        <v>90266</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236157</v>
+        <v>121236180</v>
       </c>
       <c r="B190" t="n">
-        <v>90769</v>
+        <v>98105</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,35 +26168,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5321</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -26205,10 +26205,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537695</v>
+        <v>537443</v>
       </c>
       <c r="R190" t="n">
-        <v>6656728</v>
+        <v>6656691</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26235,12 +26235,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236151</v>
+        <v>121236155</v>
       </c>
       <c r="B191" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26316,14 +26316,14 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537730</v>
+        <v>537736</v>
       </c>
       <c r="R191" t="n">
-        <v>6656998</v>
+        <v>6656837</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236198</v>
+        <v>121236170</v>
       </c>
       <c r="B192" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,50 +26398,50 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537497</v>
+        <v>537452</v>
       </c>
       <c r="R192" t="n">
-        <v>6656496</v>
+        <v>6656767</v>
       </c>
       <c r="S192" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236168</v>
+        <v>121236187</v>
       </c>
       <c r="B193" t="n">
-        <v>79593</v>
+        <v>98105</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,35 +26513,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -26550,10 +26550,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537571</v>
+        <v>537559</v>
       </c>
       <c r="R193" t="n">
-        <v>6656818</v>
+        <v>6656606</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -26616,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236162</v>
+        <v>121236140</v>
       </c>
       <c r="B194" t="n">
-        <v>91334</v>
+        <v>90685</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26632,21 +26632,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537631</v>
+        <v>537634</v>
       </c>
       <c r="R194" t="n">
-        <v>6656665</v>
+        <v>6657019</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236144</v>
+        <v>121236195</v>
       </c>
       <c r="B195" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26747,16 +26747,16 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -26771,19 +26771,19 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537672</v>
+        <v>537508</v>
       </c>
       <c r="R195" t="n">
-        <v>6656897</v>
+        <v>6656516</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -26810,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236164</v>
+        <v>121236193</v>
       </c>
       <c r="B196" t="n">
-        <v>98104</v>
+        <v>92031</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,47 +26858,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537484</v>
+        <v>537518</v>
       </c>
       <c r="R196" t="n">
-        <v>6656656</v>
+        <v>6656512</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236170</v>
+        <v>121236149</v>
       </c>
       <c r="B197" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -27006,14 +27006,14 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537452</v>
+        <v>537712</v>
       </c>
       <c r="R197" t="n">
-        <v>6656767</v>
+        <v>6657066</v>
       </c>
       <c r="S197" t="n">
         <v>4</v>
@@ -27040,12 +27040,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236150</v>
+        <v>121236166</v>
       </c>
       <c r="B198" t="n">
-        <v>105209</v>
+        <v>92029</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27092,46 +27092,46 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221144</v>
+        <v>5964</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537738</v>
+        <v>537531</v>
       </c>
       <c r="R198" t="n">
-        <v>6657048</v>
+        <v>6657006</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27155,12 +27155,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27191,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236154</v>
+        <v>121236173</v>
       </c>
       <c r="B199" t="n">
-        <v>94518</v>
+        <v>98105</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27203,35 +27203,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -27240,13 +27240,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537724</v>
+        <v>537505</v>
       </c>
       <c r="R199" t="n">
-        <v>6656830</v>
+        <v>6656739</v>
       </c>
       <c r="S199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27270,12 +27270,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -27306,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236146</v>
+        <v>121236176</v>
       </c>
       <c r="B200" t="n">
-        <v>57508</v>
+        <v>98105</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27318,30 +27318,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -27350,13 +27355,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537687</v>
+        <v>537462</v>
       </c>
       <c r="R200" t="n">
-        <v>6656879</v>
+        <v>6656736</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27380,12 +27385,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27416,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236192</v>
+        <v>121236185</v>
       </c>
       <c r="B201" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27428,50 +27433,50 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537475</v>
+        <v>537472</v>
       </c>
       <c r="R201" t="n">
-        <v>6656526</v>
+        <v>6656651</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27531,10 +27536,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236181</v>
+        <v>121236171</v>
       </c>
       <c r="B202" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27566,7 +27571,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -27580,13 +27585,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537438</v>
+        <v>537516</v>
       </c>
       <c r="R202" t="n">
-        <v>6656699</v>
+        <v>6656778</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27646,10 +27651,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236173</v>
+        <v>121236174</v>
       </c>
       <c r="B203" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27681,7 +27686,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -27695,10 +27700,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537505</v>
+        <v>537502</v>
       </c>
       <c r="R203" t="n">
-        <v>6656739</v>
+        <v>6656738</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -27761,10 +27766,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236176</v>
+        <v>121236186</v>
       </c>
       <c r="B204" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27810,10 +27815,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537462</v>
+        <v>537546</v>
       </c>
       <c r="R204" t="n">
-        <v>6656736</v>
+        <v>6656619</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -27879,7 +27884,7 @@
         <v>121236153</v>
       </c>
       <c r="B205" t="n">
-        <v>91475</v>
+        <v>91476</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27991,10 +27996,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236196</v>
+        <v>121236177</v>
       </c>
       <c r="B206" t="n">
-        <v>91063</v>
+        <v>98105</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28007,43 +28012,43 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537490</v>
+        <v>537470</v>
       </c>
       <c r="R206" t="n">
-        <v>6656495</v>
+        <v>6656705</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -28106,10 +28111,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236152</v>
+        <v>121236172</v>
       </c>
       <c r="B207" t="n">
-        <v>91334</v>
+        <v>98105</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28118,47 +28123,47 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537756</v>
+        <v>537513</v>
       </c>
       <c r="R207" t="n">
-        <v>6656968</v>
+        <v>6656728</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28185,12 +28190,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28221,10 +28226,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236145</v>
+        <v>121236169</v>
       </c>
       <c r="B208" t="n">
-        <v>94506</v>
+        <v>98105</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28233,35 +28238,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -28270,10 +28275,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537686</v>
+        <v>537474</v>
       </c>
       <c r="R208" t="n">
-        <v>6656878</v>
+        <v>6656770</v>
       </c>
       <c r="S208" t="n">
         <v>4</v>
@@ -28300,12 +28305,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -28336,10 +28341,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236167</v>
+        <v>121236197</v>
       </c>
       <c r="B209" t="n">
-        <v>98104</v>
+        <v>91006</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28348,47 +28353,47 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537517</v>
+        <v>537490</v>
       </c>
       <c r="R209" t="n">
-        <v>6656819</v>
+        <v>6656487</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28451,10 +28456,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236172</v>
+        <v>121236135</v>
       </c>
       <c r="B210" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28486,7 +28491,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -28500,10 +28505,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537513</v>
+        <v>537439</v>
       </c>
       <c r="R210" t="n">
-        <v>6656728</v>
+        <v>6656570</v>
       </c>
       <c r="S210" t="n">
         <v>4</v>
@@ -28530,12 +28535,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28566,10 +28571,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236185</v>
+        <v>121236164</v>
       </c>
       <c r="B211" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28615,10 +28620,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537472</v>
+        <v>537484</v>
       </c>
       <c r="R211" t="n">
-        <v>6656651</v>
+        <v>6656656</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -28681,10 +28686,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236190</v>
+        <v>121236181</v>
       </c>
       <c r="B212" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28693,50 +28698,50 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537476</v>
+        <v>537438</v>
       </c>
       <c r="R212" t="n">
-        <v>6656522</v>
+        <v>6656699</v>
       </c>
       <c r="S212" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28796,10 +28801,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236155</v>
+        <v>121236159</v>
       </c>
       <c r="B213" t="n">
-        <v>90719</v>
+        <v>91476</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28812,21 +28817,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -28845,10 +28850,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537736</v>
+        <v>537686</v>
       </c>
       <c r="R213" t="n">
-        <v>6656837</v>
+        <v>6656739</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28911,10 +28916,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236147</v>
+        <v>121236162</v>
       </c>
       <c r="B214" t="n">
-        <v>90719</v>
+        <v>91335</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28923,25 +28928,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28960,13 +28965,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537705</v>
+        <v>537631</v>
       </c>
       <c r="R214" t="n">
-        <v>6656899</v>
+        <v>6656665</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -29026,10 +29031,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236149</v>
+        <v>121236139</v>
       </c>
       <c r="B215" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29038,47 +29043,54 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J215" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537712</v>
+        <v>537547</v>
       </c>
       <c r="R215" t="n">
-        <v>6657066</v>
+        <v>6656935</v>
       </c>
       <c r="S215" t="n">
         <v>4</v>
@@ -29141,10 +29153,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236184</v>
+        <v>121236182</v>
       </c>
       <c r="B216" t="n">
-        <v>91987</v>
+        <v>90720</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29157,26 +29169,26 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -29190,13 +29202,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537431</v>
+        <v>537413</v>
       </c>
       <c r="R216" t="n">
-        <v>6656597</v>
+        <v>6656645</v>
       </c>
       <c r="S216" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29256,10 +29268,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236163</v>
+        <v>121236147</v>
       </c>
       <c r="B217" t="n">
-        <v>90684</v>
+        <v>90720</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29268,25 +29280,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -29301,17 +29313,17 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537447</v>
+        <v>537705</v>
       </c>
       <c r="R217" t="n">
-        <v>6656508</v>
+        <v>6656899</v>
       </c>
       <c r="S217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29371,10 +29383,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236160</v>
+        <v>121236151</v>
       </c>
       <c r="B218" t="n">
-        <v>94626</v>
+        <v>90720</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29383,47 +29395,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537624</v>
+        <v>537730</v>
       </c>
       <c r="R218" t="n">
-        <v>6656708</v>
+        <v>6656998</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29486,10 +29498,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236139</v>
+        <v>121236196</v>
       </c>
       <c r="B219" t="n">
-        <v>57371</v>
+        <v>91064</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,25 +29510,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29524,28 +29536,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537547</v>
+        <v>537490</v>
       </c>
       <c r="R219" t="n">
-        <v>6656935</v>
+        <v>6656495</v>
       </c>
       <c r="S219" t="n">
         <v>4</v>
@@ -29572,12 +29577,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29608,10 +29613,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236142</v>
+        <v>121236146</v>
       </c>
       <c r="B220" t="n">
-        <v>90684</v>
+        <v>57509</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29620,35 +29625,30 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29660,7 +29660,7 @@
         <v>537687</v>
       </c>
       <c r="R220" t="n">
-        <v>6656911</v>
+        <v>6656879</v>
       </c>
       <c r="S220" t="n">
         <v>4</v>
@@ -29723,10 +29723,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236138</v>
+        <v>121236165</v>
       </c>
       <c r="B221" t="n">
-        <v>94605</v>
+        <v>8424</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29739,43 +29739,43 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>2667</v>
+        <v>106554</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537620</v>
+        <v>537568</v>
       </c>
       <c r="R221" t="n">
-        <v>6656858</v>
+        <v>6657060</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29802,12 +29802,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29816,6 +29816,7 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
+      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -29838,10 +29839,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236187</v>
+        <v>121236143</v>
       </c>
       <c r="B222" t="n">
-        <v>98104</v>
+        <v>91653</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29850,35 +29851,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -29887,10 +29888,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537559</v>
+        <v>537674</v>
       </c>
       <c r="R222" t="n">
-        <v>6656606</v>
+        <v>6656893</v>
       </c>
       <c r="S222" t="n">
         <v>5</v>
@@ -29917,12 +29918,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29953,10 +29954,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236180</v>
+        <v>121236178</v>
       </c>
       <c r="B223" t="n">
-        <v>98104</v>
+        <v>57509</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29965,35 +29966,30 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -30002,13 +29998,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537443</v>
+        <v>537468</v>
       </c>
       <c r="R223" t="n">
-        <v>6656691</v>
+        <v>6656748</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30068,10 +30064,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236197</v>
+        <v>121236138</v>
       </c>
       <c r="B224" t="n">
-        <v>91005</v>
+        <v>94606</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30080,47 +30076,47 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>658</v>
+        <v>2667</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537490</v>
+        <v>537620</v>
       </c>
       <c r="R224" t="n">
-        <v>6656487</v>
+        <v>6656858</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -30147,12 +30143,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30183,10 +30179,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236193</v>
+        <v>121236145</v>
       </c>
       <c r="B225" t="n">
-        <v>92030</v>
+        <v>94507</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30195,50 +30191,50 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5966</v>
+        <v>2809</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537518</v>
+        <v>537686</v>
       </c>
       <c r="R225" t="n">
-        <v>6656512</v>
+        <v>6656878</v>
       </c>
       <c r="S225" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30262,12 +30258,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30298,10 +30294,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236159</v>
+        <v>121236194</v>
       </c>
       <c r="B226" t="n">
-        <v>91475</v>
+        <v>90685</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30310,25 +30306,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>366</v>
+        <v>5447</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -30343,17 +30339,17 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537686</v>
+        <v>537520</v>
       </c>
       <c r="R226" t="n">
-        <v>6656739</v>
+        <v>6656530</v>
       </c>
       <c r="S226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30377,12 +30373,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30413,10 +30409,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236177</v>
+        <v>121236192</v>
       </c>
       <c r="B227" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30425,47 +30421,47 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537470</v>
+        <v>537475</v>
       </c>
       <c r="R227" t="n">
-        <v>6656705</v>
+        <v>6656526</v>
       </c>
       <c r="S227" t="n">
         <v>4</v>
@@ -30528,10 +30524,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236171</v>
+        <v>121236142</v>
       </c>
       <c r="B228" t="n">
-        <v>98104</v>
+        <v>90685</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30540,35 +30536,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30577,10 +30573,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537516</v>
+        <v>537687</v>
       </c>
       <c r="R228" t="n">
-        <v>6656778</v>
+        <v>6656911</v>
       </c>
       <c r="S228" t="n">
         <v>4</v>
@@ -30607,12 +30603,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30643,10 +30639,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236141</v>
+        <v>121236184</v>
       </c>
       <c r="B229" t="n">
-        <v>98104</v>
+        <v>91988</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30655,35 +30651,35 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -30692,13 +30688,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537629</v>
+        <v>537431</v>
       </c>
       <c r="R229" t="n">
-        <v>6656969</v>
+        <v>6656597</v>
       </c>
       <c r="S229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30722,12 +30718,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30758,10 +30754,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236166</v>
+        <v>121236168</v>
       </c>
       <c r="B230" t="n">
-        <v>92028</v>
+        <v>79594</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30774,31 +30770,31 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5964</v>
+        <v>6456</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30807,10 +30803,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537531</v>
+        <v>537571</v>
       </c>
       <c r="R230" t="n">
-        <v>6657006</v>
+        <v>6656818</v>
       </c>
       <c r="S230" t="n">
         <v>5</v>
@@ -30873,10 +30869,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236135</v>
+        <v>121236188</v>
       </c>
       <c r="B231" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30885,50 +30881,57 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537439</v>
+        <v>537594</v>
       </c>
       <c r="R231" t="n">
-        <v>6656570</v>
+        <v>6656653</v>
       </c>
       <c r="S231" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30952,12 +30955,12 @@
       </c>
       <c r="Y231" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -30988,10 +30991,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236182</v>
+        <v>121236137</v>
       </c>
       <c r="B232" t="n">
-        <v>90719</v>
+        <v>91335</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31000,25 +31003,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1202</v>
+        <v>1339</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31037,13 +31040,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537413</v>
+        <v>537682</v>
       </c>
       <c r="R232" t="n">
-        <v>6656645</v>
+        <v>6656810</v>
       </c>
       <c r="S232" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31067,12 +31070,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -31103,10 +31106,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236195</v>
+        <v>121236167</v>
       </c>
       <c r="B233" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -31115,47 +31118,47 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537508</v>
+        <v>537517</v>
       </c>
       <c r="R233" t="n">
-        <v>6656516</v>
+        <v>6656819</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31218,10 +31221,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236137</v>
+        <v>121236141</v>
       </c>
       <c r="B234" t="n">
-        <v>91334</v>
+        <v>98105</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31230,35 +31233,35 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -31267,10 +31270,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537682</v>
+        <v>537629</v>
       </c>
       <c r="R234" t="n">
-        <v>6656810</v>
+        <v>6656969</v>
       </c>
       <c r="S234" t="n">
         <v>4</v>
@@ -31333,10 +31336,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236175</v>
+        <v>121236150</v>
       </c>
       <c r="B235" t="n">
-        <v>98104</v>
+        <v>105210</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31345,30 +31348,30 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -31378,17 +31381,17 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537491</v>
+        <v>537738</v>
       </c>
       <c r="R235" t="n">
-        <v>6656738</v>
+        <v>6657048</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31412,12 +31415,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31448,10 +31451,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236136</v>
+        <v>121236152</v>
       </c>
       <c r="B236" t="n">
-        <v>90666</v>
+        <v>91335</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31460,25 +31463,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>112</v>
+        <v>1339</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -31488,19 +31491,19 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537697</v>
+        <v>537756</v>
       </c>
       <c r="R236" t="n">
-        <v>6656821</v>
+        <v>6656968</v>
       </c>
       <c r="S236" t="n">
         <v>4</v>
@@ -31563,10 +31566,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236143</v>
+        <v>121236136</v>
       </c>
       <c r="B237" t="n">
-        <v>91652</v>
+        <v>90667</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31575,25 +31578,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4769</v>
+        <v>112</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -31603,7 +31606,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31612,13 +31615,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537674</v>
+        <v>537697</v>
       </c>
       <c r="R237" t="n">
-        <v>6656893</v>
+        <v>6656821</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31678,10 +31681,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236186</v>
+        <v>121236160</v>
       </c>
       <c r="B238" t="n">
-        <v>98104</v>
+        <v>94627</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31690,35 +31693,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31727,13 +31730,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537546</v>
+        <v>537624</v>
       </c>
       <c r="R238" t="n">
-        <v>6656619</v>
+        <v>6656708</v>
       </c>
       <c r="S238" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -31757,12 +31760,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31793,10 +31796,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236188</v>
+        <v>121236163</v>
       </c>
       <c r="B239" t="n">
-        <v>57371</v>
+        <v>90685</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31805,25 +31808,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -31831,31 +31834,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537594</v>
+        <v>537447</v>
       </c>
       <c r="R239" t="n">
-        <v>6656653</v>
+        <v>6656508</v>
       </c>
       <c r="S239" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31879,12 +31875,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31915,10 +31911,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236140</v>
+        <v>121236157</v>
       </c>
       <c r="B240" t="n">
-        <v>90684</v>
+        <v>90770</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31931,21 +31927,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -31964,10 +31960,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537634</v>
+        <v>537695</v>
       </c>
       <c r="R240" t="n">
-        <v>6657019</v>
+        <v>6656728</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -32030,10 +32026,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236165</v>
+        <v>121236189</v>
       </c>
       <c r="B241" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32042,47 +32038,47 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537568</v>
+        <v>537497</v>
       </c>
       <c r="R241" t="n">
-        <v>6657060</v>
+        <v>6656581</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32123,7 +32119,6 @@
       <c r="AE241" t="b">
         <v>0</v>
       </c>
-      <c r="AF241" t="inlineStr"/>
       <c r="AG241" t="b">
         <v>0</v>
       </c>
@@ -32146,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236178</v>
+        <v>121236175</v>
       </c>
       <c r="B242" t="n">
-        <v>57508</v>
+        <v>98105</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32158,30 +32153,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32190,13 +32190,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537468</v>
+        <v>537491</v>
       </c>
       <c r="R242" t="n">
-        <v>6656748</v>
+        <v>6656738</v>
       </c>
       <c r="S242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236174</v>
+        <v>121236154</v>
       </c>
       <c r="B243" t="n">
-        <v>98104</v>
+        <v>94519</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32268,35 +32268,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>220787</v>
+        <v>2813</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -32305,13 +32305,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537502</v>
+        <v>537724</v>
       </c>
       <c r="R243" t="n">
-        <v>6656738</v>
+        <v>6656830</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32335,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236194</v>
+        <v>121236144</v>
       </c>
       <c r="B244" t="n">
-        <v>90684</v>
+        <v>57372</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,25 +32383,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -32409,21 +32409,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537520</v>
+        <v>537672</v>
       </c>
       <c r="R244" t="n">
-        <v>6656530</v>
+        <v>6656897</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -32450,12 +32450,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236169</v>
+        <v>121236198</v>
       </c>
       <c r="B245" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537474</v>
+        <v>537497</v>
       </c>
       <c r="R245" t="n">
-        <v>6656770</v>
+        <v>6656496</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236189</v>
+        <v>121236190</v>
       </c>
       <c r="B246" t="n">
-        <v>98104</v>
+        <v>90720</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,50 +32613,50 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537497</v>
+        <v>537476</v>
       </c>
       <c r="R246" t="n">
-        <v>6656581</v>
+        <v>6656522</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>121236156</v>
       </c>
       <c r="B247" t="n">
-        <v>94722</v>
+        <v>94723</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>121236134</v>
       </c>
       <c r="B248" t="n">
-        <v>94722</v>
+        <v>94723</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236180</v>
+        <v>121236193</v>
       </c>
       <c r="B190" t="n">
-        <v>98105</v>
+        <v>92031</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,47 +26168,47 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537443</v>
+        <v>537518</v>
       </c>
       <c r="R190" t="n">
-        <v>6656691</v>
+        <v>6656512</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236155</v>
+        <v>121236186</v>
       </c>
       <c r="B191" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,35 +26283,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -26320,13 +26320,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537736</v>
+        <v>537546</v>
       </c>
       <c r="R191" t="n">
-        <v>6656837</v>
+        <v>6656619</v>
       </c>
       <c r="S191" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -26350,12 +26350,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236170</v>
+        <v>121236184</v>
       </c>
       <c r="B192" t="n">
-        <v>98105</v>
+        <v>91988</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,35 +26398,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -26435,13 +26435,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537452</v>
+        <v>537431</v>
       </c>
       <c r="R192" t="n">
-        <v>6656767</v>
+        <v>6656597</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236187</v>
+        <v>121236176</v>
       </c>
       <c r="B193" t="n">
         <v>98105</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -26550,10 +26550,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537559</v>
+        <v>537462</v>
       </c>
       <c r="R193" t="n">
-        <v>6656606</v>
+        <v>6656736</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -26616,10 +26616,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236140</v>
+        <v>121236141</v>
       </c>
       <c r="B194" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -26628,35 +26628,35 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537634</v>
+        <v>537629</v>
       </c>
       <c r="R194" t="n">
-        <v>6657019</v>
+        <v>6656969</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236195</v>
+        <v>121236150</v>
       </c>
       <c r="B195" t="n">
-        <v>57356</v>
+        <v>105210</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,25 +26743,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -26769,24 +26769,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537508</v>
+        <v>537738</v>
       </c>
       <c r="R195" t="n">
-        <v>6656516</v>
+        <v>6657048</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -26810,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236193</v>
+        <v>121236166</v>
       </c>
       <c r="B196" t="n">
-        <v>92031</v>
+        <v>92029</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,30 +26858,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -26891,14 +26891,14 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537518</v>
+        <v>537531</v>
       </c>
       <c r="R196" t="n">
-        <v>6656512</v>
+        <v>6657006</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236149</v>
+        <v>121236190</v>
       </c>
       <c r="B197" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,50 +26973,50 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537712</v>
+        <v>537476</v>
       </c>
       <c r="R197" t="n">
-        <v>6657066</v>
+        <v>6656522</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27040,12 +27040,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236166</v>
+        <v>121236136</v>
       </c>
       <c r="B198" t="n">
-        <v>92029</v>
+        <v>90667</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27088,35 +27088,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5964</v>
+        <v>112</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27125,13 +27125,13 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537531</v>
+        <v>537697</v>
       </c>
       <c r="R198" t="n">
-        <v>6657006</v>
+        <v>6656821</v>
       </c>
       <c r="S198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27155,12 +27155,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27191,7 +27191,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236173</v>
+        <v>121236170</v>
       </c>
       <c r="B199" t="n">
         <v>98105</v>
@@ -27226,7 +27226,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -27240,13 +27240,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537505</v>
+        <v>537452</v>
       </c>
       <c r="R199" t="n">
-        <v>6656739</v>
+        <v>6656767</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27306,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236176</v>
+        <v>121236162</v>
       </c>
       <c r="B200" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27318,35 +27318,35 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -27355,13 +27355,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537462</v>
+        <v>537631</v>
       </c>
       <c r="R200" t="n">
-        <v>6656736</v>
+        <v>6656665</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27385,12 +27385,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27421,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236185</v>
+        <v>121236139</v>
       </c>
       <c r="B201" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27433,50 +27433,57 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537472</v>
+        <v>537547</v>
       </c>
       <c r="R201" t="n">
-        <v>6656651</v>
+        <v>6656935</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27500,12 +27507,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27536,10 +27543,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236171</v>
+        <v>121236153</v>
       </c>
       <c r="B202" t="n">
-        <v>98105</v>
+        <v>91476</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27548,35 +27555,35 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -27585,13 +27592,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537516</v>
+        <v>537763</v>
       </c>
       <c r="R202" t="n">
-        <v>6656778</v>
+        <v>6656846</v>
       </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27615,12 +27622,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27651,10 +27658,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236174</v>
+        <v>121236155</v>
       </c>
       <c r="B203" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27663,35 +27670,35 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27700,13 +27707,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537502</v>
+        <v>537736</v>
       </c>
       <c r="R203" t="n">
-        <v>6656738</v>
+        <v>6656837</v>
       </c>
       <c r="S203" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -27730,12 +27737,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -27766,10 +27773,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236186</v>
+        <v>121236192</v>
       </c>
       <c r="B204" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27778,50 +27785,50 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537546</v>
+        <v>537475</v>
       </c>
       <c r="R204" t="n">
-        <v>6656619</v>
+        <v>6656526</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -27881,10 +27888,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236153</v>
+        <v>121236138</v>
       </c>
       <c r="B205" t="n">
-        <v>91476</v>
+        <v>94606</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27893,35 +27900,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>366</v>
+        <v>2667</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27930,10 +27937,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537763</v>
+        <v>537620</v>
       </c>
       <c r="R205" t="n">
-        <v>6656846</v>
+        <v>6656858</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -27996,7 +28003,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236177</v>
+        <v>121236187</v>
       </c>
       <c r="B206" t="n">
         <v>98105</v>
@@ -28031,7 +28038,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -28045,13 +28052,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537470</v>
+        <v>537559</v>
       </c>
       <c r="R206" t="n">
-        <v>6656705</v>
+        <v>6656606</v>
       </c>
       <c r="S206" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28111,10 +28118,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236172</v>
+        <v>121236151</v>
       </c>
       <c r="B207" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28123,47 +28130,47 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537513</v>
+        <v>537730</v>
       </c>
       <c r="R207" t="n">
-        <v>6656728</v>
+        <v>6656998</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28190,12 +28197,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28226,7 +28233,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236169</v>
+        <v>121236173</v>
       </c>
       <c r="B208" t="n">
         <v>98105</v>
@@ -28261,7 +28268,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -28275,13 +28282,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537474</v>
+        <v>537505</v>
       </c>
       <c r="R208" t="n">
-        <v>6656770</v>
+        <v>6656739</v>
       </c>
       <c r="S208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28341,10 +28348,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236197</v>
+        <v>121236167</v>
       </c>
       <c r="B209" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28353,47 +28360,47 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537490</v>
+        <v>537517</v>
       </c>
       <c r="R209" t="n">
-        <v>6656487</v>
+        <v>6656819</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28456,10 +28463,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236135</v>
+        <v>121236163</v>
       </c>
       <c r="B210" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28468,47 +28475,47 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537439</v>
+        <v>537447</v>
       </c>
       <c r="R210" t="n">
-        <v>6656570</v>
+        <v>6656508</v>
       </c>
       <c r="S210" t="n">
         <v>4</v>
@@ -28571,10 +28578,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236164</v>
+        <v>121236145</v>
       </c>
       <c r="B211" t="n">
-        <v>98105</v>
+        <v>94507</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28583,35 +28590,35 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -28620,13 +28627,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537484</v>
+        <v>537686</v>
       </c>
       <c r="R211" t="n">
-        <v>6656656</v>
+        <v>6656878</v>
       </c>
       <c r="S211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28650,12 +28657,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28686,10 +28693,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236181</v>
+        <v>121236197</v>
       </c>
       <c r="B212" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28698,50 +28705,50 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537438</v>
+        <v>537490</v>
       </c>
       <c r="R212" t="n">
-        <v>6656699</v>
+        <v>6656487</v>
       </c>
       <c r="S212" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28801,10 +28808,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236159</v>
+        <v>121236146</v>
       </c>
       <c r="B213" t="n">
-        <v>91476</v>
+        <v>57509</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28817,31 +28824,26 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>366</v>
+        <v>103021</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -28850,10 +28852,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537686</v>
+        <v>537687</v>
       </c>
       <c r="R213" t="n">
-        <v>6656739</v>
+        <v>6656879</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28916,10 +28918,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236162</v>
+        <v>121236140</v>
       </c>
       <c r="B214" t="n">
-        <v>91335</v>
+        <v>90685</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28932,21 +28934,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28965,13 +28967,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537631</v>
+        <v>537634</v>
       </c>
       <c r="R214" t="n">
-        <v>6656665</v>
+        <v>6657019</v>
       </c>
       <c r="S214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -29031,10 +29033,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236139</v>
+        <v>121236180</v>
       </c>
       <c r="B215" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29043,57 +29045,50 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537547</v>
+        <v>537443</v>
       </c>
       <c r="R215" t="n">
-        <v>6656935</v>
+        <v>6656691</v>
       </c>
       <c r="S215" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29117,12 +29112,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29153,7 +29148,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236182</v>
+        <v>121236147</v>
       </c>
       <c r="B216" t="n">
         <v>90720</v>
@@ -29202,13 +29197,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537413</v>
+        <v>537705</v>
       </c>
       <c r="R216" t="n">
-        <v>6656645</v>
+        <v>6656899</v>
       </c>
       <c r="S216" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29232,12 +29227,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -29268,10 +29263,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236147</v>
+        <v>121236154</v>
       </c>
       <c r="B217" t="n">
-        <v>90720</v>
+        <v>94519</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29280,25 +29275,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1202</v>
+        <v>2813</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -29308,7 +29303,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29317,13 +29312,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537705</v>
+        <v>537724</v>
       </c>
       <c r="R217" t="n">
-        <v>6656899</v>
+        <v>6656830</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29383,10 +29378,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236151</v>
+        <v>121236169</v>
       </c>
       <c r="B218" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29395,47 +29390,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537730</v>
+        <v>537474</v>
       </c>
       <c r="R218" t="n">
-        <v>6656998</v>
+        <v>6656770</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29462,12 +29457,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29498,10 +29493,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236196</v>
+        <v>121236198</v>
       </c>
       <c r="B219" t="n">
-        <v>91064</v>
+        <v>90720</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29510,25 +29505,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29547,13 +29542,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537490</v>
+        <v>537497</v>
       </c>
       <c r="R219" t="n">
-        <v>6656495</v>
+        <v>6656496</v>
       </c>
       <c r="S219" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29613,10 +29608,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236146</v>
+        <v>121236194</v>
       </c>
       <c r="B220" t="n">
-        <v>57509</v>
+        <v>90685</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29625,45 +29620,50 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537687</v>
+        <v>537520</v>
       </c>
       <c r="R220" t="n">
-        <v>6656879</v>
+        <v>6656530</v>
       </c>
       <c r="S220" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -29687,12 +29687,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29723,10 +29723,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236165</v>
+        <v>121236195</v>
       </c>
       <c r="B221" t="n">
-        <v>8424</v>
+        <v>57356</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29735,47 +29735,47 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537568</v>
+        <v>537508</v>
       </c>
       <c r="R221" t="n">
-        <v>6657060</v>
+        <v>6656516</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -29816,7 +29816,6 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
       </c>
@@ -29839,10 +29838,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236143</v>
+        <v>121236196</v>
       </c>
       <c r="B222" t="n">
-        <v>91653</v>
+        <v>91064</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29851,25 +29850,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4769</v>
+        <v>2062</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -29884,17 +29883,17 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537674</v>
+        <v>537490</v>
       </c>
       <c r="R222" t="n">
-        <v>6656893</v>
+        <v>6656495</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29918,12 +29917,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -29954,10 +29953,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236178</v>
+        <v>121236135</v>
       </c>
       <c r="B223" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29966,30 +29965,35 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -29998,10 +30002,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537468</v>
+        <v>537439</v>
       </c>
       <c r="R223" t="n">
-        <v>6656748</v>
+        <v>6656570</v>
       </c>
       <c r="S223" t="n">
         <v>4</v>
@@ -30028,12 +30032,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30064,10 +30068,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236138</v>
+        <v>121236175</v>
       </c>
       <c r="B224" t="n">
-        <v>94606</v>
+        <v>98105</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30076,35 +30080,35 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -30113,10 +30117,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537620</v>
+        <v>537491</v>
       </c>
       <c r="R224" t="n">
-        <v>6656858</v>
+        <v>6656738</v>
       </c>
       <c r="S224" t="n">
         <v>5</v>
@@ -30143,12 +30147,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30179,10 +30183,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236145</v>
+        <v>121236185</v>
       </c>
       <c r="B225" t="n">
-        <v>94507</v>
+        <v>98105</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30191,35 +30195,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -30228,13 +30232,13 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537686</v>
+        <v>537472</v>
       </c>
       <c r="R225" t="n">
-        <v>6656878</v>
+        <v>6656651</v>
       </c>
       <c r="S225" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -30258,12 +30262,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30294,10 +30298,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236194</v>
+        <v>121236144</v>
       </c>
       <c r="B226" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30306,25 +30310,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -30332,21 +30336,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537520</v>
+        <v>537672</v>
       </c>
       <c r="R226" t="n">
-        <v>6656530</v>
+        <v>6656897</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -30373,12 +30377,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30409,10 +30413,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236192</v>
+        <v>121236178</v>
       </c>
       <c r="B227" t="n">
-        <v>57356</v>
+        <v>57509</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30425,43 +30429,38 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537475</v>
+        <v>537468</v>
       </c>
       <c r="R227" t="n">
-        <v>6656526</v>
+        <v>6656748</v>
       </c>
       <c r="S227" t="n">
         <v>4</v>
@@ -30524,10 +30523,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236142</v>
+        <v>121236189</v>
       </c>
       <c r="B228" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30536,35 +30535,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30573,13 +30572,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537687</v>
+        <v>537497</v>
       </c>
       <c r="R228" t="n">
-        <v>6656911</v>
+        <v>6656581</v>
       </c>
       <c r="S228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30603,12 +30602,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30639,10 +30638,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236184</v>
+        <v>121236137</v>
       </c>
       <c r="B229" t="n">
-        <v>91988</v>
+        <v>91335</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30651,30 +30650,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4361</v>
+        <v>1339</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -30688,13 +30687,13 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537431</v>
+        <v>537682</v>
       </c>
       <c r="R229" t="n">
-        <v>6656597</v>
+        <v>6656810</v>
       </c>
       <c r="S229" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30718,12 +30717,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30754,10 +30753,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236168</v>
+        <v>121236149</v>
       </c>
       <c r="B230" t="n">
-        <v>79594</v>
+        <v>98105</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30766,50 +30765,50 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537571</v>
+        <v>537712</v>
       </c>
       <c r="R230" t="n">
-        <v>6656818</v>
+        <v>6657066</v>
       </c>
       <c r="S230" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30833,12 +30832,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30869,10 +30868,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236188</v>
+        <v>121236182</v>
       </c>
       <c r="B231" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30885,21 +30884,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -30907,31 +30906,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537594</v>
+        <v>537413</v>
       </c>
       <c r="R231" t="n">
-        <v>6656653</v>
+        <v>6656645</v>
       </c>
       <c r="S231" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30991,10 +30983,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236137</v>
+        <v>121236157</v>
       </c>
       <c r="B232" t="n">
-        <v>91335</v>
+        <v>90770</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31007,21 +30999,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>1339</v>
+        <v>5321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31040,13 +31032,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537682</v>
+        <v>537695</v>
       </c>
       <c r="R232" t="n">
-        <v>6656810</v>
+        <v>6656728</v>
       </c>
       <c r="S232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31106,7 +31098,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236167</v>
+        <v>121236174</v>
       </c>
       <c r="B233" t="n">
         <v>98105</v>
@@ -31141,7 +31133,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -31155,10 +31147,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537517</v>
+        <v>537502</v>
       </c>
       <c r="R233" t="n">
-        <v>6656819</v>
+        <v>6656738</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31221,10 +31213,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236141</v>
+        <v>121236168</v>
       </c>
       <c r="B234" t="n">
-        <v>98105</v>
+        <v>79594</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31233,35 +31225,35 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -31270,13 +31262,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537629</v>
+        <v>537571</v>
       </c>
       <c r="R234" t="n">
-        <v>6656969</v>
+        <v>6656818</v>
       </c>
       <c r="S234" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31300,12 +31292,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -31336,10 +31328,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236150</v>
+        <v>121236164</v>
       </c>
       <c r="B235" t="n">
-        <v>105210</v>
+        <v>98105</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31348,30 +31340,30 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -31381,17 +31373,17 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537738</v>
+        <v>537484</v>
       </c>
       <c r="R235" t="n">
-        <v>6657048</v>
+        <v>6656656</v>
       </c>
       <c r="S235" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31415,12 +31407,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31451,10 +31443,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236152</v>
+        <v>121236177</v>
       </c>
       <c r="B236" t="n">
-        <v>91335</v>
+        <v>98105</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31463,47 +31455,47 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537756</v>
+        <v>537470</v>
       </c>
       <c r="R236" t="n">
-        <v>6656968</v>
+        <v>6656705</v>
       </c>
       <c r="S236" t="n">
         <v>4</v>
@@ -31530,12 +31522,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31566,10 +31558,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236136</v>
+        <v>121236181</v>
       </c>
       <c r="B237" t="n">
-        <v>90667</v>
+        <v>98105</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -31578,35 +31570,35 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P237" t="inlineStr">
@@ -31615,13 +31607,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537697</v>
+        <v>537438</v>
       </c>
       <c r="R237" t="n">
-        <v>6656821</v>
+        <v>6656699</v>
       </c>
       <c r="S237" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31645,12 +31637,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31681,10 +31673,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236160</v>
+        <v>121236159</v>
       </c>
       <c r="B238" t="n">
-        <v>94627</v>
+        <v>91476</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31693,35 +31685,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2818</v>
+        <v>366</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31730,10 +31722,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537624</v>
+        <v>537686</v>
       </c>
       <c r="R238" t="n">
-        <v>6656708</v>
+        <v>6656739</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31796,10 +31788,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236163</v>
+        <v>121236171</v>
       </c>
       <c r="B239" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31808,47 +31800,47 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537447</v>
+        <v>537516</v>
       </c>
       <c r="R239" t="n">
-        <v>6656508</v>
+        <v>6656778</v>
       </c>
       <c r="S239" t="n">
         <v>4</v>
@@ -31875,12 +31867,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31911,10 +31903,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236157</v>
+        <v>121236165</v>
       </c>
       <c r="B240" t="n">
-        <v>90770</v>
+        <v>8424</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31927,43 +31919,43 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5321</v>
+        <v>106554</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J240" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537695</v>
+        <v>537568</v>
       </c>
       <c r="R240" t="n">
-        <v>6656728</v>
+        <v>6657060</v>
       </c>
       <c r="S240" t="n">
         <v>5</v>
@@ -31990,12 +31982,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32004,6 +31996,7 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
+      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
@@ -32026,10 +32019,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236189</v>
+        <v>121236188</v>
       </c>
       <c r="B241" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32038,47 +32031,54 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537497</v>
+        <v>537594</v>
       </c>
       <c r="R241" t="n">
-        <v>6656581</v>
+        <v>6656653</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32141,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236175</v>
+        <v>121236152</v>
       </c>
       <c r="B242" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32153,50 +32153,50 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537491</v>
+        <v>537756</v>
       </c>
       <c r="R242" t="n">
-        <v>6656738</v>
+        <v>6656968</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32220,12 +32220,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236154</v>
+        <v>121236160</v>
       </c>
       <c r="B243" t="n">
-        <v>94519</v>
+        <v>94627</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32272,31 +32272,31 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2813</v>
+        <v>2818</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -32305,10 +32305,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537724</v>
+        <v>537624</v>
       </c>
       <c r="R243" t="n">
-        <v>6656830</v>
+        <v>6656708</v>
       </c>
       <c r="S243" t="n">
         <v>4</v>
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236144</v>
+        <v>121236142</v>
       </c>
       <c r="B244" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,25 +32383,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -32409,9 +32409,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537672</v>
+        <v>537687</v>
       </c>
       <c r="R244" t="n">
-        <v>6656897</v>
+        <v>6656911</v>
       </c>
       <c r="S244" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236198</v>
+        <v>121236172</v>
       </c>
       <c r="B245" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537497</v>
+        <v>537513</v>
       </c>
       <c r="R245" t="n">
-        <v>6656496</v>
+        <v>6656728</v>
       </c>
       <c r="S245" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236190</v>
+        <v>121236143</v>
       </c>
       <c r="B246" t="n">
-        <v>90720</v>
+        <v>91653</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32613,25 +32613,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -32646,17 +32646,17 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537476</v>
+        <v>537674</v>
       </c>
       <c r="R246" t="n">
-        <v>6656522</v>
+        <v>6656893</v>
       </c>
       <c r="S246" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32680,12 +32680,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -32716,7 +32716,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B247" t="n">
         <v>94723</v>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R247" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B248" t="n">
         <v>94723</v>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R248" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S248" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236193</v>
+        <v>121236155</v>
       </c>
       <c r="B190" t="n">
-        <v>92031</v>
+        <v>90720</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26172,26 +26172,26 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -26201,17 +26201,17 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537518</v>
+        <v>537736</v>
       </c>
       <c r="R190" t="n">
-        <v>6656512</v>
+        <v>6656837</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -26235,12 +26235,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236186</v>
+        <v>121236193</v>
       </c>
       <c r="B191" t="n">
-        <v>98105</v>
+        <v>92031</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,47 +26283,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537546</v>
+        <v>537518</v>
       </c>
       <c r="R191" t="n">
-        <v>6656619</v>
+        <v>6656512</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236184</v>
+        <v>121236170</v>
       </c>
       <c r="B192" t="n">
-        <v>91988</v>
+        <v>98105</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,35 +26398,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -26435,13 +26435,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537431</v>
+        <v>537452</v>
       </c>
       <c r="R192" t="n">
-        <v>6656597</v>
+        <v>6656767</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,7 +26501,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236176</v>
+        <v>121236185</v>
       </c>
       <c r="B193" t="n">
         <v>98105</v>
@@ -26536,7 +26536,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -26550,10 +26550,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537462</v>
+        <v>537472</v>
       </c>
       <c r="R193" t="n">
-        <v>6656736</v>
+        <v>6656651</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -26616,7 +26616,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236141</v>
+        <v>121236174</v>
       </c>
       <c r="B194" t="n">
         <v>98105</v>
@@ -26651,7 +26651,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537629</v>
+        <v>537502</v>
       </c>
       <c r="R194" t="n">
-        <v>6656969</v>
+        <v>6656738</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26695,12 +26695,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26731,10 +26731,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236150</v>
+        <v>121236149</v>
       </c>
       <c r="B195" t="n">
-        <v>105210</v>
+        <v>98105</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,30 +26743,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -26780,10 +26780,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537738</v>
+        <v>537712</v>
       </c>
       <c r="R195" t="n">
-        <v>6657048</v>
+        <v>6657066</v>
       </c>
       <c r="S195" t="n">
         <v>4</v>
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236166</v>
+        <v>121236153</v>
       </c>
       <c r="B196" t="n">
-        <v>92029</v>
+        <v>91476</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,30 +26858,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5964</v>
+        <v>366</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537531</v>
+        <v>537763</v>
       </c>
       <c r="R196" t="n">
-        <v>6657006</v>
+        <v>6656846</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26925,12 +26925,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236190</v>
+        <v>121236138</v>
       </c>
       <c r="B197" t="n">
-        <v>90720</v>
+        <v>94606</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26973,50 +26973,50 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1202</v>
+        <v>2667</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537476</v>
+        <v>537620</v>
       </c>
       <c r="R197" t="n">
-        <v>6656522</v>
+        <v>6656858</v>
       </c>
       <c r="S197" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27040,12 +27040,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236136</v>
+        <v>121236178</v>
       </c>
       <c r="B198" t="n">
-        <v>90667</v>
+        <v>57509</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27092,31 +27092,26 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27125,10 +27120,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537697</v>
+        <v>537468</v>
       </c>
       <c r="R198" t="n">
-        <v>6656821</v>
+        <v>6656748</v>
       </c>
       <c r="S198" t="n">
         <v>4</v>
@@ -27155,12 +27150,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27191,7 +27186,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236170</v>
+        <v>121236171</v>
       </c>
       <c r="B199" t="n">
         <v>98105</v>
@@ -27226,7 +27221,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -27240,10 +27235,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537452</v>
+        <v>537516</v>
       </c>
       <c r="R199" t="n">
-        <v>6656767</v>
+        <v>6656778</v>
       </c>
       <c r="S199" t="n">
         <v>4</v>
@@ -27306,10 +27301,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236162</v>
+        <v>121236163</v>
       </c>
       <c r="B200" t="n">
-        <v>91335</v>
+        <v>90685</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27322,21 +27317,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1339</v>
+        <v>5447</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -27351,14 +27346,14 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537631</v>
+        <v>537447</v>
       </c>
       <c r="R200" t="n">
-        <v>6656665</v>
+        <v>6656508</v>
       </c>
       <c r="S200" t="n">
         <v>4</v>
@@ -27421,10 +27416,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236139</v>
+        <v>121236166</v>
       </c>
       <c r="B201" t="n">
-        <v>57372</v>
+        <v>92029</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27433,57 +27428,50 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537547</v>
+        <v>537531</v>
       </c>
       <c r="R201" t="n">
-        <v>6656935</v>
+        <v>6657006</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27507,12 +27495,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27543,10 +27531,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236153</v>
+        <v>121236198</v>
       </c>
       <c r="B202" t="n">
-        <v>91476</v>
+        <v>90720</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27559,21 +27547,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27588,17 +27576,17 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537763</v>
+        <v>537497</v>
       </c>
       <c r="R202" t="n">
-        <v>6656846</v>
+        <v>6656496</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27622,12 +27610,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27658,10 +27646,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236155</v>
+        <v>121236145</v>
       </c>
       <c r="B203" t="n">
-        <v>90720</v>
+        <v>94507</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27670,25 +27658,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -27698,7 +27686,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -27707,10 +27695,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537736</v>
+        <v>537686</v>
       </c>
       <c r="R203" t="n">
-        <v>6656837</v>
+        <v>6656878</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -27773,10 +27761,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236192</v>
+        <v>121236177</v>
       </c>
       <c r="B204" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27785,47 +27773,47 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537475</v>
+        <v>537470</v>
       </c>
       <c r="R204" t="n">
-        <v>6656526</v>
+        <v>6656705</v>
       </c>
       <c r="S204" t="n">
         <v>4</v>
@@ -27888,10 +27876,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236138</v>
+        <v>121236187</v>
       </c>
       <c r="B205" t="n">
-        <v>94606</v>
+        <v>98105</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27900,35 +27888,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27937,10 +27925,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537620</v>
+        <v>537559</v>
       </c>
       <c r="R205" t="n">
-        <v>6656858</v>
+        <v>6656606</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -27967,12 +27955,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -28003,10 +27991,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236187</v>
+        <v>121236182</v>
       </c>
       <c r="B206" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28015,35 +28003,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -28052,13 +28040,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537559</v>
+        <v>537413</v>
       </c>
       <c r="R206" t="n">
-        <v>6656606</v>
+        <v>6656645</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28118,10 +28106,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236151</v>
+        <v>121236169</v>
       </c>
       <c r="B207" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28130,47 +28118,47 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537730</v>
+        <v>537474</v>
       </c>
       <c r="R207" t="n">
-        <v>6656998</v>
+        <v>6656770</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28197,12 +28185,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28233,10 +28221,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236173</v>
+        <v>121236150</v>
       </c>
       <c r="B208" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28245,30 +28233,30 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -28278,17 +28266,17 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537505</v>
+        <v>537738</v>
       </c>
       <c r="R208" t="n">
-        <v>6656739</v>
+        <v>6657048</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28312,12 +28300,12 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -28348,10 +28336,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236167</v>
+        <v>121236194</v>
       </c>
       <c r="B209" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28360,47 +28348,47 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537517</v>
+        <v>537520</v>
       </c>
       <c r="R209" t="n">
-        <v>6656819</v>
+        <v>6656530</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28463,10 +28451,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236163</v>
+        <v>121236195</v>
       </c>
       <c r="B210" t="n">
-        <v>90685</v>
+        <v>57356</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28475,25 +28463,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -28501,9 +28489,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -28512,13 +28500,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537447</v>
+        <v>537508</v>
       </c>
       <c r="R210" t="n">
-        <v>6656508</v>
+        <v>6656516</v>
       </c>
       <c r="S210" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28542,12 +28530,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28578,10 +28566,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236145</v>
+        <v>121236196</v>
       </c>
       <c r="B211" t="n">
-        <v>94507</v>
+        <v>91064</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28590,25 +28578,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2809</v>
+        <v>2062</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -28618,19 +28606,19 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537686</v>
+        <v>537490</v>
       </c>
       <c r="R211" t="n">
-        <v>6656878</v>
+        <v>6656495</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
@@ -28657,12 +28645,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28693,10 +28681,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236197</v>
+        <v>121236165</v>
       </c>
       <c r="B212" t="n">
-        <v>91006</v>
+        <v>8424</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28705,47 +28693,47 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>658</v>
+        <v>106554</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537490</v>
+        <v>537568</v>
       </c>
       <c r="R212" t="n">
-        <v>6656487</v>
+        <v>6657060</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -28786,6 +28774,7 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
+      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -28808,10 +28797,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236146</v>
+        <v>121236190</v>
       </c>
       <c r="B213" t="n">
-        <v>57509</v>
+        <v>90720</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28824,41 +28813,46 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537687</v>
+        <v>537476</v>
       </c>
       <c r="R213" t="n">
-        <v>6656879</v>
+        <v>6656522</v>
       </c>
       <c r="S213" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28882,12 +28876,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -28918,10 +28912,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236140</v>
+        <v>121236154</v>
       </c>
       <c r="B214" t="n">
-        <v>90685</v>
+        <v>94519</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28934,21 +28928,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5447</v>
+        <v>2813</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -28958,7 +28952,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -28967,13 +28961,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537634</v>
+        <v>537724</v>
       </c>
       <c r="R214" t="n">
-        <v>6657019</v>
+        <v>6656830</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -29033,10 +29027,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236180</v>
+        <v>121236160</v>
       </c>
       <c r="B215" t="n">
-        <v>98105</v>
+        <v>94627</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29045,35 +29039,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29082,13 +29076,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537443</v>
+        <v>537624</v>
       </c>
       <c r="R215" t="n">
-        <v>6656691</v>
+        <v>6656708</v>
       </c>
       <c r="S215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -29112,12 +29106,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29148,10 +29142,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236147</v>
+        <v>121236146</v>
       </c>
       <c r="B216" t="n">
-        <v>90720</v>
+        <v>57509</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29164,31 +29158,26 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29197,13 +29186,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537705</v>
+        <v>537687</v>
       </c>
       <c r="R216" t="n">
-        <v>6656899</v>
+        <v>6656879</v>
       </c>
       <c r="S216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -29263,10 +29252,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236154</v>
+        <v>121236181</v>
       </c>
       <c r="B217" t="n">
-        <v>94519</v>
+        <v>98105</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29275,35 +29264,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29312,13 +29301,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537724</v>
+        <v>537438</v>
       </c>
       <c r="R217" t="n">
-        <v>6656830</v>
+        <v>6656699</v>
       </c>
       <c r="S217" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29342,12 +29331,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29378,10 +29367,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236169</v>
+        <v>121236152</v>
       </c>
       <c r="B218" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29390,47 +29379,47 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537474</v>
+        <v>537756</v>
       </c>
       <c r="R218" t="n">
-        <v>6656770</v>
+        <v>6656968</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29457,12 +29446,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29493,7 +29482,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236198</v>
+        <v>121236147</v>
       </c>
       <c r="B219" t="n">
         <v>90720</v>
@@ -29538,17 +29527,17 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537497</v>
+        <v>537705</v>
       </c>
       <c r="R219" t="n">
-        <v>6656496</v>
+        <v>6656899</v>
       </c>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29572,12 +29561,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29608,10 +29597,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236194</v>
+        <v>121236144</v>
       </c>
       <c r="B220" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29620,25 +29609,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -29646,21 +29635,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537520</v>
+        <v>537672</v>
       </c>
       <c r="R220" t="n">
-        <v>6656530</v>
+        <v>6656897</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29687,12 +29676,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29723,10 +29712,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236195</v>
+        <v>121236151</v>
       </c>
       <c r="B221" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29739,21 +29728,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -29761,24 +29750,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537508</v>
+        <v>537730</v>
       </c>
       <c r="R221" t="n">
-        <v>6656516</v>
+        <v>6656998</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29802,12 +29791,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29838,10 +29827,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236196</v>
+        <v>121236168</v>
       </c>
       <c r="B222" t="n">
-        <v>91064</v>
+        <v>79594</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29850,25 +29839,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>2062</v>
+        <v>6456</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -29878,22 +29867,22 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537490</v>
+        <v>537571</v>
       </c>
       <c r="R222" t="n">
-        <v>6656495</v>
+        <v>6656818</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29953,7 +29942,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236135</v>
+        <v>121236167</v>
       </c>
       <c r="B223" t="n">
         <v>98105</v>
@@ -30002,13 +29991,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537439</v>
+        <v>537517</v>
       </c>
       <c r="R223" t="n">
-        <v>6656570</v>
+        <v>6656819</v>
       </c>
       <c r="S223" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30032,12 +30021,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30068,10 +30057,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236175</v>
+        <v>121236136</v>
       </c>
       <c r="B224" t="n">
-        <v>98105</v>
+        <v>90667</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30080,35 +30069,35 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -30117,13 +30106,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537491</v>
+        <v>537697</v>
       </c>
       <c r="R224" t="n">
-        <v>6656738</v>
+        <v>6656821</v>
       </c>
       <c r="S224" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30147,12 +30136,12 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -30183,10 +30172,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236185</v>
+        <v>121236143</v>
       </c>
       <c r="B225" t="n">
-        <v>98105</v>
+        <v>91653</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30195,35 +30184,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -30232,10 +30221,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537472</v>
+        <v>537674</v>
       </c>
       <c r="R225" t="n">
-        <v>6656651</v>
+        <v>6656893</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -30262,12 +30251,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30298,10 +30287,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236144</v>
+        <v>121236159</v>
       </c>
       <c r="B226" t="n">
-        <v>57372</v>
+        <v>91476</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30314,21 +30303,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>366</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -30336,9 +30325,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30347,13 +30336,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537672</v>
+        <v>537686</v>
       </c>
       <c r="R226" t="n">
-        <v>6656897</v>
+        <v>6656739</v>
       </c>
       <c r="S226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30413,10 +30402,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236178</v>
+        <v>121236173</v>
       </c>
       <c r="B227" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30425,30 +30414,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30457,13 +30451,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537468</v>
+        <v>537505</v>
       </c>
       <c r="R227" t="n">
-        <v>6656748</v>
+        <v>6656739</v>
       </c>
       <c r="S227" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30523,7 +30517,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236189</v>
+        <v>121236176</v>
       </c>
       <c r="B228" t="n">
         <v>98105</v>
@@ -30558,7 +30552,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -30572,10 +30566,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537497</v>
+        <v>537462</v>
       </c>
       <c r="R228" t="n">
-        <v>6656581</v>
+        <v>6656736</v>
       </c>
       <c r="S228" t="n">
         <v>5</v>
@@ -30638,10 +30632,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236137</v>
+        <v>121236197</v>
       </c>
       <c r="B229" t="n">
-        <v>91335</v>
+        <v>91006</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30650,25 +30644,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>1339</v>
+        <v>658</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -30683,17 +30677,17 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537682</v>
+        <v>537490</v>
       </c>
       <c r="R229" t="n">
-        <v>6656810</v>
+        <v>6656487</v>
       </c>
       <c r="S229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -30717,12 +30711,12 @@
       </c>
       <c r="Y229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -30753,10 +30747,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236149</v>
+        <v>121236137</v>
       </c>
       <c r="B230" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30765,47 +30759,47 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537712</v>
+        <v>537682</v>
       </c>
       <c r="R230" t="n">
-        <v>6657066</v>
+        <v>6656810</v>
       </c>
       <c r="S230" t="n">
         <v>4</v>
@@ -30868,10 +30862,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236182</v>
+        <v>121236189</v>
       </c>
       <c r="B231" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30880,35 +30874,35 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -30917,13 +30911,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537413</v>
+        <v>537497</v>
       </c>
       <c r="R231" t="n">
-        <v>6656645</v>
+        <v>6656581</v>
       </c>
       <c r="S231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -30983,10 +30977,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236157</v>
+        <v>121236142</v>
       </c>
       <c r="B232" t="n">
-        <v>90770</v>
+        <v>90685</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30999,21 +30993,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5321</v>
+        <v>5447</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -31032,13 +31026,13 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537695</v>
+        <v>537687</v>
       </c>
       <c r="R232" t="n">
-        <v>6656728</v>
+        <v>6656911</v>
       </c>
       <c r="S232" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31098,7 +31092,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236174</v>
+        <v>121236186</v>
       </c>
       <c r="B233" t="n">
         <v>98105</v>
@@ -31133,7 +31127,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -31147,10 +31141,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537502</v>
+        <v>537546</v>
       </c>
       <c r="R233" t="n">
-        <v>6656738</v>
+        <v>6656619</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31213,10 +31207,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236168</v>
+        <v>121236188</v>
       </c>
       <c r="B234" t="n">
-        <v>79594</v>
+        <v>57372</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31225,25 +31219,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -31251,21 +31245,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537571</v>
+        <v>537594</v>
       </c>
       <c r="R234" t="n">
-        <v>6656818</v>
+        <v>6656653</v>
       </c>
       <c r="S234" t="n">
         <v>5</v>
@@ -31328,10 +31329,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236164</v>
+        <v>121236157</v>
       </c>
       <c r="B235" t="n">
-        <v>98105</v>
+        <v>90770</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31340,35 +31341,35 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -31377,10 +31378,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537484</v>
+        <v>537695</v>
       </c>
       <c r="R235" t="n">
-        <v>6656656</v>
+        <v>6656728</v>
       </c>
       <c r="S235" t="n">
         <v>5</v>
@@ -31407,12 +31408,12 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -31443,10 +31444,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236177</v>
+        <v>121236139</v>
       </c>
       <c r="B236" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31455,47 +31456,54 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537470</v>
+        <v>537547</v>
       </c>
       <c r="R236" t="n">
-        <v>6656705</v>
+        <v>6656935</v>
       </c>
       <c r="S236" t="n">
         <v>4</v>
@@ -31522,12 +31530,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31558,7 +31566,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236181</v>
+        <v>121236164</v>
       </c>
       <c r="B237" t="n">
         <v>98105</v>
@@ -31593,7 +31601,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -31607,13 +31615,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537438</v>
+        <v>537484</v>
       </c>
       <c r="R237" t="n">
-        <v>6656699</v>
+        <v>6656656</v>
       </c>
       <c r="S237" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31673,10 +31681,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236159</v>
+        <v>121236162</v>
       </c>
       <c r="B238" t="n">
-        <v>91476</v>
+        <v>91335</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31685,25 +31693,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>366</v>
+        <v>1339</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -31722,10 +31730,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537686</v>
+        <v>537631</v>
       </c>
       <c r="R238" t="n">
-        <v>6656739</v>
+        <v>6656665</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31788,10 +31796,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236171</v>
+        <v>121236184</v>
       </c>
       <c r="B239" t="n">
-        <v>98105</v>
+        <v>91988</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31800,35 +31808,35 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -31837,13 +31845,13 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537516</v>
+        <v>537431</v>
       </c>
       <c r="R239" t="n">
-        <v>6656778</v>
+        <v>6656597</v>
       </c>
       <c r="S239" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31903,10 +31911,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236165</v>
+        <v>121236192</v>
       </c>
       <c r="B240" t="n">
-        <v>8424</v>
+        <v>57356</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31915,50 +31923,50 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>106554</v>
+        <v>100109</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537568</v>
+        <v>537475</v>
       </c>
       <c r="R240" t="n">
-        <v>6657060</v>
+        <v>6656526</v>
       </c>
       <c r="S240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31996,7 +32004,6 @@
       <c r="AE240" t="b">
         <v>0</v>
       </c>
-      <c r="AF240" t="inlineStr"/>
       <c r="AG240" t="b">
         <v>0</v>
       </c>
@@ -32019,10 +32026,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236188</v>
+        <v>121236180</v>
       </c>
       <c r="B241" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32031,54 +32038,47 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N241" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537594</v>
+        <v>537443</v>
       </c>
       <c r="R241" t="n">
-        <v>6656653</v>
+        <v>6656691</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32141,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236152</v>
+        <v>121236141</v>
       </c>
       <c r="B242" t="n">
-        <v>91335</v>
+        <v>98105</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32153,47 +32153,47 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537756</v>
+        <v>537629</v>
       </c>
       <c r="R242" t="n">
-        <v>6656968</v>
+        <v>6656969</v>
       </c>
       <c r="S242" t="n">
         <v>4</v>
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236160</v>
+        <v>121236175</v>
       </c>
       <c r="B243" t="n">
-        <v>94627</v>
+        <v>98105</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32268,35 +32268,35 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
@@ -32305,13 +32305,13 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537624</v>
+        <v>537491</v>
       </c>
       <c r="R243" t="n">
-        <v>6656708</v>
+        <v>6656738</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32335,12 +32335,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236142</v>
+        <v>121236172</v>
       </c>
       <c r="B244" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,35 +32383,35 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -32420,10 +32420,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537687</v>
+        <v>537513</v>
       </c>
       <c r="R244" t="n">
-        <v>6656911</v>
+        <v>6656728</v>
       </c>
       <c r="S244" t="n">
         <v>4</v>
@@ -32450,12 +32450,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -32486,7 +32486,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236172</v>
+        <v>121236135</v>
       </c>
       <c r="B245" t="n">
         <v>98105</v>
@@ -32521,7 +32521,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -32535,10 +32535,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537513</v>
+        <v>537439</v>
       </c>
       <c r="R245" t="n">
-        <v>6656728</v>
+        <v>6656570</v>
       </c>
       <c r="S245" t="n">
         <v>4</v>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236143</v>
+        <v>121236140</v>
       </c>
       <c r="B246" t="n">
-        <v>91653</v>
+        <v>90685</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32617,21 +32617,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4769</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -32650,10 +32650,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537674</v>
+        <v>537634</v>
       </c>
       <c r="R246" t="n">
-        <v>6656893</v>
+        <v>6657019</v>
       </c>
       <c r="S246" t="n">
         <v>5</v>
@@ -32716,7 +32716,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236134</v>
+        <v>121236156</v>
       </c>
       <c r="B247" t="n">
         <v>94723</v>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32761,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537430</v>
+        <v>537701</v>
       </c>
       <c r="R247" t="n">
-        <v>6656501</v>
+        <v>6656808</v>
       </c>
       <c r="S247" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B248" t="n">
         <v>94723</v>
@@ -32866,7 +32866,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -32876,17 +32876,17 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R248" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S248" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -26156,10 +26156,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236155</v>
+        <v>121236141</v>
       </c>
       <c r="B190" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -26168,35 +26168,35 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -26205,10 +26205,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537736</v>
+        <v>537629</v>
       </c>
       <c r="R190" t="n">
-        <v>6656837</v>
+        <v>6656969</v>
       </c>
       <c r="S190" t="n">
         <v>4</v>
@@ -26271,10 +26271,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236193</v>
+        <v>121236186</v>
       </c>
       <c r="B191" t="n">
-        <v>92031</v>
+        <v>98105</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,47 +26283,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537518</v>
+        <v>537546</v>
       </c>
       <c r="R191" t="n">
-        <v>6656512</v>
+        <v>6656619</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -26386,10 +26386,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236170</v>
+        <v>121236166</v>
       </c>
       <c r="B192" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,35 +26398,35 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -26435,13 +26435,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537452</v>
+        <v>537531</v>
       </c>
       <c r="R192" t="n">
-        <v>6656767</v>
+        <v>6657006</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,10 +26501,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236185</v>
+        <v>121236198</v>
       </c>
       <c r="B193" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,50 +26513,50 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537472</v>
+        <v>537497</v>
       </c>
       <c r="R193" t="n">
-        <v>6656651</v>
+        <v>6656496</v>
       </c>
       <c r="S193" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236174</v>
+        <v>121236177</v>
       </c>
       <c r="B194" t="n">
         <v>98105</v>
@@ -26651,7 +26651,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -26665,13 +26665,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537502</v>
+        <v>537470</v>
       </c>
       <c r="R194" t="n">
-        <v>6656738</v>
+        <v>6656705</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236149</v>
+        <v>121236187</v>
       </c>
       <c r="B195" t="n">
         <v>98105</v>
@@ -26766,7 +26766,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -26776,17 +26776,17 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537712</v>
+        <v>537559</v>
       </c>
       <c r="R195" t="n">
-        <v>6657066</v>
+        <v>6656606</v>
       </c>
       <c r="S195" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -26810,12 +26810,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26846,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236153</v>
+        <v>121236147</v>
       </c>
       <c r="B196" t="n">
-        <v>91476</v>
+        <v>90720</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26862,21 +26862,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -26895,10 +26895,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537763</v>
+        <v>537705</v>
       </c>
       <c r="R196" t="n">
-        <v>6656846</v>
+        <v>6656899</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26961,10 +26961,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236138</v>
+        <v>121236168</v>
       </c>
       <c r="B197" t="n">
-        <v>94606</v>
+        <v>79594</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26977,31 +26977,31 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -27010,10 +27010,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537620</v>
+        <v>537571</v>
       </c>
       <c r="R197" t="n">
-        <v>6656858</v>
+        <v>6656818</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -27040,12 +27040,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27076,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236178</v>
+        <v>121236154</v>
       </c>
       <c r="B198" t="n">
-        <v>57509</v>
+        <v>94519</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27088,30 +27088,35 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>103021</v>
+        <v>2813</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -27120,10 +27125,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537468</v>
+        <v>537724</v>
       </c>
       <c r="R198" t="n">
-        <v>6656748</v>
+        <v>6656830</v>
       </c>
       <c r="S198" t="n">
         <v>4</v>
@@ -27150,12 +27155,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27186,10 +27191,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236171</v>
+        <v>121236194</v>
       </c>
       <c r="B199" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27198,50 +27203,50 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537516</v>
+        <v>537520</v>
       </c>
       <c r="R199" t="n">
-        <v>6656778</v>
+        <v>6656530</v>
       </c>
       <c r="S199" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27301,10 +27306,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236163</v>
+        <v>121236182</v>
       </c>
       <c r="B200" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27313,25 +27318,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -27346,17 +27351,17 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537447</v>
+        <v>537413</v>
       </c>
       <c r="R200" t="n">
-        <v>6656508</v>
+        <v>6656645</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27380,12 +27385,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27416,10 +27421,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236166</v>
+        <v>121236139</v>
       </c>
       <c r="B201" t="n">
-        <v>92029</v>
+        <v>57372</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -27428,50 +27433,57 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537531</v>
+        <v>537547</v>
       </c>
       <c r="R201" t="n">
-        <v>6657006</v>
+        <v>6656935</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27495,12 +27507,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27531,10 +27543,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236198</v>
+        <v>121236188</v>
       </c>
       <c r="B202" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27547,21 +27559,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27569,24 +27581,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537497</v>
+        <v>537594</v>
       </c>
       <c r="R202" t="n">
-        <v>6656496</v>
+        <v>6656653</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27646,10 +27665,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236145</v>
+        <v>121236163</v>
       </c>
       <c r="B203" t="n">
-        <v>94507</v>
+        <v>90685</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27662,21 +27681,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -27686,19 +27705,19 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537686</v>
+        <v>537447</v>
       </c>
       <c r="R203" t="n">
-        <v>6656878</v>
+        <v>6656508</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -27761,10 +27780,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236177</v>
+        <v>121236137</v>
       </c>
       <c r="B204" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27773,35 +27792,35 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27810,10 +27829,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537470</v>
+        <v>537682</v>
       </c>
       <c r="R204" t="n">
-        <v>6656705</v>
+        <v>6656810</v>
       </c>
       <c r="S204" t="n">
         <v>4</v>
@@ -27840,12 +27859,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27876,10 +27895,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236187</v>
+        <v>121236178</v>
       </c>
       <c r="B205" t="n">
-        <v>98105</v>
+        <v>57509</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27888,35 +27907,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27925,13 +27939,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537559</v>
+        <v>537468</v>
       </c>
       <c r="R205" t="n">
-        <v>6656606</v>
+        <v>6656748</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -27991,10 +28005,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236182</v>
+        <v>121236167</v>
       </c>
       <c r="B206" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28003,35 +28017,35 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -28040,13 +28054,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537413</v>
+        <v>537517</v>
       </c>
       <c r="R206" t="n">
-        <v>6656645</v>
+        <v>6656819</v>
       </c>
       <c r="S206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28106,10 +28120,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236169</v>
+        <v>121236150</v>
       </c>
       <c r="B207" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28118,30 +28132,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -28151,14 +28165,14 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537474</v>
+        <v>537738</v>
       </c>
       <c r="R207" t="n">
-        <v>6656770</v>
+        <v>6657048</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28185,12 +28199,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -28221,10 +28235,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236150</v>
+        <v>121236136</v>
       </c>
       <c r="B208" t="n">
-        <v>105210</v>
+        <v>90667</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28233,25 +28247,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221144</v>
+        <v>112</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -28261,19 +28275,19 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537738</v>
+        <v>537697</v>
       </c>
       <c r="R208" t="n">
-        <v>6657048</v>
+        <v>6656821</v>
       </c>
       <c r="S208" t="n">
         <v>4</v>
@@ -28336,10 +28350,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236194</v>
+        <v>121236143</v>
       </c>
       <c r="B209" t="n">
-        <v>90685</v>
+        <v>91653</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28352,21 +28366,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -28381,14 +28395,14 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537520</v>
+        <v>537674</v>
       </c>
       <c r="R209" t="n">
-        <v>6656530</v>
+        <v>6656893</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28415,12 +28429,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -28451,10 +28465,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236195</v>
+        <v>121236144</v>
       </c>
       <c r="B210" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28467,16 +28481,16 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -28491,19 +28505,19 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537508</v>
+        <v>537672</v>
       </c>
       <c r="R210" t="n">
-        <v>6656516</v>
+        <v>6656897</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -28530,12 +28544,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -28566,10 +28580,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236196</v>
+        <v>121236149</v>
       </c>
       <c r="B211" t="n">
-        <v>91064</v>
+        <v>98105</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28582,43 +28596,43 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537490</v>
+        <v>537712</v>
       </c>
       <c r="R211" t="n">
-        <v>6656495</v>
+        <v>6657066</v>
       </c>
       <c r="S211" t="n">
         <v>4</v>
@@ -28645,12 +28659,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -28681,10 +28695,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236165</v>
+        <v>121236153</v>
       </c>
       <c r="B212" t="n">
-        <v>8424</v>
+        <v>91476</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28693,47 +28707,47 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>106554</v>
+        <v>366</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N212" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537568</v>
+        <v>537763</v>
       </c>
       <c r="R212" t="n">
-        <v>6657060</v>
+        <v>6656846</v>
       </c>
       <c r="S212" t="n">
         <v>5</v>
@@ -28760,12 +28774,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28774,7 +28788,6 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -28797,10 +28810,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236190</v>
+        <v>121236171</v>
       </c>
       <c r="B213" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -28809,50 +28822,50 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537476</v>
+        <v>537516</v>
       </c>
       <c r="R213" t="n">
-        <v>6656522</v>
+        <v>6656778</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -28912,10 +28925,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236154</v>
+        <v>121236169</v>
       </c>
       <c r="B214" t="n">
-        <v>94519</v>
+        <v>98105</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -28924,35 +28937,35 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2813</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -28961,10 +28974,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537724</v>
+        <v>537474</v>
       </c>
       <c r="R214" t="n">
-        <v>6656830</v>
+        <v>6656770</v>
       </c>
       <c r="S214" t="n">
         <v>4</v>
@@ -28991,12 +29004,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -29027,10 +29040,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236160</v>
+        <v>121236172</v>
       </c>
       <c r="B215" t="n">
-        <v>94627</v>
+        <v>98105</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29039,35 +29052,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29076,10 +29089,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537624</v>
+        <v>537513</v>
       </c>
       <c r="R215" t="n">
-        <v>6656708</v>
+        <v>6656728</v>
       </c>
       <c r="S215" t="n">
         <v>4</v>
@@ -29106,12 +29119,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29142,10 +29155,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236146</v>
+        <v>121236159</v>
       </c>
       <c r="B216" t="n">
-        <v>57509</v>
+        <v>91476</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29158,26 +29171,31 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>103021</v>
+        <v>366</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29186,10 +29204,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537687</v>
+        <v>537686</v>
       </c>
       <c r="R216" t="n">
-        <v>6656879</v>
+        <v>6656739</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29252,10 +29270,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236181</v>
+        <v>121236160</v>
       </c>
       <c r="B217" t="n">
-        <v>98105</v>
+        <v>94627</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29264,35 +29282,35 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29301,13 +29319,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537438</v>
+        <v>537624</v>
       </c>
       <c r="R217" t="n">
-        <v>6656699</v>
+        <v>6656708</v>
       </c>
       <c r="S217" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -29331,12 +29349,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -29367,10 +29385,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236152</v>
+        <v>121236146</v>
       </c>
       <c r="B218" t="n">
-        <v>91335</v>
+        <v>57509</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29379,47 +29397,42 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J218" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537756</v>
+        <v>537687</v>
       </c>
       <c r="R218" t="n">
-        <v>6656968</v>
+        <v>6656879</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29482,10 +29495,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236147</v>
+        <v>121236192</v>
       </c>
       <c r="B219" t="n">
-        <v>90720</v>
+        <v>57356</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29498,21 +29511,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -29520,24 +29533,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537705</v>
+        <v>537475</v>
       </c>
       <c r="R219" t="n">
-        <v>6656899</v>
+        <v>6656526</v>
       </c>
       <c r="S219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29561,12 +29574,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -29597,10 +29610,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236144</v>
+        <v>121236173</v>
       </c>
       <c r="B220" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29609,35 +29622,35 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -29646,10 +29659,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537672</v>
+        <v>537505</v>
       </c>
       <c r="R220" t="n">
-        <v>6656897</v>
+        <v>6656739</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29676,12 +29689,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -29712,10 +29725,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236151</v>
+        <v>121236197</v>
       </c>
       <c r="B221" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29728,21 +29741,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -29757,17 +29770,17 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537730</v>
+        <v>537490</v>
       </c>
       <c r="R221" t="n">
-        <v>6656998</v>
+        <v>6656487</v>
       </c>
       <c r="S221" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29791,12 +29804,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -29827,10 +29840,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236168</v>
+        <v>121236170</v>
       </c>
       <c r="B222" t="n">
-        <v>79594</v>
+        <v>98105</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -29839,35 +29852,35 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -29876,13 +29889,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537571</v>
+        <v>537452</v>
       </c>
       <c r="R222" t="n">
-        <v>6656818</v>
+        <v>6656767</v>
       </c>
       <c r="S222" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29942,7 +29955,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236167</v>
+        <v>121236185</v>
       </c>
       <c r="B223" t="n">
         <v>98105</v>
@@ -29977,7 +29990,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -29991,10 +30004,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537517</v>
+        <v>537472</v>
       </c>
       <c r="R223" t="n">
-        <v>6656819</v>
+        <v>6656651</v>
       </c>
       <c r="S223" t="n">
         <v>5</v>
@@ -30057,10 +30070,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236136</v>
+        <v>121236152</v>
       </c>
       <c r="B224" t="n">
-        <v>90667</v>
+        <v>91335</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30069,25 +30082,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>112</v>
+        <v>1339</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -30097,19 +30110,19 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537697</v>
+        <v>537756</v>
       </c>
       <c r="R224" t="n">
-        <v>6656821</v>
+        <v>6656968</v>
       </c>
       <c r="S224" t="n">
         <v>4</v>
@@ -30172,10 +30185,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236143</v>
+        <v>121236138</v>
       </c>
       <c r="B225" t="n">
-        <v>91653</v>
+        <v>94606</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30188,31 +30201,31 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4769</v>
+        <v>2667</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -30221,10 +30234,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537674</v>
+        <v>537620</v>
       </c>
       <c r="R225" t="n">
-        <v>6656893</v>
+        <v>6656858</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -30287,10 +30300,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236159</v>
+        <v>121236164</v>
       </c>
       <c r="B226" t="n">
-        <v>91476</v>
+        <v>98105</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -30299,35 +30312,35 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -30336,13 +30349,13 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537686</v>
+        <v>537484</v>
       </c>
       <c r="R226" t="n">
-        <v>6656739</v>
+        <v>6656656</v>
       </c>
       <c r="S226" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -30366,12 +30379,12 @@
       </c>
       <c r="Y226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -30402,7 +30415,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236173</v>
+        <v>121236174</v>
       </c>
       <c r="B227" t="n">
         <v>98105</v>
@@ -30437,7 +30450,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -30451,10 +30464,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537505</v>
+        <v>537502</v>
       </c>
       <c r="R227" t="n">
-        <v>6656739</v>
+        <v>6656738</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -30517,10 +30530,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236176</v>
+        <v>121236162</v>
       </c>
       <c r="B228" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30529,35 +30542,35 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -30566,13 +30579,13 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537462</v>
+        <v>537631</v>
       </c>
       <c r="R228" t="n">
-        <v>6656736</v>
+        <v>6656665</v>
       </c>
       <c r="S228" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30596,12 +30609,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30632,10 +30645,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236197</v>
+        <v>121236193</v>
       </c>
       <c r="B229" t="n">
-        <v>91006</v>
+        <v>92031</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30648,26 +30661,26 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>658</v>
+        <v>5966</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -30681,10 +30694,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537490</v>
+        <v>537518</v>
       </c>
       <c r="R229" t="n">
-        <v>6656487</v>
+        <v>6656512</v>
       </c>
       <c r="S229" t="n">
         <v>5</v>
@@ -30747,10 +30760,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236137</v>
+        <v>121236175</v>
       </c>
       <c r="B230" t="n">
-        <v>91335</v>
+        <v>98105</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -30759,35 +30772,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -30796,13 +30809,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537682</v>
+        <v>537491</v>
       </c>
       <c r="R230" t="n">
-        <v>6656810</v>
+        <v>6656738</v>
       </c>
       <c r="S230" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -30826,12 +30839,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -30862,7 +30875,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236189</v>
+        <v>121236176</v>
       </c>
       <c r="B231" t="n">
         <v>98105</v>
@@ -30897,7 +30910,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -30911,10 +30924,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537497</v>
+        <v>537462</v>
       </c>
       <c r="R231" t="n">
-        <v>6656581</v>
+        <v>6656736</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -30977,10 +30990,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236142</v>
+        <v>121236165</v>
       </c>
       <c r="B232" t="n">
-        <v>90685</v>
+        <v>8424</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -30993,46 +31006,46 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537687</v>
+        <v>537568</v>
       </c>
       <c r="R232" t="n">
-        <v>6656911</v>
+        <v>6657060</v>
       </c>
       <c r="S232" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -31056,12 +31069,12 @@
       </c>
       <c r="Y232" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -31070,6 +31083,7 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
+      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -31092,7 +31106,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236186</v>
+        <v>121236180</v>
       </c>
       <c r="B233" t="n">
         <v>98105</v>
@@ -31127,7 +31141,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -31141,10 +31155,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537546</v>
+        <v>537443</v>
       </c>
       <c r="R233" t="n">
-        <v>6656619</v>
+        <v>6656691</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -31207,10 +31221,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236188</v>
+        <v>121236181</v>
       </c>
       <c r="B234" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31219,57 +31233,50 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537594</v>
+        <v>537438</v>
       </c>
       <c r="R234" t="n">
-        <v>6656653</v>
+        <v>6656699</v>
       </c>
       <c r="S234" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31329,10 +31336,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236157</v>
+        <v>121236151</v>
       </c>
       <c r="B235" t="n">
-        <v>90770</v>
+        <v>90720</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31341,25 +31348,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5321</v>
+        <v>1202</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -31374,17 +31381,17 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537695</v>
+        <v>537730</v>
       </c>
       <c r="R235" t="n">
-        <v>6656728</v>
+        <v>6656998</v>
       </c>
       <c r="S235" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -31444,10 +31451,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236139</v>
+        <v>121236142</v>
       </c>
       <c r="B236" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31456,25 +31463,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -31482,28 +31489,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537547</v>
+        <v>537687</v>
       </c>
       <c r="R236" t="n">
-        <v>6656935</v>
+        <v>6656911</v>
       </c>
       <c r="S236" t="n">
         <v>4</v>
@@ -31566,7 +31566,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236164</v>
+        <v>121236189</v>
       </c>
       <c r="B237" t="n">
         <v>98105</v>
@@ -31615,10 +31615,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537484</v>
+        <v>537497</v>
       </c>
       <c r="R237" t="n">
-        <v>6656656</v>
+        <v>6656581</v>
       </c>
       <c r="S237" t="n">
         <v>5</v>
@@ -31681,10 +31681,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236162</v>
+        <v>121236135</v>
       </c>
       <c r="B238" t="n">
-        <v>91335</v>
+        <v>98105</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31693,35 +31693,35 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -31730,10 +31730,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537631</v>
+        <v>537439</v>
       </c>
       <c r="R238" t="n">
-        <v>6656665</v>
+        <v>6656570</v>
       </c>
       <c r="S238" t="n">
         <v>4</v>
@@ -31796,10 +31796,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236184</v>
+        <v>121236190</v>
       </c>
       <c r="B239" t="n">
-        <v>91988</v>
+        <v>90720</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -31812,26 +31812,26 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -31841,17 +31841,17 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537431</v>
+        <v>537476</v>
       </c>
       <c r="R239" t="n">
-        <v>6656597</v>
+        <v>6656522</v>
       </c>
       <c r="S239" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31911,10 +31911,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236192</v>
+        <v>121236155</v>
       </c>
       <c r="B240" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31927,21 +31927,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -31949,21 +31949,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537475</v>
+        <v>537736</v>
       </c>
       <c r="R240" t="n">
-        <v>6656526</v>
+        <v>6656837</v>
       </c>
       <c r="S240" t="n">
         <v>4</v>
@@ -31990,12 +31990,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32026,10 +32026,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236180</v>
+        <v>121236184</v>
       </c>
       <c r="B241" t="n">
-        <v>98105</v>
+        <v>91988</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32038,35 +32038,35 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -32075,10 +32075,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537443</v>
+        <v>537431</v>
       </c>
       <c r="R241" t="n">
-        <v>6656691</v>
+        <v>6656597</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32141,10 +32141,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236141</v>
+        <v>121236157</v>
       </c>
       <c r="B242" t="n">
-        <v>98105</v>
+        <v>90770</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32153,35 +32153,35 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>220787</v>
+        <v>5321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P242" t="inlineStr">
@@ -32190,13 +32190,13 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537629</v>
+        <v>537695</v>
       </c>
       <c r="R242" t="n">
-        <v>6656969</v>
+        <v>6656728</v>
       </c>
       <c r="S242" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236175</v>
+        <v>121236196</v>
       </c>
       <c r="B243" t="n">
-        <v>98105</v>
+        <v>91064</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32272,46 +32272,46 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537491</v>
+        <v>537490</v>
       </c>
       <c r="R243" t="n">
-        <v>6656738</v>
+        <v>6656495</v>
       </c>
       <c r="S243" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32371,10 +32371,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236172</v>
+        <v>121236140</v>
       </c>
       <c r="B244" t="n">
-        <v>98105</v>
+        <v>90685</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,35 +32383,35 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
@@ -32420,13 +32420,13 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537513</v>
+        <v>537634</v>
       </c>
       <c r="R244" t="n">
-        <v>6656728</v>
+        <v>6657019</v>
       </c>
       <c r="S244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -32450,12 +32450,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -32486,10 +32486,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236135</v>
+        <v>121236195</v>
       </c>
       <c r="B245" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,50 +32498,50 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537439</v>
+        <v>537508</v>
       </c>
       <c r="R245" t="n">
-        <v>6656570</v>
+        <v>6656516</v>
       </c>
       <c r="S245" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32565,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,10 +32601,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236140</v>
+        <v>121236145</v>
       </c>
       <c r="B246" t="n">
-        <v>90685</v>
+        <v>94507</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -32617,21 +32617,21 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5447</v>
+        <v>2809</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -32641,7 +32641,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -32650,13 +32650,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537634</v>
+        <v>537686</v>
       </c>
       <c r="R246" t="n">
-        <v>6657019</v>
+        <v>6656878</v>
       </c>
       <c r="S246" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -29498,7 +29498,7 @@
         <v>121236192</v>
       </c>
       <c r="B219" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>121236195</v>
       </c>
       <c r="B245" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>

--- a/artfynd/A 10784-2020 artfynd.xlsx
+++ b/artfynd/A 10784-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY248"/>
+  <dimension ref="A1:AY247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25873,10 +25873,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>120076879</v>
+        <v>120076351</v>
       </c>
       <c r="B188" t="n">
-        <v>91335</v>
+        <v>86398</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -25885,30 +25885,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>366</v>
+        <v>248955</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Kauffman</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -25924,10 +25924,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>537784</v>
+        <v>537522</v>
       </c>
       <c r="R188" t="n">
-        <v>6656889</v>
+        <v>6656647</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -25962,6 +25962,11 @@
           <t>2024-09-28</t>
         </is>
       </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+        </is>
+      </c>
       <c r="AD188" t="b">
         <v>0</v>
       </c>
@@ -25984,17 +25989,17 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr"/>
@@ -26012,10 +26017,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>120076351</v>
+        <v>121236141</v>
       </c>
       <c r="B189" t="n">
-        <v>86398</v>
+        <v>98105</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -26028,48 +26033,46 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>248955</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Kauffman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>537522</v>
+        <v>537629</v>
       </c>
       <c r="R189" t="n">
-        <v>6656647</v>
+        <v>6656969</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -26093,17 +26096,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>K+ röd på hatt och fot. Skivor brunvioletta.</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -26112,51 +26110,29 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
-      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
-      </c>
-      <c r="AH189" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI189" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ189" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr"/>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>Karl Hedin Sågverk - Second opinion Dullbo</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121236141</v>
+        <v>121236186</v>
       </c>
       <c r="B190" t="n">
         <v>98105</v>
@@ -26191,7 +26167,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -26205,13 +26181,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>537629</v>
+        <v>537546</v>
       </c>
       <c r="R190" t="n">
-        <v>6656969</v>
+        <v>6656619</v>
       </c>
       <c r="S190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -26235,12 +26211,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -26271,10 +26247,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121236186</v>
+        <v>121236166</v>
       </c>
       <c r="B191" t="n">
-        <v>98105</v>
+        <v>92029</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -26283,35 +26259,35 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -26320,10 +26296,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>537546</v>
+        <v>537531</v>
       </c>
       <c r="R191" t="n">
-        <v>6656619</v>
+        <v>6657006</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -26386,10 +26362,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121236166</v>
+        <v>121236198</v>
       </c>
       <c r="B192" t="n">
-        <v>92029</v>
+        <v>90720</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -26398,30 +26374,30 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -26431,17 +26407,17 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>537531</v>
+        <v>537497</v>
       </c>
       <c r="R192" t="n">
-        <v>6657006</v>
+        <v>6656496</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -26501,10 +26477,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>121236198</v>
+        <v>121236177</v>
       </c>
       <c r="B193" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -26513,50 +26489,50 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>537497</v>
+        <v>537470</v>
       </c>
       <c r="R193" t="n">
-        <v>6656496</v>
+        <v>6656705</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -26616,7 +26592,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>121236177</v>
+        <v>121236187</v>
       </c>
       <c r="B194" t="n">
         <v>98105</v>
@@ -26651,7 +26627,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -26665,13 +26641,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>537470</v>
+        <v>537559</v>
       </c>
       <c r="R194" t="n">
-        <v>6656705</v>
+        <v>6656606</v>
       </c>
       <c r="S194" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -26731,10 +26707,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>121236187</v>
+        <v>121236147</v>
       </c>
       <c r="B195" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -26743,35 +26719,35 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -26780,10 +26756,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>537559</v>
+        <v>537705</v>
       </c>
       <c r="R195" t="n">
-        <v>6656606</v>
+        <v>6656899</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -26810,12 +26786,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -26846,10 +26822,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>121236147</v>
+        <v>121236168</v>
       </c>
       <c r="B196" t="n">
-        <v>90720</v>
+        <v>79594</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -26858,25 +26834,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -26886,7 +26862,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -26895,10 +26871,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>537705</v>
+        <v>537571</v>
       </c>
       <c r="R196" t="n">
-        <v>6656899</v>
+        <v>6656818</v>
       </c>
       <c r="S196" t="n">
         <v>5</v>
@@ -26925,12 +26901,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -26961,10 +26937,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121236168</v>
+        <v>121236154</v>
       </c>
       <c r="B197" t="n">
-        <v>79594</v>
+        <v>94519</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -26977,21 +26953,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6456</v>
+        <v>2813</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -27001,7 +26977,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -27010,13 +26986,13 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>537571</v>
+        <v>537724</v>
       </c>
       <c r="R197" t="n">
-        <v>6656818</v>
+        <v>6656830</v>
       </c>
       <c r="S197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -27040,12 +27016,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -27076,10 +27052,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121236154</v>
+        <v>121236194</v>
       </c>
       <c r="B198" t="n">
-        <v>94519</v>
+        <v>90685</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -27092,21 +27068,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2813</v>
+        <v>5447</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -27116,22 +27092,22 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>537724</v>
+        <v>537520</v>
       </c>
       <c r="R198" t="n">
-        <v>6656830</v>
+        <v>6656530</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -27155,12 +27131,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -27191,10 +27167,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121236194</v>
+        <v>121236182</v>
       </c>
       <c r="B199" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -27203,25 +27179,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -27236,17 +27212,17 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>537520</v>
+        <v>537413</v>
       </c>
       <c r="R199" t="n">
-        <v>6656530</v>
+        <v>6656645</v>
       </c>
       <c r="S199" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -27306,10 +27282,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>121236182</v>
+        <v>121236139</v>
       </c>
       <c r="B200" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -27322,21 +27298,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -27344,24 +27320,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>537413</v>
+        <v>537547</v>
       </c>
       <c r="R200" t="n">
-        <v>6656645</v>
+        <v>6656935</v>
       </c>
       <c r="S200" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -27385,12 +27368,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -27421,7 +27404,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>121236139</v>
+        <v>121236188</v>
       </c>
       <c r="B201" t="n">
         <v>57372</v>
@@ -27477,13 +27460,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>537547</v>
+        <v>537594</v>
       </c>
       <c r="R201" t="n">
-        <v>6656935</v>
+        <v>6656653</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -27507,12 +27490,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -27543,10 +27526,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>121236188</v>
+        <v>121236163</v>
       </c>
       <c r="B202" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -27555,25 +27538,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -27581,31 +27564,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>537594</v>
+        <v>537447</v>
       </c>
       <c r="R202" t="n">
-        <v>6656653</v>
+        <v>6656508</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -27629,12 +27605,12 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -27665,10 +27641,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>121236163</v>
+        <v>121236137</v>
       </c>
       <c r="B203" t="n">
-        <v>90685</v>
+        <v>91335</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -27681,21 +27657,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -27710,14 +27686,14 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>537447</v>
+        <v>537682</v>
       </c>
       <c r="R203" t="n">
-        <v>6656508</v>
+        <v>6656810</v>
       </c>
       <c r="S203" t="n">
         <v>4</v>
@@ -27780,10 +27756,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>121236137</v>
+        <v>121236178</v>
       </c>
       <c r="B204" t="n">
-        <v>91335</v>
+        <v>57509</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -27792,35 +27768,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -27829,10 +27800,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>537682</v>
+        <v>537468</v>
       </c>
       <c r="R204" t="n">
-        <v>6656810</v>
+        <v>6656748</v>
       </c>
       <c r="S204" t="n">
         <v>4</v>
@@ -27859,12 +27830,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -27895,10 +27866,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>121236178</v>
+        <v>121236167</v>
       </c>
       <c r="B205" t="n">
-        <v>57509</v>
+        <v>98105</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -27907,30 +27878,35 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -27939,13 +27915,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>537468</v>
+        <v>537517</v>
       </c>
       <c r="R205" t="n">
-        <v>6656748</v>
+        <v>6656819</v>
       </c>
       <c r="S205" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -28005,10 +27981,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>121236167</v>
+        <v>121236150</v>
       </c>
       <c r="B206" t="n">
-        <v>98105</v>
+        <v>105210</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -28017,30 +27993,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -28050,17 +28026,17 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>537517</v>
+        <v>537738</v>
       </c>
       <c r="R206" t="n">
-        <v>6656819</v>
+        <v>6657048</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -28084,12 +28060,12 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -28120,10 +28096,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121236150</v>
+        <v>121236136</v>
       </c>
       <c r="B207" t="n">
-        <v>105210</v>
+        <v>90667</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -28132,25 +28108,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221144</v>
+        <v>112</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -28160,19 +28136,19 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>537738</v>
+        <v>537697</v>
       </c>
       <c r="R207" t="n">
-        <v>6657048</v>
+        <v>6656821</v>
       </c>
       <c r="S207" t="n">
         <v>4</v>
@@ -28235,10 +28211,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>121236136</v>
+        <v>121236143</v>
       </c>
       <c r="B208" t="n">
-        <v>90667</v>
+        <v>91653</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -28247,25 +28223,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>112</v>
+        <v>4769</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -28275,7 +28251,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -28284,13 +28260,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>537697</v>
+        <v>537674</v>
       </c>
       <c r="R208" t="n">
-        <v>6656821</v>
+        <v>6656893</v>
       </c>
       <c r="S208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -28350,10 +28326,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>121236143</v>
+        <v>121236144</v>
       </c>
       <c r="B209" t="n">
-        <v>91653</v>
+        <v>57372</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -28362,25 +28338,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -28388,9 +28364,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -28399,10 +28375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>537674</v>
+        <v>537672</v>
       </c>
       <c r="R209" t="n">
-        <v>6656893</v>
+        <v>6656897</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -28465,10 +28441,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>121236144</v>
+        <v>121236149</v>
       </c>
       <c r="B210" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -28477,50 +28453,50 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>537672</v>
+        <v>537712</v>
       </c>
       <c r="R210" t="n">
-        <v>6656897</v>
+        <v>6657066</v>
       </c>
       <c r="S210" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -28580,10 +28556,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>121236149</v>
+        <v>121236153</v>
       </c>
       <c r="B211" t="n">
-        <v>98105</v>
+        <v>91476</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -28592,50 +28568,50 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>537712</v>
+        <v>537763</v>
       </c>
       <c r="R211" t="n">
-        <v>6657066</v>
+        <v>6656846</v>
       </c>
       <c r="S211" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -28695,10 +28671,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>121236153</v>
+        <v>121236171</v>
       </c>
       <c r="B212" t="n">
-        <v>91476</v>
+        <v>98105</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28707,35 +28683,35 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>366</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -28744,13 +28720,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>537763</v>
+        <v>537516</v>
       </c>
       <c r="R212" t="n">
-        <v>6656846</v>
+        <v>6656778</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -28774,12 +28750,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28810,7 +28786,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>121236171</v>
+        <v>121236169</v>
       </c>
       <c r="B213" t="n">
         <v>98105</v>
@@ -28859,10 +28835,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>537516</v>
+        <v>537474</v>
       </c>
       <c r="R213" t="n">
-        <v>6656778</v>
+        <v>6656770</v>
       </c>
       <c r="S213" t="n">
         <v>4</v>
@@ -28925,7 +28901,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>121236169</v>
+        <v>121236172</v>
       </c>
       <c r="B214" t="n">
         <v>98105</v>
@@ -28960,7 +28936,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -28974,10 +28950,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>537474</v>
+        <v>537513</v>
       </c>
       <c r="R214" t="n">
-        <v>6656770</v>
+        <v>6656728</v>
       </c>
       <c r="S214" t="n">
         <v>4</v>
@@ -29040,10 +29016,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>121236172</v>
+        <v>121236159</v>
       </c>
       <c r="B215" t="n">
-        <v>98105</v>
+        <v>91476</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -29052,35 +29028,35 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>366</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -29089,10 +29065,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>537513</v>
+        <v>537686</v>
       </c>
       <c r="R215" t="n">
-        <v>6656728</v>
+        <v>6656739</v>
       </c>
       <c r="S215" t="n">
         <v>4</v>
@@ -29119,12 +29095,12 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -29155,10 +29131,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>121236159</v>
+        <v>121236160</v>
       </c>
       <c r="B216" t="n">
-        <v>91476</v>
+        <v>94627</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -29167,35 +29143,35 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>366</v>
+        <v>2818</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -29204,10 +29180,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>537686</v>
+        <v>537624</v>
       </c>
       <c r="R216" t="n">
-        <v>6656739</v>
+        <v>6656708</v>
       </c>
       <c r="S216" t="n">
         <v>4</v>
@@ -29270,10 +29246,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>121236160</v>
+        <v>121236146</v>
       </c>
       <c r="B217" t="n">
-        <v>94627</v>
+        <v>57509</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -29282,35 +29258,30 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2818</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -29319,10 +29290,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>537624</v>
+        <v>537687</v>
       </c>
       <c r="R217" t="n">
-        <v>6656708</v>
+        <v>6656879</v>
       </c>
       <c r="S217" t="n">
         <v>4</v>
@@ -29385,10 +29356,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>121236146</v>
+        <v>121236192</v>
       </c>
       <c r="B218" t="n">
-        <v>57509</v>
+        <v>57481</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -29401,38 +29372,43 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>537687</v>
+        <v>537475</v>
       </c>
       <c r="R218" t="n">
-        <v>6656879</v>
+        <v>6656526</v>
       </c>
       <c r="S218" t="n">
         <v>4</v>
@@ -29459,12 +29435,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -29495,10 +29471,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>121236192</v>
+        <v>121236173</v>
       </c>
       <c r="B219" t="n">
-        <v>57481</v>
+        <v>98105</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -29507,50 +29483,50 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>537475</v>
+        <v>537505</v>
       </c>
       <c r="R219" t="n">
-        <v>6656526</v>
+        <v>6656739</v>
       </c>
       <c r="S219" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -29610,10 +29586,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>121236173</v>
+        <v>121236197</v>
       </c>
       <c r="B220" t="n">
-        <v>98105</v>
+        <v>91006</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -29622,47 +29598,47 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>537505</v>
+        <v>537490</v>
       </c>
       <c r="R220" t="n">
-        <v>6656739</v>
+        <v>6656487</v>
       </c>
       <c r="S220" t="n">
         <v>5</v>
@@ -29725,10 +29701,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>121236197</v>
+        <v>121236170</v>
       </c>
       <c r="B221" t="n">
-        <v>91006</v>
+        <v>98105</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -29737,50 +29713,50 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>537490</v>
+        <v>537452</v>
       </c>
       <c r="R221" t="n">
-        <v>6656487</v>
+        <v>6656767</v>
       </c>
       <c r="S221" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -29840,7 +29816,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>121236170</v>
+        <v>121236185</v>
       </c>
       <c r="B222" t="n">
         <v>98105</v>
@@ -29875,7 +29851,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -29889,13 +29865,13 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>537452</v>
+        <v>537472</v>
       </c>
       <c r="R222" t="n">
-        <v>6656767</v>
+        <v>6656651</v>
       </c>
       <c r="S222" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -29955,10 +29931,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>121236185</v>
+        <v>121236152</v>
       </c>
       <c r="B223" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -29967,50 +29943,50 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>537472</v>
+        <v>537756</v>
       </c>
       <c r="R223" t="n">
-        <v>6656651</v>
+        <v>6656968</v>
       </c>
       <c r="S223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -30034,12 +30010,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -30070,10 +30046,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>121236152</v>
+        <v>121236138</v>
       </c>
       <c r="B224" t="n">
-        <v>91335</v>
+        <v>94606</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -30086,46 +30062,46 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1339</v>
+        <v>2667</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>537756</v>
+        <v>537620</v>
       </c>
       <c r="R224" t="n">
-        <v>6656968</v>
+        <v>6656858</v>
       </c>
       <c r="S224" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -30185,10 +30161,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>121236138</v>
+        <v>121236164</v>
       </c>
       <c r="B225" t="n">
-        <v>94606</v>
+        <v>98105</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -30197,35 +30173,35 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2667</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -30234,10 +30210,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>537620</v>
+        <v>537484</v>
       </c>
       <c r="R225" t="n">
-        <v>6656858</v>
+        <v>6656656</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -30264,12 +30240,12 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -30300,7 +30276,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>121236164</v>
+        <v>121236174</v>
       </c>
       <c r="B226" t="n">
         <v>98105</v>
@@ -30335,7 +30311,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -30349,10 +30325,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>537484</v>
+        <v>537502</v>
       </c>
       <c r="R226" t="n">
-        <v>6656656</v>
+        <v>6656738</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -30415,10 +30391,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>121236174</v>
+        <v>121236162</v>
       </c>
       <c r="B227" t="n">
-        <v>98105</v>
+        <v>91335</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -30427,35 +30403,35 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -30464,13 +30440,13 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>537502</v>
+        <v>537631</v>
       </c>
       <c r="R227" t="n">
-        <v>6656738</v>
+        <v>6656665</v>
       </c>
       <c r="S227" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -30494,12 +30470,12 @@
       </c>
       <c r="Y227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -30530,10 +30506,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>121236162</v>
+        <v>121236193</v>
       </c>
       <c r="B228" t="n">
-        <v>91335</v>
+        <v>92031</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -30542,30 +30518,30 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>1339</v>
+        <v>5966</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -30575,17 +30551,17 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>537631</v>
+        <v>537518</v>
       </c>
       <c r="R228" t="n">
-        <v>6656665</v>
+        <v>6656512</v>
       </c>
       <c r="S228" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -30609,12 +30585,12 @@
       </c>
       <c r="Y228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -30645,10 +30621,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>121236193</v>
+        <v>121236175</v>
       </c>
       <c r="B229" t="n">
-        <v>92031</v>
+        <v>98105</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -30657,47 +30633,47 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>537518</v>
+        <v>537491</v>
       </c>
       <c r="R229" t="n">
-        <v>6656512</v>
+        <v>6656738</v>
       </c>
       <c r="S229" t="n">
         <v>5</v>
@@ -30760,7 +30736,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>121236175</v>
+        <v>121236176</v>
       </c>
       <c r="B230" t="n">
         <v>98105</v>
@@ -30795,7 +30771,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -30809,10 +30785,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>537491</v>
+        <v>537462</v>
       </c>
       <c r="R230" t="n">
-        <v>6656738</v>
+        <v>6656736</v>
       </c>
       <c r="S230" t="n">
         <v>5</v>
@@ -30875,10 +30851,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>121236176</v>
+        <v>121236165</v>
       </c>
       <c r="B231" t="n">
-        <v>98105</v>
+        <v>8424</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -30887,47 +30863,47 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>537462</v>
+        <v>537568</v>
       </c>
       <c r="R231" t="n">
-        <v>6656736</v>
+        <v>6657060</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -30968,6 +30944,7 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>
@@ -30990,10 +30967,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>121236165</v>
+        <v>121236180</v>
       </c>
       <c r="B232" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -31002,47 +30979,47 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N232" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>537568</v>
+        <v>537443</v>
       </c>
       <c r="R232" t="n">
-        <v>6657060</v>
+        <v>6656691</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -31083,7 +31060,6 @@
       <c r="AE232" t="b">
         <v>0</v>
       </c>
-      <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
       </c>
@@ -31106,7 +31082,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>121236180</v>
+        <v>121236181</v>
       </c>
       <c r="B233" t="n">
         <v>98105</v>
@@ -31141,7 +31117,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -31155,13 +31131,13 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>537443</v>
+        <v>537438</v>
       </c>
       <c r="R233" t="n">
-        <v>6656691</v>
+        <v>6656699</v>
       </c>
       <c r="S233" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -31221,10 +31197,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>121236181</v>
+        <v>121236151</v>
       </c>
       <c r="B234" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -31233,50 +31209,50 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Kottars, Dlr</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>537438</v>
+        <v>537730</v>
       </c>
       <c r="R234" t="n">
-        <v>6656699</v>
+        <v>6656998</v>
       </c>
       <c r="S234" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -31300,12 +31276,12 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -31336,10 +31312,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>121236151</v>
+        <v>121236142</v>
       </c>
       <c r="B235" t="n">
-        <v>90720</v>
+        <v>90685</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -31348,25 +31324,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -31381,14 +31357,14 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>Kottars, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>537730</v>
+        <v>537687</v>
       </c>
       <c r="R235" t="n">
-        <v>6656998</v>
+        <v>6656911</v>
       </c>
       <c r="S235" t="n">
         <v>4</v>
@@ -31451,10 +31427,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>121236142</v>
+        <v>121236189</v>
       </c>
       <c r="B236" t="n">
-        <v>90685</v>
+        <v>98105</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -31463,35 +31439,35 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -31500,13 +31476,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>537687</v>
+        <v>537497</v>
       </c>
       <c r="R236" t="n">
-        <v>6656911</v>
+        <v>6656581</v>
       </c>
       <c r="S236" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -31530,12 +31506,12 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -31566,7 +31542,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>121236189</v>
+        <v>121236135</v>
       </c>
       <c r="B237" t="n">
         <v>98105</v>
@@ -31601,7 +31577,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -31615,13 +31591,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>537497</v>
+        <v>537439</v>
       </c>
       <c r="R237" t="n">
-        <v>6656581</v>
+        <v>6656570</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -31645,12 +31621,12 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -31681,10 +31657,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>121236135</v>
+        <v>121236190</v>
       </c>
       <c r="B238" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -31693,50 +31669,50 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>537439</v>
+        <v>537476</v>
       </c>
       <c r="R238" t="n">
-        <v>6656570</v>
+        <v>6656522</v>
       </c>
       <c r="S238" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -31760,12 +31736,12 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -31796,7 +31772,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>121236190</v>
+        <v>121236155</v>
       </c>
       <c r="B239" t="n">
         <v>90720</v>
@@ -31841,17 +31817,17 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>537476</v>
+        <v>537736</v>
       </c>
       <c r="R239" t="n">
-        <v>6656522</v>
+        <v>6656837</v>
       </c>
       <c r="S239" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -31875,12 +31851,12 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -31911,10 +31887,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>121236155</v>
+        <v>121236184</v>
       </c>
       <c r="B240" t="n">
-        <v>90720</v>
+        <v>91988</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -31927,26 +31903,26 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -31960,13 +31936,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>537736</v>
+        <v>537431</v>
       </c>
       <c r="R240" t="n">
-        <v>6656837</v>
+        <v>6656597</v>
       </c>
       <c r="S240" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -31990,12 +31966,12 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -32026,10 +32002,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>121236184</v>
+        <v>121236157</v>
       </c>
       <c r="B241" t="n">
-        <v>91988</v>
+        <v>90770</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -32038,30 +32014,30 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4361</v>
+        <v>5321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -32075,10 +32051,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>537431</v>
+        <v>537695</v>
       </c>
       <c r="R241" t="n">
-        <v>6656597</v>
+        <v>6656728</v>
       </c>
       <c r="S241" t="n">
         <v>5</v>
@@ -32105,12 +32081,12 @@
       </c>
       <c r="Y241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -32141,10 +32117,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>121236157</v>
+        <v>121236196</v>
       </c>
       <c r="B242" t="n">
-        <v>90770</v>
+        <v>91064</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -32153,25 +32129,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5321</v>
+        <v>2062</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -32186,17 +32162,17 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>537695</v>
+        <v>537490</v>
       </c>
       <c r="R242" t="n">
-        <v>6656728</v>
+        <v>6656495</v>
       </c>
       <c r="S242" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -32220,12 +32196,12 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -32256,10 +32232,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>121236196</v>
+        <v>121236140</v>
       </c>
       <c r="B243" t="n">
-        <v>91064</v>
+        <v>90685</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -32268,25 +32244,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -32301,17 +32277,17 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>537490</v>
+        <v>537634</v>
       </c>
       <c r="R243" t="n">
-        <v>6656495</v>
+        <v>6657019</v>
       </c>
       <c r="S243" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -32335,12 +32311,12 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -32371,10 +32347,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>121236140</v>
+        <v>121236195</v>
       </c>
       <c r="B244" t="n">
-        <v>90685</v>
+        <v>57481</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -32383,25 +32359,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -32409,21 +32385,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>537634</v>
+        <v>537508</v>
       </c>
       <c r="R244" t="n">
-        <v>6657019</v>
+        <v>6656516</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -32450,12 +32426,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -32486,10 +32462,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>121236195</v>
+        <v>121236145</v>
       </c>
       <c r="B245" t="n">
-        <v>57481</v>
+        <v>94507</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -32498,25 +32474,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>100109</v>
+        <v>2809</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -32524,24 +32500,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Svarttjärnen, Dlr</t>
+          <t>Sörsnäset, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>537508</v>
+        <v>537686</v>
       </c>
       <c r="R245" t="n">
-        <v>6656516</v>
+        <v>6656878</v>
       </c>
       <c r="S245" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -32565,12 +32541,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -32601,14 +32577,14 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>121236145</v>
+        <v>121236156</v>
       </c>
       <c r="B246" t="n">
-        <v>94507</v>
+        <v>94723</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32617,31 +32593,31 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2809</v>
+        <v>210</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P246" t="inlineStr">
@@ -32650,13 +32626,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>537686</v>
+        <v>537701</v>
       </c>
       <c r="R246" t="n">
-        <v>6656878</v>
+        <v>6656808</v>
       </c>
       <c r="S246" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -32716,7 +32692,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>121236156</v>
+        <v>121236134</v>
       </c>
       <c r="B247" t="n">
         <v>94723</v>
@@ -32751,7 +32727,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -32761,17 +32737,17 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>Sörsnäset, Dlr</t>
+          <t>Svarttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>537701</v>
+        <v>537430</v>
       </c>
       <c r="R247" t="n">
-        <v>6656808</v>
+        <v>6656501</v>
       </c>
       <c r="S247" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -32824,121 +32800,6 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr">
-        <is>
-          <t>Karl Hedin Sågverk - Second opinion Dullbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>121236134</v>
-      </c>
-      <c r="B248" t="n">
-        <v>94723</v>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E248" t="n">
-        <v>210</v>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Buxbaumia viridis</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="P248" t="inlineStr">
-        <is>
-          <t>Svarttjärnen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q248" t="n">
-        <v>537430</v>
-      </c>
-      <c r="R248" t="n">
-        <v>6656501</v>
-      </c>
-      <c r="S248" t="n">
-        <v>4</v>
-      </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>Smedjebacken</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>Söderbärke</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>2024-10-29</t>
-        </is>
-      </c>
-      <c r="AD248" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE248" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG248" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT248" t="inlineStr"/>
-      <c r="AW248" t="inlineStr">
-        <is>
-          <t>Greensway AB</t>
-        </is>
-      </c>
-      <c r="AX248" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
-      </c>
-      <c r="AY248" t="inlineStr">
         <is>
           <t>Karl Hedin Sågverk - Second opinion Dullbo</t>
         </is>
